--- a/requirement_checks/5.1.code_availability/5.1.3.pre-processing_&_pipeline_code/results/preprocessing_code_results.xlsx
+++ b/requirement_checks/5.1.code_availability/5.1.3.pre-processing_&_pipeline_code/results/preprocessing_code_results.xlsx
@@ -178,11 +178,11 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -654,7 +654,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>seq = ' '.join(list(seq.upper().replace("U", "T"))); input_ids = self.tokenizer.encode(seq, add_special_tokens=True); self.k_RNA = [[i[j:j + 4] for j in range(len(i) - 4 + 1)] for i in fasta_seqs]</t>
+          <t>self.tokenizer = AutoTokenizer.from_pretrained(SPLICEBERT_PATH); seq = ' '.join(list(seq.upper().replace("U", "T"))); input_ids = self.tokenizer.encode(seq, add_special_tokens=True)</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -664,11 +664,11 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>The repository contains executable code that tokenizes RNA sequences (including U-&gt;T normalization and k-mer segmentation) using a HuggingFace tokenizer before model processing.</t>
+          <t>Repository contains executable code that tokenizes and formats RNA sequences (including k-mer segmentation and AutoTokenizer encoding) before model use.</t>
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>7270</v>
+        <v>6796</v>
       </c>
     </row>
     <row r="3" ht="78" customHeight="1">
@@ -692,7 +692,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>prompting</t>
+          <t>filtering</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>y, x = torch.meshgrid(torch.arange(0, self.image_height), torch.arange(0, self.image_width)); point_feature_small = lang_feat[seg[1:2]].squeeze(0); concatenated_tensor = torch.cat((all_aggregated_tokens[pos]), dim=1)</t>
+          <t>mask = seg_map != -1; point_feature_small = lang_feat[seg[1:2]].squeeze(0); concatenated_tensor = torch.cat((all_aggregated_tokens[pos]), dim=1)</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -712,14 +712,14 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>The repo includes executable data pipeline code that prepares and collates features and tokens into model-ready inputs, matching the input construction/prompting category.</t>
+          <t>Non-trivial preprocessing logic (mask-based filtering and feature construction) exists in the dataset/loader pipeline.</t>
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>15451</v>
-      </c>
-    </row>
-    <row r="4" ht="97.5" customHeight="1">
+        <v>15624</v>
+      </c>
+    </row>
+    <row r="4" ht="58.5" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -742,8 +742,7 @@
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>response = self.client.chat.completions.create(model=self.model, messages=[{"role": "user", "content": prompt}],; with open(taghelper_path, "w", encoding="utf-8") as f:
-    f.write(TAGHELPER_CODE); Automation Agent → Builds playable Unity scenes programmatically.</t>
+          <t>messages=[{"role": "user", "content": prompt}]; with open(taghelper_path, "w", encoding="utf-8") as f:; f.write(TAGHELPER_CODE)</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -753,11 +752,11 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>The repository files shown do not implement tokenization, data cleaning/deduplication, or non-trivial prompt/input construction; they only include Unity script generation and a simple API call wrapper.</t>
+          <t>There is no executable tokenization, filtering/cleaning, or prompt-construction pipeline code; the code either writes C# files or forwards a provided prompt directly to the API.</t>
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>3846</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1">
@@ -791,7 +790,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>drug = drug[variable_drug].fillna(drug.mean()); Essentiality.columns = [col.split(" ")[0] for col in Essentiality.columns]; self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp))</t>
+          <t>drug = drug[variable_drug].fillna(drug.mean()); Essentiality = Essentiality[var_features].dropna(axis='columns'); common_cells = set(Expression.index)  &amp; set(Essentiality.index)</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -801,60 +800,1099 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>There is non-trivial preprocessing code for filtering/cleaning (column renaming, variable feature selection, NaN imputation, index intersection) and normalization used to construct datasets.</t>
+          <t>There is real preprocessing code that filters columns, handles missing values, aligns datasets on common indices, and normalizes inputs, which fits the filtering/cleaning pipeline category.</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>8464</v>
-      </c>
-    </row>
-    <row r="6" ht="117" customHeight="1">
+        <v>8709</v>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Accelerated Aggregated D-Optimal Designs for Estimating Main Effects in Black-Box Models</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/cchihyu/A2D2E</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>def pd_curve(f_hat, X_train, d, n_grid=100):; def ale_curve(f_hat, X_train, d, n_grid=100, K=40):; def a2d2e_curve(f_hat, X_train, d, n_grid=100, K=40, delta=0.01):</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>model_params/f0_knn.py, model_params/f1_knn.py, model_params/f2_knn.py, model_params/f3_knn.py, model_params/f4_knn.py, model_params/f5_knn.py, model_params/f6_knn.py, src/algorithms.py</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Repository contains model analysis algorithms (PD/ALE/A2D2E curves) and tuned parameter dicts, with no executable preprocessing, deduplication, or prompting pipeline code.</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>3889</v>
+      </c>
+    </row>
+    <row r="7" ht="195" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>EXISTS</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Accelerated Aggregated D-Optimal Designs for Estimating Main Effects in Black-Box Models</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/cchihyu/A2D2E</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>AccidentBench: Benchmarking Multimodal Understanding and Reasoning in Vehicle Accidents and Beyond</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>tokenization, filtering, prompting</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py, tools/make_audio_hf_dataset.ipynb, tools/live_bench/filter.ipynb</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>def analyze(self, text: str, offset: int = 0) -&gt; List[LexemeWithPositions]:; prompt_list.append("&lt;|audio_bos|&gt;&lt;|AUDIO|&gt;&lt;|audio_eos|&gt;" + json_data['prompt']); filtered_data = data["test"].filter(lambda example: example["score"] and example["score"] &gt; 5)</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>tools/make_audio_hf_dataset.ipynb, tools/make_image_hf_dataset.ipynb, tools/make_video_hf_dataset.ipynb, tools/make_video_hf_dataset_from_json.py, lmms_eval/api/filter.py, tools/data_process/data_process_revise_dataset_name.py, tools/live_bench/create_dataset.py, tools/live_bench/filter.ipynb, lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py, lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, setup.py, test_parse.py, data_results/read_results.py, lmms_eval/__main__.py, lmms_eval/evaluator.py, lmms_eval/evaluator_utils.py, lmms_eval/logging_utils.py</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>There is real preprocessing code implementing tokenization (custom analyzers/tokenizer classes), prompt wrapping for audio inputs, and a dataset filtering pipeline.</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>23153</v>
+      </c>
+    </row>
+    <row r="8" ht="39" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>A Comprehensive Survey on Trustworthiness in Reasoning with Large Language Models</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/ybwang119/Awesome-reasoning-safety</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>A Computational Approach to Visual Metonymy</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/cincynlp/ViMET</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="97.5" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>AdamMeme: Adaptively Probe the Reasoning Capacity of Multimodal Large Language Models on Harmfulness</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>prompting, filtering</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>scripts/gen_misb.py, scripts/mining.py, scripts/refinement.py, scripts/scoring.py, scripts/run_llava.py, scripts/utils.py, scripts/prompts.py</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>misb = gpt4o_generate(prompt.replace(r"{task}",data['task']), [data['image'].replace('erased','ori')]); answers = [executor.submit(gpt4o_generate, new_prompt, [data['image']],1) for _ in range(3)]; count = Counter(tasks); tasks = [item for item in count.keys() if count[item] &gt;= 2]</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>scripts/gen_misb.py, scripts/mining.py, scripts/prompts.py, scripts/refinement.py, scripts/run_llava.py, scripts/scoring.py, scripts/utils.py</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>The repo contains executable pipelines that construct prompts for image-text inputs and perform category filtering based on model responses.</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>12136</v>
+      </c>
+    </row>
+    <row r="11" ht="117" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Adaptive Graph Learning with Transformer for Multi-Reservoir Inflow Prediction</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>filtering</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>_preprocess.py, _aligning_time.ipynb, _get_weather_prediction.py</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>X.append(data[i:i+_days_x, :_input_features]); y.append(data[i+_days_x:i+_days_x+_days_y, -1]); scaler_X = MinMaxScaler(feature_range=(0, 1)); ... scaler_X.transform(data['train']['X'].reshape(-1, _input_features)); TPR['Date'] = TPR['Date'].apply(lambda x: x.replace(year=x.year-100) if x.year &gt; 2021 else x)</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>_preprocess.py, _aligning_time.ipynb, _build_graph.ipynb, _edge_change.py, _edge_track_w_detail.py, _feature_importance.py, _get_weather_prediction.py, _pretrain.py, baselines.py</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>There is concrete preprocessing code implementing time-based splitting, sliding-window construction, scaling, and data alignment/aggregation, which qualifies as a filtering/cleaning pipeline.</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>20085</v>
+      </c>
+    </row>
+    <row r="12" ht="97.5" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Addressing Logical Fallacies In Scientific Reasoning From Large Language Models: Towards a Dual-Inference Training Framework</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/hannahdavidsoncollege-maker/ScientificReasoningForEnvironment-MedicineWithLLMs</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>prompting</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>GPT_agent.R</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>.build_prompt &lt;- function(dat, x_target) {; resp &lt;- openai::create_chat_completion(model = object$model, temperature = object$temperature, messages = list(; pairs &lt;- apply(cbind(X, dat$y), 1, function(row) { paste0("((", paste(sprintf("%.6f", row[1:(length(row)-1)]), collapse = ","), "),", sprintf("%.6f", row[length(row)]), ")") })</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>A2D2E_main_function.R, alg.py, compute_truth.R, env.py, GPT_agent.R, md.py, real_data.R</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>There is executable prompt-building and wrapper code (GPT_agent.R) that constructs LLM prompts and parses predictions.</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>16961</v>
-      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Hannah+Walker_Paper.ipynb</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>API_URL = "https://generativelanguage.googleapis.com/v1beta/models/gemini-2.5-flash-lite:generateContent"; def check_implication(sentence,PQ,posP,posQ):; # It then tries all 8 combinations of P, Q and its negations and tests how times the LLM says the answer is correct.</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Hannah+Walker_Paper.ipynb</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>The notebook includes an API-based function to test implications across P/Q variants, which entails constructing prompts and sending them to the LLM.</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>5363</v>
+      </c>
+    </row>
+    <row r="13" ht="312" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>A Dual Large Language Models Architecture with Herald Guided Prompts for Parallel Fine Grained Traffic Signal Control</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/BUPT-ANTlab/HeraldLight</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>a_test_online_model/Llama_inference.py, a_test_online_model/gpt-4o-mini.py</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">messages = [
+        {"role": "system", "content": "You are a master in traffic signal control"},
+        {"role": "user", "content": prompt[0]['content'][0]['text']},
+    ]; outputs = pipeline(
+        messages,
+        max_new_tokens=2048,
+    ); prompt = {
+  "messages": [
+    {
+        "role": "system",
+        "content": [
+            {"type": "text", "text": "You are an AI assistant that helps people find information."}
+</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>utils/pipeline.py, run_dynamiclight.py, run_gpt.py, run_herald_summarize.py, run_llama.py, run_test.py, a_test_online_model/gpt-4o-mini.py, a_test_online_model/Llama_inference.py</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>There is concrete prompt construction code that formats chat messages and passes them to LLM APIs/pipelines.</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>18524</v>
+      </c>
+    </row>
+    <row r="14" ht="78" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Advancing ADMET prediction through multiscale fragment-aware pretraining with MSformer-ADMET</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/ZJUFanLab/MSformer</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>tokenization</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>msformer/MSEncoder.py</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>from tokenizer.tokenizer import MolTranBertTokenizer; encodings = self.tokenizer.batch_encode_plus(batch, padding=True, add_special_tokens=True); input_ids = torch.tensor(encodings['input_ids']).to(self.device)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>notebooks/download_tdc_datasets.ipynb, run_classification_molnet.sh, run_classification_tdc.sh, setup.py, msformer/ftarges.py, msformer/masskg.py, msformer/MSEncoder.py, msformer/MSFinetune.py, msformer/utils.py</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>MSEncoder.py implements a real tokenization/encoding pipeline (batch_encode_plus, input_ids, attention_mask) for molecular fragments, satisfying the tokenization category.</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>15741</v>
+      </c>
+    </row>
+    <row r="15" ht="58.5" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Advancing site-specific disease and pest management in precision agriculture: From reasoning-driven foundation models to adaptive, feedback-based learning</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/nitin-dominic/AgriPathogenDatabase</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="253.5" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Adversarial Attention Perturbations for Large Object Detection Transformers</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>prompting, filtering</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>utils/frcnn_utils/dataset.py, utils/frcnn_utils/voc_dataset.py, utils/dataset_utils/voc/preprocessing.py, extras/detr_extras/d2/detr/dataset_mapper.py, models/detrex/detrex/data/detr_dataset_mapper.py, models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py, models/detrex/detrex/data/dataset_mappers/coco_panoptic_new_baseline_dataset_mapper.py, models/detrex/detectron2/detectron2/data/dataset_mapper.py</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>img = sktsf.resize(img, (C, H * scale, W * scale), mode='reflect', anti_aliasing=False); annos = [utils.transform_instance_annotations(obj, transforms, image_shape) for obj in dataset_dict.pop("annotations") if obj.get("iscrowd", 0) == 0]; dataset_dict["image"] = torch.as_tensor(np.ascontiguousarray(image.transpose(2, 0, 1)))</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>utils/frcnn_utils/dataset.py, utils/frcnn_utils/voc_dataset.py, utils/dataset_utils/voc/preprocessing.py, extras/detr_extras/d2/detr/dataset_mapper.py, models/detrex/detrex/data/detr_dataset_mapper.py, models/detrex/detectron2/detectron2/data/dataset_mapper.py, models/detrex/detectron2/detectron2/layers/wrappers.py, models/detrex/detectron2/detectron2/modeling/mmdet_wrapper.py, models/detrex/detectron2/tests/data/test_dataset.py, models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py, models/detrex/detrex/data/dataset_mappers/coco_panoptic_new_baseline_dataset_mapper.py, models/detrex/detrex/data/dataset_mappers/mask_former_instance_dataset_mapper.py, scripts/attack_deformable_detr.py, scripts/attack_detr.py</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>There is real executable input construction and filtering code (resize/normalize/flip, annotation transforms, and filtering empty/iscrowd) used to prepare data for models.</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>20734</v>
+      </c>
+    </row>
+    <row r="17" ht="136.5" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>A First-Order Logic-Based Alternative to Reward Models in RLHF</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>filtering, prompting, tokenization</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>train/dpo_train.py, train/generate_fol.py, train/sft_training.py</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>train_dataset = train_dataset.filter(lambda sample: sample['better_response_id'] == sample['safer_response_id'] and sample.get(f"is_response_{sample['better_response_id']}_safe", False)); text = tokenizer.apply_chat_template([{'role': "user", "content": samples['prompt']}], tokenize=False, add_generation_prompt=True, enable_thinking=False); prompt_input_ids = Tokenizer.encode(prompt_input, add_special_tokens=False)</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>train/dpo_train.py, train/eval_safeRLHF.py, train/generate_fol.py, train/sft_training.py, train/train.py, utils/LogicalEquivalence.py, utils/sgrpo_trainer.py</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>There is executable code that filters datasets, constructs prompts/chat templates, and tokenizes examples into training inputs.</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>13340</v>
+      </c>
+    </row>
+    <row r="18" ht="78" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>A foundation model for learning genetic associations from brain imaging phenotypes</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>filtering</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>src/dataset_template.py, src/batch_sampler.py</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>idps_raw = idps_raw.loc[:, ~idps_raw.columns.str.replace("(\.\d+)$", "").duplicated()]; self.idps_filt = idps_filt.dropna(how= 'any', axis=0); seen_pairs = set()  # To track unique (item_a_id, item_b_id) combinations in the batch</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>wrapper.py, src/dataset_template.py, auc_plot.ipynb, comical_cli.sh, demo.ipynb, pretrained_weights/load_pretrained_encoders.py, src/batch_sampler.py, src/models.py, src/test.py, src/train.py</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>There is executable preprocessing code for data cleaning/deduplication, including NA/duplicate removal and unique pair filtering.</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>20898</v>
+      </c>
+    </row>
+    <row r="19" ht="58.5" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Agentmandering: A Game-Theoretic Framework for Fair Redistricting via Large Language Model Agents</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Lihaogx/AgentMandering</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>model/agent.py, model/llm_client.py</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>prompt = self.background_info + "\n\n" + self.party_name_prompt; for scheme in schemes:; messages = [{"role": "user", "content": prompt}]</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>install_r_packages.R, main.py, model/agent.py, model/legacy_YCIF_protocol.py, model/llm_client.py, model/unified_YCIF_protocol.py, model/YCIF_protocol.py</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>There is executable code that builds and formats prompts for the LLM, constituting a prompting/input construction pipeline.</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>8184</v>
+      </c>
+    </row>
+    <row r="20" ht="117" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>AgentSHAP: Interpreting LLM Agent Tool Importance with Monte Carlo Shapley Value Estimation</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/GenAISHAP/TokenSHAP</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>token_shap/base.py, token_shap/agent_shap.py</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>api_endpoint = f"{api_url}/api/{'chat' if messages else 'generate'}"; if messages:
+        data['messages'] = messages
+    elif prompt:
+        data['prompt'] = prompt; return {"prompt": original_content, "tools": filtered_tools}</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>notebooks/AgentSHAP Examples.ipynb, notebooks/TokenShap Examples.ipynb, notebooks/VideoSHAP Examples.ipynb, papers/Untitled.ipynb, token_shap/__init__.py, token_shap/agent_shap.py, token_shap/base.py</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>There is executable code that builds request payloads (messages/prompt, images) and tool-based input arguments prior to model invocation, satisfying the prompting wrapper category.</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>14042</v>
+      </c>
+    </row>
+    <row r="21" ht="156" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>A Granular Study of Safety Pretraining under Model Abliteration</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>src/evaluate.py, src/chat.py</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>evaluation_prompts = [f"{system_prompt}\n" f"### Prompt:\n{question}\n\n" f"### Response:\n{response}\n\n" "CLASSIFICATION: " for question, response in zip(batch_questions, batch_responses)]; inputs = tokenizer.batch_encode_plus(evaluation_prompts, return_tensors="pt", padding=True, truncation=True).to(device); toks = tokenizer.apply_chat_template(conversation=conversation, add_generation_prompt=True, return_tensors="pt")</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>slurm.sh, slurm_short.sh, src/abliterate.py, src/chat.py, src/compare.py, src/evaluate.py</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>The code builds structured prompts (including a system instruction and formatted Q/A) and applies chat templates before model inference, constituting an executable prompting/input construction pipeline.</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>8452</v>
+      </c>
+    </row>
+    <row r="22" ht="78" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py, llm/llm1.py, llm/llm2.py, llm/llm3.py, llm/llm4.py, llm/llm5.py, llm/llm6.py</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>response=get_completion(prompt_sys); response,history=get_completion(prompt_sys,prompt,history); You are a helpful assistant that writes data processors code to load different types of data for multimodal Auto-Machine learning task.</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py, llm/gradio.py, llm/llm1.py, llm/llm2.py, llm/llm3.py, llm/llm4.py, llm/llm5.py, llm/llm6.py</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>The repository contains executable code that builds and applies LLM prompts (e.g., safety checks, modality analysis, model selection), constituting a prompting wrapper pipeline.</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>8971</v>
+      </c>
+    </row>
+    <row r="23" ht="58.5" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>AIP-TranLAC: A Transformer-Based Method Integrating LSTM and Attention Mechanism for Predicting Anti-inflammatory Peptides</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Renjingyi123/AIP-TranLAC</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>tokenization</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>train.py</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>aa_dict = {'A': 1, 'R': 2, ... 'X': 23}; pep = pep + 'X' * (30-len_seq); current_pep.append(aa_dict[aa])</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>train.py</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>There is executable preprocessing code that tokenizes sequences (AA-to-index mapping) and pads inputs, which constitutes a tokenization pipeline.</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>3647</v>
+      </c>
+    </row>
+    <row r="24" ht="39" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Aligned or Apart? Multi-Agent Insights into Consumer and Brand Messaging Discrepancies</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/htgan-ai/OPIM</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25" ht="39" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Aligning Deep Implicit Preferences by Learning to Reason Defensively</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Zephyrian-Hugh/Deep-pref</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="78" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>prompting, filtering</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py, llm/llm1.py, llm/llm2.py, llm/llm3.py, llm/llm4.py, llm/llm5.py, llm/llm6.py</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>response=get_completion(prompt_sys); your task is to check whether it has moral or other safety problems... if it has problems ... output 0 ... Otherwise, simply output 1; response,history=get_completion(prompt_sys,prompt,history)</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py, llm/gradio.py, llm/llm1.py, llm/llm2.py, llm/llm3.py, llm/llm4.py, llm/llm5.py, llm/llm6.py</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>The repo contains executable code that constructs prompts for LLM calls and a safety filter that modifies/flags outputs, satisfying prompting and filtering pipeline criteria.</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>8526</v>
+      </c>
+    </row>
+    <row r="27" ht="175.5" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>A Solver‐Aided Hierarchical Language for LLM‐Driven Systems</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>filtering, prompting</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>AIDL/constraint_fitting/filter_programs.py, scripts/2024.02.14.collect_designs.py, scripts/parse_structures.py, scripts/specific_constraints.py</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>if program_errors[prog] &lt; threshold:
+            shutil.copyfile(os.path.join("dataset_quantized", prog), os.path.join("dataset_filtered", prog)); message_list = [
+        {"role": "system", "content": "You are a computer aided design assistant..."}
+    ]; response = client.chat.completions.create(
+                model="gpt-4-turbo-preview",
+                messages=message_list,</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>AIDL/constraint_fitting/filter_programs.py, data/gen_data.ipynb, data/plot_data.ipynb, scripts/2024.02.14.collect_designs.py, scripts/parse_structures.py, scripts/specific_constraints.py, scripts/test.py, setup.py, AIDL/__init__.py, AIDL/aidl.py, AIDL/common.py, AIDL/compositional_constraints.py, AIDL/constraints.py, AIDL/debug.py, AIDL/dispatch.py</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>There is executable code for dataset filtering and for constructing/issuing LLM prompts, satisfying the preprocessing/pipeline criteria.</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>18051</v>
+      </c>
+    </row>
+    <row r="28" ht="195" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>A Structured Framework for Evaluating and Enhancing LLM Robustness</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>filtering</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>scripts/analyze-exhibition-data.py, scripts/analyze-ppt-artworks.js</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>patterns = [r'([^《]+)《([^》]+)》', r'([^《]+)、([^《]+)《([^》]+)》', r'([^《]+)、([^《]+)、([^《]+)《([^》]+)》']; if '学院' in text or '大学' in text:
+    if len(text.strip()) &lt; 20 and '\n' not in text:; const artworkTitlePattern = /^[\u4e00-\u9fa5a-zA-Z\s]+《.+》/;</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>experiments/run_full_pipeline.sh, src/pipeline.py, src/preprocess.py, exhibitions/negative-space-of-the-tide/js/data-loader.js, scripts/add-artwork2-refs.js, scripts/add-artwork3-references.js, scripts/add-artwork4-references.js, scripts/add-multi-image-support.js, scripts/add-remaining-artworks.js, scripts/add-thread6-references.js, scripts/analyze-exhibition-data.py, scripts/analyze-image-paths.js, scripts/analyze-ppt-artworks.js, scripts/apply-batch-multi-image-updates.js, scripts/apply-metadata-enhancements.js, scripts/apply-multi-image-updates.js</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>There is non-trivial, executable data cleaning/extraction code (regex-based parsing and structuring of artworks) implementing a filtering/cleaning pipeline.</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>24154</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>A Survey of Reasoning and Agentic Systems in Time Series</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/blacksnail789521/Time-Series-Agent</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="39" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>A Survey on Latent Reasoning</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/multimodal-art-projection/Latent-Reasoning</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -867,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -977,12 +2015,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1007,7 +2045,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1072,143 +2110,983 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>AccidentBench: Benchmarking Multimodal Understanding and Reasoning in Vehicle Accidents and Beyond</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="13" t="inlineStr">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>A Comprehensive Survey on Trustworthiness in Reasoning with Large Language Models</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/ybwang119/Awesome-reasoning-safety</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>A Computational Approach to Visual Metonymy</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/cincynlp/ViMET</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>AdamMeme: Adaptively Probe the Reasoning Capacity of Multimodal Large Language Models on Harmfulness</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Adaptive Graph Learning with Transformer for Multi-Reservoir Inflow Prediction</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Addressing Logical Fallacies In Scientific Reasoning From Large Language Models: Towards a Dual-Inference Training Framework</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/hannahdavidsoncollege-maker/ScientificReasoningForEnvironment-MedicineWithLLMs</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>A Dual Large Language Models Architecture with Herald Guided Prompts for Parallel Fine Grained Traffic Signal Control</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/BUPT-ANTlab/HeraldLight</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Advancing ADMET prediction through multiscale fragment-aware pretraining with MSformer-ADMET</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/ZJUFanLab/MSformer</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Advancing site-specific disease and pest management in precision agriculture: From reasoning-driven foundation models to adaptive, feedback-based learning</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/nitin-dominic/AgriPathogenDatabase</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Adversarial Attention Perturbations for Large Object Detection Transformers</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>A First-Order Logic-Based Alternative to Reward Models in RLHF</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>A foundation model for learning genetic associations from brain imaging phenotypes</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Agentmandering: A Game-Theoretic Framework for Fair Redistricting via Large Language Model Agents</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Lihaogx/AgentMandering</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>AgentSHAP: Interpreting LLM Agent Tool Importance with Monte Carlo Shapley Value Estimation</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/GenAISHAP/TokenSHAP</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>A Granular Study of Safety Pretraining under Model Abliteration</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>AIP-TranLAC: A Transformer-Based Method Integrating LSTM and Attention Mechanism for Predicting Anti-inflammatory Peptides</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Renjingyi123/AIP-TranLAC</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Aligned or Apart? Multi-Agent Insights into Consumer and Brand Messaging Discrepancies</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/htgan-ai/OPIM</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Aligning Deep Implicit Preferences by Learning to Reason Defensively</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Zephyrian-Hugh/Deep-pref</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>A Solver‐Aided Hierarchical Language for LLM‐Driven Systems</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>A Structured Framework for Evaluating and Enhancing LLM Robustness</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>A Survey of Reasoning and Agentic Systems in Time Series</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/blacksnail789521/Time-Series-Agent</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>A Survey on Latent Reasoning</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/multimodal-art-projection/Latent-Reasoning</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>Agreement Rate</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>4/5 (80%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>18/29 (62%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>Token Usage per Model</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>Requests</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>Input Tokens</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>Output Tokens</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E35" s="15" t="inlineStr">
         <is>
           <t>Total Tokens</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>gpt-5-2025-08-07</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>46,551</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5,441</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51,992</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="B36" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>253,166</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>29,922</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>283,088</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>gpt-5-mini-2025-08-07</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>46,551</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4,441</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>50,992</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="B37" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>151,821</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>13,246</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>165,067</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>gpt-5-nano-2025-08-07</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>46,551</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>8,229</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>54,780</t>
+      <c r="B38" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>274,218</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>42,538</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>316,756</t>
         </is>
       </c>
     </row>
@@ -1223,7 +3101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1367,36 +3245,1093 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Accelerated Aggregated D-Optimal Designs for Estimating Main Effects in Black-Box Models</t>
+          <t>AccidentBench: Benchmarking Multimodal Understanding and Reasoning in Vehicle Accidents and Beyond</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/cchihyu/A2D2E</t>
+          <t>https://github.com/SafeRL-Lab/AccidentBench</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>GPT_agent.R</t>
+          <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/cchihyu/A2D2E/blob/HEAD/GPT_agent.R</t>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>tools/make_audio_hf_dataset.ipynb</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/make_audio_hf_dataset.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>tools/live_bench/filter.ipynb</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/live_bench/filter.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>AdamMeme: Adaptively Probe the Reasoning Capacity of Multimodal Large Language Models on Harmfulness</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>scripts/gen_misb.py</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/gen_misb.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>scripts/mining.py</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/mining.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>scripts/refinement.py</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/refinement.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>scripts/scoring.py</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/scoring.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>scripts/run_llava.py</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/run_llava.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>scripts/utils.py</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/utils.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>scripts/prompts.py</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/prompts.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Adaptive Graph Learning with Transformer for Multi-Reservoir Inflow Prediction</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>_preprocess.py</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_preprocess.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>_aligning_time.ipynb</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_aligning_time.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>_get_weather_prediction.py</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_get_weather_prediction.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Addressing Logical Fallacies In Scientific Reasoning From Large Language Models: Towards a Dual-Inference Training Framework</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/hannahdavidsoncollege-maker/ScientificReasoningForEnvironment-MedicineWithLLMs</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Hannah+Walker_Paper.ipynb</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/hannahdavidsoncollege-maker/ScientificReasoningForEnvironment-MedicineWithLLMs/blob/HEAD/Hannah+Walker_Paper.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>A Dual Large Language Models Architecture with Herald Guided Prompts for Parallel Fine Grained Traffic Signal Control</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/BUPT-ANTlab/HeraldLight</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>a_test_online_model/Llama_inference.py</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/BUPT-ANTlab/HeraldLight/blob/HEAD/a_test_online_model/Llama_inference.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>a_test_online_model/gpt-4o-mini.py</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/BUPT-ANTlab/HeraldLight/blob/HEAD/a_test_online_model/gpt-4o-mini.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Advancing ADMET prediction through multiscale fragment-aware pretraining with MSformer-ADMET</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/ZJUFanLab/MSformer</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>msformer/MSEncoder.py</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/MSEncoder.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Adversarial Attention Perturbations for Large Object Detection Transformers</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>utils/frcnn_utils/dataset.py</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/frcnn_utils/dataset.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>utils/frcnn_utils/voc_dataset.py</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/frcnn_utils/voc_dataset.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>utils/dataset_utils/voc/preprocessing.py</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/dataset_utils/voc/preprocessing.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>extras/detr_extras/d2/detr/dataset_mapper.py</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/extras/detr_extras/d2/detr/dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>models/detrex/detrex/data/detr_dataset_mapper.py</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detrex/data/detr_dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>models/detrex/detrex/data/dataset_mappers/coco_panoptic_new_baseline_dataset_mapper.py</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detrex/data/dataset_mappers/coco_panoptic_new_baseline_dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>models/detrex/detectron2/detectron2/data/dataset_mapper.py</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detectron2/detectron2/data/dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>A First-Order Logic-Based Alternative to Reward Models in RLHF</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>train/dpo_train.py</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/dpo_train.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="9" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>train/generate_fol.py</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/generate_fol.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="8" t="n"/>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>train/sft_training.py</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/sft_training.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>A foundation model for learning genetic associations from brain imaging phenotypes</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>src/dataset_template.py</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical/blob/HEAD/src/dataset_template.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="8" t="n"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>src/batch_sampler.py</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical/blob/HEAD/src/batch_sampler.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Agentmandering: A Game-Theoretic Framework for Fair Redistricting via Large Language Model Agents</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/Lihaogx/AgentMandering</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>model/agent.py</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lihaogx/AgentMandering/blob/HEAD/model/agent.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="8" t="n"/>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>model/llm_client.py</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lihaogx/AgentMandering/blob/HEAD/model/llm_client.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>AgentSHAP: Interpreting LLM Agent Tool Importance with Monte Carlo Shapley Value Estimation</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/GenAISHAP/TokenSHAP</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>token_shap/base.py</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/GenAISHAP/TokenSHAP/blob/HEAD/token_shap/base.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="8" t="n"/>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>token_shap/agent_shap.py</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/GenAISHAP/TokenSHAP/blob/HEAD/token_shap/agent_shap.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>A Granular Study of Safety Pretraining under Model Abliteration</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>src/evaluate.py</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/evaluate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="8" t="n"/>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>src/chat.py</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/chat.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/filter.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm1.py</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm1.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="9" t="n"/>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm2.py</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm2.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="9" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm3.py</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm3.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="9" t="n"/>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm4.py</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm4.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="9" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm5.py</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm5.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm6.py</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm6.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>AIP-TranLAC: A Transformer-Based Method Integrating LSTM and Attention Mechanism for Predicting Anti-inflammatory Peptides</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/Renjingyi123/AIP-TranLAC</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>train.py</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Renjingyi123/AIP-TranLAC/blob/HEAD/train.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/filter.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="9" t="n"/>
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm1.py</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm1.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="9" t="n"/>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm2.py</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm2.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="9" t="n"/>
+      <c r="B55" s="9" t="n"/>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm3.py</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm3.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="9" t="n"/>
+      <c r="B56" s="9" t="n"/>
+      <c r="C56" s="9" t="n"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm4.py</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm4.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="9" t="n"/>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm5.py</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm5.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="8" t="n"/>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm6.py</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm6.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>A Solver‐Aided Hierarchical Language for LLM‐Driven Systems</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>AIDL/constraint_fitting/filter_programs.py</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/AIDL/constraint_fitting/filter_programs.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="9" t="n"/>
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>scripts/2024.02.14.collect_designs.py</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/2024.02.14.collect_designs.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>scripts/parse_structures.py</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/parse_structures.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="8" t="n"/>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>scripts/specific_constraints.py</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/specific_constraints.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>A Structured Framework for Evaluating and Enhancing LLM Robustness</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>scripts/analyze-exhibition-data.py</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/scripts/analyze-exhibition-data.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="8" t="n"/>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>scripts/analyze-ppt-artworks.js</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/scripts/analyze-ppt-artworks.js</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="48">
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="B44:B50"/>
+    <mergeCell ref="C52:C58"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="B25:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="C11:C17"/>
+    <mergeCell ref="A25:A32"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="A44:A50"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C25:C32"/>
+    <mergeCell ref="A52:A58"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="B18:B20"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B11:B17"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B52:B58"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="C44:C50"/>
+    <mergeCell ref="A18:A20"/>
     <mergeCell ref="C5:C6"/>
   </mergeCells>
   <hyperlinks>
@@ -1406,6 +4341,63 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1437,133 +4429,133 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Total Repos Checked</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n">
-        <v>5</v>
+      <c r="B2" s="11" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>EXISTS</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
-        <v>4</v>
+      <c r="B3" s="11" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>NOT_APPLICABLE</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
-        <v>1</v>
+      <c r="B4" s="11" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Skipped (non-GitHub)</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Coverage (%)</t>
         </is>
       </c>
-      <c r="B7" s="10">
-        <f>4/5*100</f>
+      <c r="B7" s="11">
+        <f>20/29*100</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr"/>
-      <c r="B8" s="10" t="inlineStr"/>
+      <c r="A8" s="10" t="inlineStr"/>
+      <c r="B8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>LLM Token Usage</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr"/>
+      <c r="B9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Model / Deployment</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>gpt-5-2025-08-07</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Requests</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>5</v>
+      <c r="B11" s="11" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Input Tokens</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>46,551</t>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>253,166</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Output Tokens</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>5,441</t>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>29,922</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Tokens</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>51,992</t>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>283,088</t>
         </is>
       </c>
     </row>
@@ -1578,7 +4570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1666,7 +4658,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>tokenization, prompting</t>
+          <t>tokenization</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -1676,7 +4668,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>self.tokenizer = AutoTokenizer.from_pretrained(SPLICEBERT_PATH); seq = ' '.join(list(seq.upper().replace("U", "T"))); input_ids = tokenizer.encode(seq, add_special_tokens=True)</t>
+          <t>seq = ' '.join(list(seq.upper().replace("U", "T"))); input_ids = self.tokenizer.encode(seq, add_special_tokens=True); k_RNA = [[i[j:j + 4] for j in range(len(i) - 4 + 1)] for i in fasta_seqs]</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -1686,14 +4678,14 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Executable code in data/mydataset.py and predict.py performs tokenization and input-construction pipelines (SpliceBERT tokenizer + k-mer/Word2Vec features), so preprocessing exists.</t>
+          <t>data/mydataset.py and predict.py implement non-trivial tokenization and input-construction pipelines (sequence normalization, k-mer extraction, tokenizer.encode, Word2Vec feature creation).</t>
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>7146</v>
-      </c>
-    </row>
-    <row r="3" ht="195" customHeight="1">
+        <v>6773</v>
+      </c>
+    </row>
+    <row r="3" ht="156" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -1714,20 +4706,17 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>tokenization</t>
+          <t>tokenization, prompting</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>preprocess/generate_vggttoken.py, utils/demo_dataloader.py, scripts/infer.sh</t>
+          <t>preprocess/generate_vggttoken.py, utils/demo_dataloader.py</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>streamvggt.inference_long_video(image_files, save_dir=save_dir, keys=keys, mode=args.mode, max_num=args.max_num); streamvggt_path = os.path.join(self.img_root, cat, self.streamvggt_token_root, key + '.npy')
-streamvggt_info = np.load(streamvggt_path, allow_pickle=True).item(); all_aggregated_tokens[pos].append(torch.from_numpy(item[key][pos]))
-concatenated_tensor = torch.cat((all_aggregated_tokens[pos]), dim=1)
-collated['aggregated_tokens_list'] = aggregated_tokens_list</t>
+          <t>streamvggt.inference_long_video(image_files, save_dir=save_dir, keys=keys, mode=args.mode, max_num=args.max_num); streamvggt_path = os.path.join(self.img_root, cat, self.streamvggt_token_root, key + '.npy')\nstreamvggt_info = np.load(streamvggt_path, allow_pickle=True).item(); for pos in range(24):\n    concatenated_tensor = torch.cat((all_aggregated_tokens[pos]), dim=1)\n    aggregated_tokens_list.append(concatenated_tensor)</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -1737,20 +4726,20 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>generate_vggttoken.py produces token .npy files via StreamVGGT inference and demo_dataloader.py loads and collates those tokens into input tensors, which qualifies as an executable tokenization/preprocessing pipeline.</t>
+          <t>Preprocessing code to produce and assemble visual tokens (generate_vggttoken.py and demo_dataloader.py) is present, so an executable input/tokenization pipeline exists.</t>
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>14803</v>
-      </c>
-    </row>
-    <row r="4" ht="253.5" customHeight="1">
+        <v>14973</v>
+      </c>
+    </row>
+    <row r="4" ht="78" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>EXISTS</t>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1763,41 +4752,25 @@
           <t>https://github.com/yxwan123/UniGen</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>prompting</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>with open(taghelper_path, "w", encoding="utf-8") as f:\n    f.write(TAGHELPER_CODE); def ask(self, prompt: str, max_retries=3) -&gt; str:; response = self.client.chat.completions.create(... messages=[{"role": "user", "content": prompt}])</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>blue_pipeline.py, gpt_interface.py</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>import os
-import json
-import re
-from gpt_interface import GPT4Bot # MLLM backbone (e.g., GPT-4.1); response = self.client.chat.completions.create(
-                    model=self.model,
-                    messages=[{"role": "user", "content": prompt}],
-                    max_tokens=4096,
-                    temperature=0,; Each agent builds upon the structured output of the previous one,
-forming a complete end-to-end pipeline for automated 3D game generation.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>blue_pipeline.py, gpt_interface.py</t>
-        </is>
-      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>There is executable code for prompting (a GPT wrapper and a multi-agent pipeline that composes/uses prompts to generate project files), so prompting-related preprocessing exists.</t>
+          <t>No executable tokenization, filtering/deduplication, or prompt-input construction code is present in the provided files; they mainly write C# templates and call the model with a raw prompt.</t>
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>4040</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="5" ht="97.5" customHeight="1">
@@ -1821,7 +4794,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>filtering</t>
+          <t>filtering, prompting</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1831,7 +4804,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>drug = drug[variable_drug].fillna(drug.mean()); with open("../data/top1000_variable_genes.txt", 'r') as file:\n        var_features = file.read().splitlines(); self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp))</t>
+          <t>drug = drug[variable_drug].fillna(drug.mean()); self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp)); dataset_processed[cell] = {"data_ess": torch.tensor(Essentiality.loc[cell]), "data_exp": torch.tensor(Expression.loc[cell])}</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -1841,69 +4814,993 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Files implement non-trivial preprocessing: selecting variable features, dropping/ filling missing columns, assembling per-cell tensors, and normalizing expression data, so a filtering/cleaning pipeline exists.</t>
+          <t>Utilities and a dataset class implement real preprocessing/cleaning and input construction (feature selection, NaN imputation, StandardScaler normalization, and dataset splitting), so preprocessing code exists.</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>8297</v>
-      </c>
-    </row>
-    <row r="6" ht="292.5" customHeight="1">
+        <v>8815</v>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Accelerated Aggregated D-Optimal Designs for Estimating Main Effects in Black-Box Models</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/cchihyu/A2D2E</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>def _bin_boundaries(data_d, K): """Equal-frequency (quantile) bin boundaries."""; def pd_curve(f_hat, X_train, d, n_grid=100):; PARAMS = { 'model': 'knn', 'best_params': { ... } }</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>model_params/f0_knn.py, model_params/f1_knn.py, model_params/f2_knn.py, model_params/f3_knn.py, model_params/f4_knn.py, model_params/f5_knn.py, model_params/f6_knn.py, src/algorithms.py</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Files implement analysis and modelling utilities (curve estimation and model params) rather than any executable preprocessing, filtering/deduplication, or prompt-building pipelines.</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>3761</v>
+      </c>
+    </row>
+    <row r="7" ht="195" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>EXISTS</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Accelerated Aggregated D-Optimal Designs for Estimating Main Effects in Black-Box Models</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/cchihyu/A2D2E</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>AccidentBench: Benchmarking Multimodal Understanding and Reasoning in Vehicle Accidents and Beyond</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>tokenization, filtering, prompting</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>tools/make_audio_hf_dataset.ipynb, tools/make_image_hf_dataset.ipynb, tools/make_video_hf_dataset.ipynb, tools/make_video_hf_dataset_from_json.py, lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py, lmms_eval/api/filter.py, tools/live_bench/filter.ipynb, tools/live_bench/create_dataset.py</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>prompt_list.append("&lt;|audio_bos|&gt;&lt;|AUDIO|&gt;&lt;|audio_eos|&gt;" + json_data['prompt']); DEFAULT_SETTINGS = { ... 'lexeme_splitter': nltk.tokenize.word_tokenize, 'do_stem': False, 'do_lemma': False, 'do_punct_removal': False, 'do_lower': False, ... }; filtered_data = data["test"].filter(lambda example: example["score"] and example["score"] &gt; 5)</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>tools/make_audio_hf_dataset.ipynb, tools/make_image_hf_dataset.ipynb, tools/make_video_hf_dataset.ipynb, tools/make_video_hf_dataset_from_json.py, lmms_eval/api/filter.py, tools/data_process/data_process_revise_dataset_name.py, tools/live_bench/create_dataset.py, tools/live_bench/filter.ipynb, lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py, lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, setup.py, test_parse.py, data_results/read_results.py, lmms_eval/__main__.py, lmms_eval/evaluator.py, lmms_eval/evaluator_utils.py, lmms_eval/logging_utils.py</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>There is non-trivial, executable preprocessing code for tokenization, data filtering/cleaning, and prompt/input construction spread across notebooks and Python modules in the repo.</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>21924</v>
+      </c>
+    </row>
+    <row r="8" ht="39" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>A Comprehensive Survey on Trustworthiness in Reasoning with Large Language Models</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/ybwang119/Awesome-reasoning-safety</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>A Computational Approach to Visual Metonymy</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/cincynlp/ViMET</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="253.5" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>AdamMeme: Adaptively Probe the Reasoning Capacity of Multimodal Large Language Models on Harmfulness</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>prompting</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>GPT_agent.R</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>.build_prompt &lt;- function(dat, x_target) {; sprintf(paste0(
-    "You are given training data in the form of ((x1,...,xd),y):\n%s\n\n",
-    "Question: What is your prediction of y at x = (%s)?\n",
-    "Return only a single numerical scalar with no explanation."; resp &lt;- openai::create_chat_completion(
-      model = object$model, temperature = object$temperature,
-      messages = list(
-        list(role = "system", content = object$system_prompt),
-        list(role = "user",   content = user_prompt)
-      )
-    )</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>A2D2E_main_function.R, alg.py, compute_truth.R, env.py, GPT_agent.R, md.py, real_data.R</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>GPT_agent.R implements a full prompt-construction pipeline (.build_prompt) and uses create_chat_completion to query a model, which clearly matches the prompting wrappers / input construction category.</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>16706</v>
-      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>scripts/gen_misb.py, scripts/mining.py, scripts/refinement.py, scripts/prompts.py, scripts/scoring.py, scripts/utils.py, scripts/run_llava.py</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>prompt = prompts.prompt_cls1
+prompt = prompt.replace(r"{taxonomy}", json.dumps(taxonomy["meme_harmfulness"],indent=1)).\
+                        replace(r"{text_content}",data['text']); optimized_res = gpt4o_generate_imglist(optimized_prompt, target_meme_image_paths,temp=1); content = [{"type": "text", "text": text}]
+for image_path in image_paths:
+    with open(image_path, "rb") as image_file:
+        base64_image = base64.b64encode(image_file.read()).decode('utf-8')
+    content.append({"type": "image_url", "image_url": {"url": f"data:image/png;base64,{base64_image}"}})</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>scripts/gen_misb.py, scripts/mining.py, scripts/prompts.py, scripts/refinement.py, scripts/run_llava.py, scripts/scoring.py, scripts/utils.py</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>There is clear, non-trivial code that constructs prompts, prepares multimodal inputs (images + text), and orchestrates LLM-based preprocessing pipelines, so prompting/input-construction preprocessing exists.</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>11348</v>
+      </c>
+    </row>
+    <row r="11" ht="78" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Adaptive Graph Learning with Transformer for Multi-Reservoir Inflow Prediction</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>filtering</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>_preprocess.py, _get_weather_prediction.py, _build_graph.ipynb, _aligning_time.ipynb</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>def create_sliding_windows(data, _days_x=30, _days_y=7, _input_features=3):; scaler_X.fit(all_train_X)
+scaler_y.fit(all_train_y); def process_weather_data(years, reservoir_coords, data_path_template):</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>_preprocess.py, _aligning_time.ipynb, _build_graph.ipynb, _edge_change.py, _edge_track_w_detail.py, _feature_importance.py, _get_weather_prediction.py, _pretrain.py, baselines.py</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>There is executable preprocessing and data-cleaning pipeline code (windowing, scaling, aggregation and alignment) so preprocessing exists.</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>19466</v>
+      </c>
+    </row>
+    <row r="12" ht="97.5" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Addressing Logical Fallacies In Scientific Reasoning From Large Language Models: Towards a Dual-Inference Training Framework</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/hannahdavidsoncollege-maker/ScientificReasoningForEnvironment-MedicineWithLLMs</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Hannah+Walker_Paper.ipynb</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>"It then tries all 8 combinations of P, Q and its negations and tests how times the LLM says the answer is correct."; API_URL = "https://generativelanguage.googleapis.com/v1beta/models/gemini-2.5-flash-lite:generateContent"; def check_implication(sentence,PQ,posP,posQ):</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Hannah+Walker_Paper.ipynb</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>The notebook implements prompt construction and LLM querying logic (combinatorial P/Q variants and an API call), matching the 'prompting wrappers / input construction pipeline' category.</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13" ht="58.5" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>A Dual Large Language Models Architecture with Herald Guided Prompts for Parallel Fine Grained Traffic Signal Control</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/BUPT-ANTlab/HeraldLight</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>utils/pipeline.py, run_dynamiclight.py, run_gpt.py, run_herald_summarize.py, run_llama.py, run_test.py, a_test_online_model/gpt-4o-mini.py, a_test_online_model/Llama_inference.py</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Unexpected error: litellm.APIConnectionError: AzureException APIConnectionError - Connection error.</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="78" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Advancing ADMET prediction through multiscale fragment-aware pretraining with MSformer-ADMET</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/ZJUFanLab/MSformer</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>notebooks/download_tdc_datasets.ipynb, run_classification_molnet.sh, run_classification_tdc.sh, setup.py, msformer/ftarges.py, msformer/masskg.py, msformer/MSEncoder.py, msformer/MSFinetune.py, msformer/utils.py</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Unexpected error: litellm.APIConnectionError: AzureException APIConnectionError - Connection error.</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58.5" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Advancing site-specific disease and pest management in precision agriculture: From reasoning-driven foundation models to adaptive, feedback-based learning</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/nitin-dominic/AgriPathogenDatabase</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="253.5" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Adversarial Attention Perturbations for Large Object Detection Transformers</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>utils/frcnn_utils/dataset.py, utils/frcnn_utils/voc_dataset.py, utils/dataset_utils/voc/preprocessing.py, extras/detr_extras/d2/detr/dataset_mapper.py, models/detrex/detrex/data/detr_dataset_mapper.py, models/detrex/detectron2/detectron2/data/dataset_mapper.py, models/detrex/detectron2/detectron2/layers/wrappers.py, models/detrex/detectron2/detectron2/modeling/mmdet_wrapper.py, models/detrex/detectron2/tests/data/test_dataset.py, models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py, models/detrex/detrex/data/dataset_mappers/coco_panoptic_new_baseline_dataset_mapper.py, models/detrex/detrex/data/dataset_mappers/mask_former_instance_dataset_mapper.py, scripts/attack_deformable_detr.py, scripts/attack_detr.py</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Unexpected error: litellm.APIConnectionError: AzureException APIConnectionError - Connection error.</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58.5" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>A First-Order Logic-Based Alternative to Reward Models in RLHF</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>train/dpo_train.py, train/eval_safeRLHF.py, train/generate_fol.py, train/sft_training.py, train/train.py, utils/LogicalEquivalence.py, utils/sgrpo_trainer.py</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Unexpected error: litellm.APIConnectionError: AzureException APIConnectionError - Connection error.</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="78" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>A foundation model for learning genetic associations from brain imaging phenotypes</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>wrapper.py, src/dataset_template.py, auc_plot.ipynb, comical_cli.sh, demo.ipynb, pretrained_weights/load_pretrained_encoders.py, src/batch_sampler.py, src/models.py, src/test.py, src/train.py</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Unexpected error: litellm.APIConnectionError: AzureException APIConnectionError - Connection error.</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58.5" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Agentmandering: A Game-Theoretic Framework for Fair Redistricting via Large Language Model Agents</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Lihaogx/AgentMandering</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>install_r_packages.R, main.py, model/agent.py, model/legacy_YCIF_protocol.py, model/llm_client.py, model/unified_YCIF_protocol.py, model/YCIF_protocol.py</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Unexpected error: litellm.APIConnectionError: AzureException APIConnectionError - Connection error.</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="78" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>AgentSHAP: Interpreting LLM Agent Tool Importance with Monte Carlo Shapley Value Estimation</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/GenAISHAP/TokenSHAP</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>notebooks/AgentSHAP Examples.ipynb, notebooks/TokenShap Examples.ipynb, notebooks/VideoSHAP Examples.ipynb, papers/Untitled.ipynb, token_shap/__init__.py, token_shap/agent_shap.py, token_shap/base.py</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Unexpected error: litellm.APIConnectionError: AzureException APIConnectionError - Connection error.</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="136.5" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>A Granular Study of Safety Pretraining under Model Abliteration</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>src/chat.py, src/evaluate.py</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>conversation.append({"role": "user", "content": prompt}); toks = tokenizer.apply_chat_template(conversation=conversation, add_generation_prompt=True, return_tensors="pt"); evaluation_prompts = [f"{system_prompt}\n" f"### Prompt:\n{question}\n\n" f"### Response:\n{response}\n\n" "CLASSIFICATION: " for question, response in zip(batch_questions, batch_responses)]</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>slurm.sh, slurm_short.sh, src/abliterate.py, src/chat.py, src/compare.py, src/evaluate.py</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>The repository includes executable code that constructs prompting wrappers and prepares inputs (prompt templates and batch encoding) for model calls, so prompting preprocessing exists.</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>8702</v>
+      </c>
+    </row>
+    <row r="22" ht="234" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>prompting, filtering</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py, llm/llm1.py, llm/llm3.py</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>def censorship(user_prompt):
+    prompt_sys=f""" 
+    {user_prompt} is the user prompt for the LLM,your task is to check whether it has moral or other safety problems; prompt_sys=f"""You are a helpful assistant that analyze data modalities
+in multimodal Auto-Machine learning task.
+Your task is to analyze the data type of each column; prompt_sys=f"""You are a helpful assistant that writes data processors
+        code to load different types of data for multimodal
+        Auto-Machine learning task.</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py, llm/gradio.py, llm/llm1.py, llm/llm2.py, llm/llm3.py, llm/llm4.py, llm/llm5.py, llm/llm6.py</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>The code implements prompt construction/wrappers and a content-filtering function (censorship/filter) rather than only training or evaluation scripts, so prompting and filtering pipelines exist.</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>8325</v>
+      </c>
+    </row>
+    <row r="23" ht="78" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>AIP-TranLAC: A Transformer-Based Method Integrating LSTM and Attention Mechanism for Predicting Anti-inflammatory Peptides</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Renjingyi123/AIP-TranLAC</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>tokenization</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>train.py</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>aa_dict = {'A': 1, 'R': 2, 'N': 3, ... 'X': 23}; pep = pep + 'X' * (30-len_seq); for aa in pep:\n                current_pep.append(aa_dict[aa])\n            pep_codes.append(torch.tensor(current_pep))</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>train.py</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>The repository includes executable preprocessing code that tokenizes peptide sequences and performs padding/dataset construction, which qualifies as a tokenization pipeline.</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>3421</v>
+      </c>
+    </row>
+    <row r="24" ht="39" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Aligned or Apart? Multi-Agent Insights into Consumer and Brand Messaging Discrepancies</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/htgan-ai/OPIM</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25" ht="39" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Aligning Deep Implicit Preferences by Learning to Reason Defensively</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Zephyrian-Hugh/Deep-pref</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="136.5" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py, llm/llm1.py, llm/llm3.py, llm/llm4.py, llm/llm5.py, llm/llm6.py</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>prompt_sys=f""" \n    {user_prompt} is the user prompt for the LLM,your task is to check whether it has moral or other safety problems; response,history=get_completion(prompt_sys,prompt,history); prompt_sys=f"""You are a helpful assistant that writes data processors\n        code to load different types of data for multimodal\n        Auto-Machine learning task.</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py, llm/gradio.py, llm/llm1.py, llm/llm2.py, llm/llm3.py, llm/llm4.py, llm/llm5.py, llm/llm6.py</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>The repository contains real code that builds prompts and wraps LLM calls (prompting pipeline), so prompting preprocessing EXISTS.</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>8224</v>
+      </c>
+    </row>
+    <row r="27" ht="117" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>A Solver‐Aided Hierarchical Language for LLM‐Driven Systems</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>filtering, prompting</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>AIDL/constraint_fitting/filter_programs.py, scripts/2024.02.14.collect_designs.py, scripts/parse_structures.py, scripts/specific_constraints.py</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>if program_errors[prog] &lt; threshold: shutil.copyfile(os.path.join("dataset_quantized", prog), os.path.join("dataset_filtered", prog)); response = client.chat.completions.create(model="gpt-4-turbo-preview", messages=message_list, temperature=1, max_tokens=2048, ...); natural_param_response = query(system_prompt, [natural_param_prompt])</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>AIDL/constraint_fitting/filter_programs.py, data/gen_data.ipynb, data/plot_data.ipynb, scripts/2024.02.14.collect_designs.py, scripts/parse_structures.py, scripts/specific_constraints.py, scripts/test.py, setup.py, AIDL/__init__.py, AIDL/aidl.py, AIDL/common.py, AIDL/compositional_constraints.py, AIDL/constraints.py, AIDL/debug.py, AIDL/dispatch.py</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>There is real, executable code for filtering datasets and for constructing / sending prompts (prompting wrappers), so preprocessing pipelines exist.</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>18114</v>
+      </c>
+    </row>
+    <row r="28" ht="195" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>A Structured Framework for Evaluating and Enhancing LLM Robustness</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>filtering</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>src/preprocess.py, src/pipeline.py, experiments/run_full_pipeline.sh, scripts/analyze-exhibition-data.py, scripts/add-remaining-artworks.js, scripts/add-multi-image-support.js, scripts/apply-multi-image-updates.js, scripts/apply-batch-multi-image-updates.js, exhibitions/negative-space-of-the-tide/js/data-loader.js</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>def process_image(; from preprocess import process_image; def extract_artwork_info(text):</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>experiments/run_full_pipeline.sh, src/pipeline.py, src/preprocess.py, exhibitions/negative-space-of-the-tide/js/data-loader.js, scripts/add-artwork2-refs.js, scripts/add-artwork3-references.js, scripts/add-artwork4-references.js, scripts/add-multi-image-support.js, scripts/add-remaining-artworks.js, scripts/add-thread6-references.js, scripts/analyze-exhibition-data.py, scripts/analyze-image-paths.js, scripts/analyze-ppt-artworks.js, scripts/apply-batch-multi-image-updates.js, scripts/apply-metadata-enhancements.js, scripts/apply-multi-image-updates.js</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>EXISTS — multiple scripts implement real preprocessing and cleaning pipelines (image processing, metadata generation and data JSON transformations) that qualify as filtering/cleaning pipelines.</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>22490</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>A Survey of Reasoning and Agentic Systems in Time Series</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/blacksnail789521/Time-Series-Agent</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="39" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>A Survey on Latent Reasoning</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/multimodal-art-projection/Latent-Reasoning</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1916,7 +5813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2019,9 +5916,9 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>utils/demo_dataloader.py</t>
@@ -2034,139 +5931,870 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
+      <c r="A6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Abstract A024: DeepVul: A multi-task transformer model for joint prediction of gene essentiality and drug response</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/alaaj27/DeepVul.git</t>
+        </is>
+      </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>scripts/infer.sh</t>
+          <t>src/utils.py</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/scripts/infer.sh</t>
+          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/utils.py</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>90% Faster, 100% Code-Free: MLLM-Driven Zero-Code 3D Game Development</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/yxwan123/UniGen</t>
-        </is>
-      </c>
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>blue_pipeline.py</t>
+          <t>src/JointDataset.py</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/yxwan123/UniGen/blob/HEAD/blue_pipeline.py</t>
+          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/JointDataset.py</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
+      <c r="A8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>AccidentBench: Benchmarking Multimodal Understanding and Reasoning in Vehicle Accidents and Beyond</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench</t>
+        </is>
+      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>gpt_interface.py</t>
+          <t>tools/make_audio_hf_dataset.ipynb</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/yxwan123/UniGen/blob/HEAD/gpt_interface.py</t>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/make_audio_hf_dataset.ipynb</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Abstract A024: DeepVul: A multi-task transformer model for joint prediction of gene essentiality and drug response</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/alaaj27/DeepVul.git</t>
-        </is>
-      </c>
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>src/utils.py</t>
+          <t>tools/make_image_hf_dataset.ipynb</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/utils.py</t>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/make_image_hf_dataset.ipynb</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>src/JointDataset.py</t>
+          <t>tools/make_video_hf_dataset.ipynb</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/JointDataset.py</t>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/make_video_hf_dataset.ipynb</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Accelerated Aggregated D-Optimal Designs for Estimating Main Effects in Black-Box Models</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/cchihyu/A2D2E</t>
-        </is>
-      </c>
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>GPT_agent.R</t>
+          <t>tools/make_video_hf_dataset_from_json.py</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/cchihyu/A2D2E/blob/HEAD/GPT_agent.R</t>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/make_video_hf_dataset_from_json.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>lmms_eval/api/filter.py</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/api/filter.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>tools/live_bench/filter.ipynb</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/live_bench/filter.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>tools/live_bench/create_dataset.py</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/live_bench/create_dataset.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>AdamMeme: Adaptively Probe the Reasoning Capacity of Multimodal Large Language Models on Harmfulness</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>scripts/gen_misb.py</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/gen_misb.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>scripts/mining.py</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/mining.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>scripts/refinement.py</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/refinement.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>scripts/prompts.py</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/prompts.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>scripts/scoring.py</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/scoring.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>scripts/utils.py</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/utils.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>scripts/run_llava.py</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/run_llava.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Adaptive Graph Learning with Transformer for Multi-Reservoir Inflow Prediction</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>_preprocess.py</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_preprocess.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>_get_weather_prediction.py</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_get_weather_prediction.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>_build_graph.ipynb</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_build_graph.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>_aligning_time.ipynb</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_aligning_time.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Addressing Logical Fallacies In Scientific Reasoning From Large Language Models: Towards a Dual-Inference Training Framework</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/hannahdavidsoncollege-maker/ScientificReasoningForEnvironment-MedicineWithLLMs</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Hannah+Walker_Paper.ipynb</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/hannahdavidsoncollege-maker/ScientificReasoningForEnvironment-MedicineWithLLMs/blob/HEAD/Hannah+Walker_Paper.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>A Granular Study of Safety Pretraining under Model Abliteration</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>src/chat.py</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/chat.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>src/evaluate.py</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/evaluate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/filter.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm1.py</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm1.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="8" t="n"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm3.py</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm3.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>AIP-TranLAC: A Transformer-Based Method Integrating LSTM and Attention Mechanism for Predicting Anti-inflammatory Peptides</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/Renjingyi123/AIP-TranLAC</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>train.py</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Renjingyi123/AIP-TranLAC/blob/HEAD/train.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/filter.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="9" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm1.py</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm1.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm3.py</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm3.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="9" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm4.py</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm4.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="9" t="n"/>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm5.py</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm5.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm6.py</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm6.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>A Solver‐Aided Hierarchical Language for LLM‐Driven Systems</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>AIDL/constraint_fitting/filter_programs.py</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/AIDL/constraint_fitting/filter_programs.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="9" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>scripts/2024.02.14.collect_designs.py</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/2024.02.14.collect_designs.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="9" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>scripts/parse_structures.py</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/parse_structures.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>scripts/specific_constraints.py</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/specific_constraints.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>A Structured Framework for Evaluating and Enhancing LLM Robustness</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>src/preprocess.py</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/src/preprocess.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="9" t="n"/>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>src/pipeline.py</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/src/pipeline.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="9" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>experiments/run_full_pipeline.sh</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/experiments/run_full_pipeline.sh</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="9" t="n"/>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>scripts/analyze-exhibition-data.py</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/scripts/analyze-exhibition-data.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="9" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>scripts/add-remaining-artworks.js</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/scripts/add-remaining-artworks.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="9" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>scripts/add-multi-image-support.js</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/scripts/add-multi-image-support.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="9" t="n"/>
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>scripts/apply-multi-image-updates.js</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/scripts/apply-multi-image-updates.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="9" t="n"/>
+      <c r="B52" s="9" t="n"/>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>scripts/apply-batch-multi-image-updates.js</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/scripts/apply-batch-multi-image-updates.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="8" t="n"/>
+      <c r="B53" s="8" t="n"/>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>exhibitions/negative-space-of-the-tide/js/data-loader.js</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/exhibitions/negative-space-of-the-tide/js/data-loader.js</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
+  <mergeCells count="33">
+    <mergeCell ref="B35:B40"/>
+    <mergeCell ref="B8:B16"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C17:C23"/>
     <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C35:C40"/>
+    <mergeCell ref="A8:A16"/>
+    <mergeCell ref="C8:C16"/>
+    <mergeCell ref="A41:A44"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B45:B53"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="A45:A53"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C45:C53"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="C24:C27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
@@ -2179,6 +6807,48 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2210,133 +6880,133 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Total Repos Checked</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n">
-        <v>5</v>
+      <c r="B2" s="11" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>EXISTS</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
-        <v>5</v>
+      <c r="B3" s="11" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>NOT_APPLICABLE</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Skipped (non-GitHub)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Skipped (non-GitHub)</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
-        <v>0</v>
+      <c r="B6" s="11" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Coverage (%)</t>
         </is>
       </c>
-      <c r="B7" s="10">
-        <f>5/5*100</f>
+      <c r="B7" s="11">
+        <f>13/29*100</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr"/>
-      <c r="B8" s="10" t="inlineStr"/>
+      <c r="A8" s="10" t="inlineStr"/>
+      <c r="B8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>LLM Token Usage</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr"/>
+      <c r="B9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Model / Deployment</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>gpt-5-mini-2025-08-07</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Requests</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>5</v>
+      <c r="B11" s="11" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Input Tokens</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>46,551</t>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>151,821</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Output Tokens</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>4,441</t>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>13,246</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Tokens</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>50,992</t>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>165,067</t>
         </is>
       </c>
     </row>
@@ -2351,7 +7021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2444,12 +7114,12 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>data/mydataset.py, predict.py</t>
+          <t>data/mydataset.py</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>self.tokenizer = AutoTokenizer.from_pretrained(SPLICEBERT_PATH); input_ids = self.tokenizer.encode(seq, add_special_tokens=True); seq = ' '.join(list(seq.upper().replace("U", "T")))</t>
+          <t>self.tokenizer = AutoTokenizer.from_pretrained(SPLICEBERT_PATH); input_ids = self.tokenizer.encode(seq, add_special_tokens=True); k_RNA = [[i[j:j + 4] for j in range(len(i) - 4 + 1)] for i in fasta_seqs]</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -2459,20 +7129,20 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>There is executable tokenization and input-construction code that builds model-ready inputs from RNA sequences.</t>
+          <t>There's a non-trivial preprocessing pipeline (tokenization and feature extraction) in the repo.</t>
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>7305</v>
+        <v>7302</v>
       </c>
     </row>
     <row r="3" ht="78" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>EXISTS</t>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2485,19 +7155,11 @@
           <t>https://github.com/hustvl/4DLangVGGT</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>prompting</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>preprocess/generate_vggttoken.py, utils/demo_dataloader.py</t>
-        </is>
-      </c>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>from streamvggt.models.streamvggt import StreamVGGT; streamvggt.inference_long_video(; save_dir = os.path.join(args.img_root, cat, 'streamvggt_token')</t>
+          <t>Repository contains model code, data loading utilities, and training/inference scripts, but no explicit, non-trivial preprocessing pipelines for tokenization, filtering/cleaning, or prompting wrappers in the shown files.</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -2507,11 +7169,11 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>The repository includes non-trivial preprocessing/input-construction code (token generation and data loading) rather than purely training or inference scripts.</t>
+          <t>No executable preprocessing pipelines matching the categories (tokenization, filtering/cleaning, prompting wrappers) are present among the shown files.</t>
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>16848</v>
+        <v>15250</v>
       </c>
     </row>
     <row r="4" ht="58.5" customHeight="1">
@@ -2545,7 +7207,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>from gpt_interface import GPT4Bot # MLLM backbone (e.g., GPT-4.1); TAGHELPER_CODE = '''using UnityEditor;; def CreateUIManagerGO()</t>
+          <t>from gpt_interface import GPT4Bot # MLLM backbone (e.g., GPT-4.1); class GPT4Bot:; def ask(self, prompt: str, max_retries=3) -&gt; str:</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -2555,14 +7217,14 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>The shown code implements a prompting/input-construction pipeline that leverages an LLM to generate and assemble Unity project components.</t>
+          <t>The blue_pipeline.py file demonstrates an executable prompting/input-construction workflow using a GPT-4 based bot to drive multi-agent generation for Unity projects.</t>
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>4190</v>
-      </c>
-    </row>
-    <row r="5" ht="78" customHeight="1">
+        <v>4656</v>
+      </c>
+    </row>
+    <row r="5" ht="97.5" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -2593,7 +7255,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Essentiality = Essentiality[var_features].dropna(axis='columns'); with open("../data/top500_variable_drug.txt", 'r') as file:; self.data_exp = self.normalize_tensor_columns(self.data_exp)</t>
+          <t>self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp)); with open("../data/top1000_variable_genes.txt", 'r') as file: var_features = file.read().splitlines(); Essentiality = Essentiality[var_features].dropna(axis='columns')</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -2603,60 +7265,1076 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>There are executable preprocessing components (data filtering/cleaning and normalization) implemented in Python modules, not just training/inference scripts.</t>
+          <t>There is executable preprocessing code (data loading, feature selection, normalization) beyond simple file reads.</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>8966</v>
-      </c>
-    </row>
-    <row r="6" ht="58.5" customHeight="1">
+        <v>9215</v>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Accelerated Aggregated D-Optimal Designs for Estimating Main Effects in Black-Box Models</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/cchihyu/A2D2E</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>def pd_curve(f_hat, X_train, d, n_grid=100):; def _bin_boundaries(data_d, K):; def a2d2e_curve(f_hat, X_train, d, n_grid=100, K=40, delta=0.01):</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>model_params/f0_knn.py, model_params/f1_knn.py, model_params/f2_knn.py, model_params/f3_knn.py, model_params/f4_knn.py, model_params/f5_knn.py, model_params/f6_knn.py, src/algorithms.py</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>No executable preprocessing pipeline code for tokenization, filtering/cleaning, or prompting is present in the shown repository files.</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>4702</v>
+      </c>
+    </row>
+    <row r="7" ht="195" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>EXISTS</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Accelerated Aggregated D-Optimal Designs for Estimating Main Effects in Black-Box Models</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/cchihyu/A2D2E</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>AccidentBench: Benchmarking Multimodal Understanding and Reasoning in Vehicle Accidents and Beyond</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>tokenization, prompting</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py, tools/make_audio_hf_dataset.ipynb</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>class LexicalAnalyzer(PickleWriteable):; class MplugOwlTokenizer(LlamaTokenizer):; prompt_list.append("&lt;|audio_bos|&gt;&lt;|AUDIO|&gt;&lt;|audio_eos|&gt;" + json_data['prompt'])</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>tools/make_audio_hf_dataset.ipynb, tools/make_image_hf_dataset.ipynb, tools/make_video_hf_dataset.ipynb, tools/make_video_hf_dataset_from_json.py, lmms_eval/api/filter.py, tools/data_process/data_process_revise_dataset_name.py, tools/live_bench/create_dataset.py, tools/live_bench/filter.ipynb, lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py, lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, setup.py, test_parse.py, data_results/read_results.py, lmms_eval/__main__.py, lmms_eval/evaluator.py, lmms_eval/evaluator_utils.py, lmms_eval/logging_utils.py</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>There are concrete preprocessing implementations for tokenization and input/prompt construction in the repo.</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>23550</v>
+      </c>
+    </row>
+    <row r="8" ht="39" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>A Comprehensive Survey on Trustworthiness in Reasoning with Large Language Models</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/ybwang119/Awesome-reasoning-safety</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>A Computational Approach to Visual Metonymy</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/cincynlp/ViMET</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="97.5" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>AdamMeme: Adaptively Probe the Reasoning Capacity of Multimodal Large Language Models on Harmfulness</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>prompting, filtering</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>scripts/gen_misb.py, scripts/mining.py, scripts/refinement.py, scripts/prompts.py, scripts/run_llava.py, scripts/scoring.py, scripts/utils.py</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>new_prompt = "Given a meme, with which meme_text will be embedded in the image, you are tasked with analyzing the meme to assess potential risks associated to a certain aspect."; prompt = prompts.prompt_cls1; def iter_search(pool, meme_data):</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>scripts/gen_misb.py, scripts/mining.py, scripts/prompts.py, scripts/refinement.py, scripts/run_llava.py, scripts/scoring.py, scripts/utils.py</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>The repository provides non-trivial preprocessing and input-construction pipelines (prompt wrappers and data filtering) rather than mere data loading or model inference code.</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>23005</v>
+      </c>
+    </row>
+    <row r="11" ht="117" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Adaptive Graph Learning with Transformer for Multi-Reservoir Inflow Prediction</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>_preprocess.py</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>def create_sliding_windows(data, _days_x=30, _days_y=7, _input_features=3):; def load_and_split_data(data_path, reservoir_name, _input_features=3, _days_x=30, _days_y=7):; def preprocess_reservoir_data(data_path="./graph/data", output_path="./graph/data/parsed", _input_features=3, _days_x=30, _days_y=7, scaler_type="global"):</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>_preprocess.py, _aligning_time.ipynb, _build_graph.ipynb, _edge_change.py, _edge_track_w_detail.py, _feature_importance.py, _get_weather_prediction.py, _pretrain.py, baselines.py</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Non-tokenization, non-prompting, and non-deduplication preprocessing code is present; hence not applicable to the listed categories.</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>21170</v>
+      </c>
+    </row>
+    <row r="12" ht="97.5" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Addressing Logical Fallacies In Scientific Reasoning From Large Language Models: Towards a Dual-Inference Training Framework</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/hannahdavidsoncollege-maker/ScientificReasoningForEnvironment-MedicineWithLLMs</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>prompting</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>GPT_agent.R</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>You are given training data in the form of ((x1,...,xd),y):; Return only a single numerical scalar with no explanation.; openai::create_chat_completion</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>A2D2E_main_function.R, alg.py, compute_truth.R, env.py, GPT_agent.R, md.py, real_data.R</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>GPT_agent.R implements a prompting wrapper, creating input prompts and handling API responses, i.e., an input-construction pipeline.</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>17471</v>
-      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Hannah+Walker_Paper.ipynb</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t># This code requires sentences.txt to contain a set of scientific implications of the form P implies Q.; API_URL = "https://generativelanguage.googleapis.com/v1beta/models/gemini-2.5-flash-lite:generateContent"; def check_implication(sentence,PQ,posP,posQ):</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Hannah+Walker_Paper.ipynb</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>The repository includes executable code that constructs prompts and interacts with an LLM, i.e., a prompting wrapper/input construction pipeline.</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>5353</v>
+      </c>
+    </row>
+    <row r="13" ht="214.5" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>A Dual Large Language Models Architecture with Herald Guided Prompts for Parallel Fine Grained Traffic Signal Control</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/BUPT-ANTlab/HeraldLight</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>filtering</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>utils/pipeline.py</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>def path_check(dic_path):; cs = ConstructSample(path_to_samples=train_round, cnt_round=cnt_round,
+                                 dic_traffic_env_conf=self.dic_traffic_env_conf)
+        cs.prepare_samples_for_system(); generator = Generator(cnt_round=cnt_round,
+                          cnt_gen=cnt_gen,
+                          dic_path=dic_path,
+                          dic_agent_conf=dic_agent_conf,
+                          dic_traffic_env_conf=dic_traffic_env_conf)</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>utils/pipeline.py, run_dynamiclight.py, run_gpt.py, run_herald_summarize.py, run_llama.py, run_test.py, a_test_online_model/gpt-4o-mini.py, a_test_online_model/Llama_inference.py</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Existence of an actionable preprocessing/pipeline module (utils/pipeline.py) with sample construction and data-generation orchestration indicates real preprocessing code is present.</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>20029</v>
+      </c>
+    </row>
+    <row r="14" ht="78" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Advancing ADMET prediction through multiscale fragment-aware pretraining with MSformer-ADMET</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/ZJUFanLab/MSformer</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>tokenization</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>msformer/MSEncoder.py, tokenizer/tokenizer.py</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>MolTranBertTokenizer(vocab_file); tokenizer.batch_encode_plus; embeddings = np.zeros((len(fragments), self.max_fragments, self.embed_dim))</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>notebooks/download_tdc_datasets.ipynb, run_classification_molnet.sh, run_classification_tdc.sh, setup.py, msformer/ftarges.py, msformer/masskg.py, msformer/MSEncoder.py, msformer/MSFinetune.py, msformer/utils.py</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Code shows an actual tokenization+encoding workflow for molecular fragments, indicating a functional tokenization pipeline in the repo.</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>16823</v>
+      </c>
+    </row>
+    <row r="15" ht="58.5" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Advancing site-specific disease and pest management in precision agriculture: From reasoning-driven foundation models to adaptive, feedback-based learning</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/nitin-dominic/AgriPathogenDatabase</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="253.5" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Adversarial Attention Perturbations for Large Object Detection Transformers</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>utils/frcnn_utils/dataset.py, utils/frcnn_utils/voc_dataset.py, utils/dataset_utils/voc/preprocessing.py, extras/detr_extras/d2/detr/dataset_mapper.py, models/detrex/detectron2/detectron2/data/dataset_mapper.py, models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py, models/detrex/detrex/data/dataset_mappers/coco_panoptic_new_baseline_dataset_mapper.py</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>def preprocess(img, min_size=600, max_size=600, resize=True):; return normalize(img); def letterbox_image_padded(image, size=(416, 416)):</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>utils/frcnn_utils/dataset.py, utils/frcnn_utils/voc_dataset.py, utils/dataset_utils/voc/preprocessing.py, extras/detr_extras/d2/detr/dataset_mapper.py, models/detrex/detrex/data/detr_dataset_mapper.py, models/detrex/detectron2/detectron2/data/dataset_mapper.py, models/detrex/detectron2/detectron2/layers/wrappers.py, models/detrex/detectron2/detectron2/modeling/mmdet_wrapper.py, models/detrex/detectron2/tests/data/test_dataset.py, models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py, models/detrex/detrex/data/dataset_mappers/coco_panoptic_new_baseline_dataset_mapper.py, models/detrex/detrex/data/dataset_mappers/mask_former_instance_dataset_mapper.py, scripts/attack_deformable_detr.py, scripts/attack_detr.py</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>There exists substantial preprocessing code, but it does not fit the requested tokenization, filtering/cleaning, or prompting wrapper categories.</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>21171</v>
+      </c>
+    </row>
+    <row r="17" ht="78" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>A First-Order Logic-Based Alternative to Reward Models in RLHF</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>train/dpo_train.py, train/generate_fol.py, train/sft_training.py, train/train.py</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>def to_hha_chat_template(samples):; train_dataset = train_dataset.filter(lambda sample: sample['better_response_id'] == sample['safer_response_id']; prompts = list(batch_prompts['prompt'])</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>train/dpo_train.py, train/eval_safeRLHF.py, train/generate_fol.py, train/sft_training.py, train/train.py, utils/LogicalEquivalence.py, utils/sgrpo_trainer.py</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>There is non-trivial prompt construction / data-preparation pipeline code present in the repo.</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>13346</v>
+      </c>
+    </row>
+    <row r="18" ht="97.5" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>A foundation model for learning genetic associations from brain imaging phenotypes</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>tokenization, filtering</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>src/dataset_template.py</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>return idp_tokenization('cpu',count,self.rnd_st,data.index,{'train':data.values.astype('float')}); idps_raw = idps_raw.loc[:, ~idps_raw.columns.str.replace("(\.\d+)$", "").duplicated()]; self.idps_filt = idps_filt.dropna(how= 'any', axis=0)</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>wrapper.py, src/dataset_template.py, auc_plot.ipynb, comical_cli.sh, demo.ipynb, pretrained_weights/load_pretrained_encoders.py, src/batch_sampler.py, src/models.py, src/test.py, src/train.py</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>There is non-trivial preprocessing logic (deduplication/NA handling and a tokenization wrapper) in the repo that qualifies as preprocessing code.</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>21525</v>
+      </c>
+    </row>
+    <row r="19" ht="78" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Agentmandering: A Game-Theoretic Framework for Fair Redistricting via Large Language Model Agents</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Lihaogx/AgentMandering</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>model/agent.py</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>def choose_draw(self, schemes: List[Dict], party: str) -&gt; str; prompt = self.background_info + "\n\n" + self.party_name_prompt; There are {num_districts} congressional districts in this state.</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>install_r_packages.R, main.py, model/agent.py, model/legacy_YCIF_protocol.py, model/llm_client.py, model/unified_YCIF_protocol.py, model/YCIF_protocol.py</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>There is executable code that builds and formats prompts used to query the LLM, i.e., a prompting/input construction pipeline.</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>8435</v>
+      </c>
+    </row>
+    <row r="20" ht="78" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>AgentSHAP: Interpreting LLM Agent Tool Importance with Monte Carlo Shapley Value Estimation</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/GenAISHAP/TokenSHAP</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>token_shap/agent_shap.py</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>def _prepare_generate_args(self, content: Any, **kwargs) -&gt; Dict:; return {"prompt": content, "tools": self.tools}; response, tool_usage = self.model.generate_with_tools(</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>notebooks/AgentSHAP Examples.ipynb, notebooks/TokenShap Examples.ipynb, notebooks/VideoSHAP Examples.ipynb, papers/Untitled.ipynb, token_shap/__init__.py, token_shap/agent_shap.py, token_shap/base.py</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>The AgentSHAP implementation includes executable code that constructs prompts using a subset of tools and runs the model, qualifying as a prompting/input-construction pipeline.</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>27973</v>
+      </c>
+    </row>
+    <row r="21" ht="78" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>A Granular Study of Safety Pretraining under Model Abliteration</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>prompting</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>src/evaluate.py, src/chat.py</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>evaluation_prompts = [; system_prompt = """; tokenizer.batch_encode_plus(</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>slurm.sh, slurm_short.sh, src/abliterate.py, src/chat.py, src/compare.py, src/evaluate.py</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>There is explicit prompting/input construction logic (in evaluate.py and chat.py) that wraps inputs into prompts before model invocation, satisfying the prompting wrapper requirement.</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>9008</v>
+      </c>
+    </row>
+    <row r="22" ht="78" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>filtering, prompting</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py, llm/llm1.py, llm/llm2.py, llm/llm3.py, llm/llm4.py, llm/llm5.py, llm/llm6.py, GENERIC SOURCE: llm/gradio.py</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>def censorship(user_prompt):; def filter(stage_response):; if it has problems or input is irrelevant with machine learning, please output 0 and provide a brief explanation of the problem and suggest a solution. Otherwise,simply output 1.</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py, llm/gradio.py, llm/llm1.py, llm/llm2.py, llm/llm3.py, llm/llm4.py, llm/llm5.py, llm/llm6.py</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>There exist real preprocessing-like components implementing a filtering pipeline and prompting wrappers, satisfying the criteria for executable preprocessing code.</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>8787</v>
+      </c>
+    </row>
+    <row r="23" ht="78" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>AIP-TranLAC: A Transformer-Based Method Integrating LSTM and Attention Mechanism for Predicting Anti-inflammatory Peptides</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Renjingyi123/AIP-TranLAC</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>tokenization</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>train.py</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>aa_dict = {'A': 1, 'R': 2, 'N': 3, 'D': 4, 'C': 5, 'Q': 6, 'E': 7, 'G': 8, 'H': 9, 'I': 10,; pep = pep + 'X' * (30-len_seq); data = rnn_utils.pad_sequence(pep_codes, batch_first=True)</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>train.py</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>The code implements non-trivial preprocessing (tokenization-like mapping of amino acids and sequence padding) within train.py.</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="24" ht="39" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Aligned or Apart? Multi-Agent Insights into Consumer and Brand Messaging Discrepancies</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/htgan-ai/OPIM</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25" ht="39" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Aligning Deep Implicit Preferences by Learning to Reason Defensively</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Zephyrian-Hugh/Deep-pref</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58.5" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>filtering</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>def censorship(user_prompt):; def filter(stage_response):; response=get_completion(prompt_sys)</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py, llm/gradio.py, llm/llm1.py, llm/llm2.py, llm/llm3.py, llm/llm4.py, llm/llm5.py, llm/llm6.py</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>The llm/filter.py file contains non-trivial, executable filtering logic that implements a moderation/cleaning pipeline for prompts and responses.</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>8554</v>
+      </c>
+    </row>
+    <row r="27" ht="214.5" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>A Solver‐Aided Hierarchical Language for LLM‐Driven Systems</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>filtering, prompting</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>AIDL/constraint_fitting/filter_programs.py, scripts/2024.02.14.collect_designs.py</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>for prog in program_errors.keys():
+        if program_errors[prog] &lt; threshold:
+            counter += 1
+            shutil.copyfile(os.path.join("dataset_quantized", prog), os.path.join("dataset_filtered", prog)); def query(system: str, messages: list, seed=27, force_json=False, start_max_tokens = 1024, final_max_tokens=16384):; natural_param_template = "Which design decisions and parameters must be decided upon when designing {}? List the 5 most important, focusing on numerical decisions like measurements (distances and angles) and counts.\n"</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>AIDL/constraint_fitting/filter_programs.py, data/gen_data.ipynb, data/plot_data.ipynb, scripts/2024.02.14.collect_designs.py, scripts/parse_structures.py, scripts/specific_constraints.py, scripts/test.py, setup.py, AIDL/__init__.py, AIDL/aidl.py, AIDL/common.py, AIDL/compositional_constraints.py, AIDL/constraints.py, AIDL/debug.py, AIDL/dispatch.py</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>There are non-trivial preprocessing scripts for filtering datasets and constructing prompts, demonstrating executable preprocessing pipelines.</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>18949</v>
+      </c>
+    </row>
+    <row r="28" ht="195" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>A Structured Framework for Evaluating and Enhancing LLM Robustness</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>src/preprocess.py, src/pipeline.py</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>VULCA Framework - Image Preprocessing Module; def adaptive_sliding_window(; def process_image(
+    image_path: str,</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>experiments/run_full_pipeline.sh, src/pipeline.py, src/preprocess.py, exhibitions/negative-space-of-the-tide/js/data-loader.js, scripts/add-artwork2-refs.js, scripts/add-artwork3-references.js, scripts/add-artwork4-references.js, scripts/add-multi-image-support.js, scripts/add-remaining-artworks.js, scripts/add-thread6-references.js, scripts/analyze-exhibition-data.py, scripts/analyze-image-paths.js, scripts/analyze-ppt-artworks.js, scripts/apply-batch-multi-image-updates.js, scripts/apply-metadata-enhancements.js, scripts/apply-multi-image-updates.js</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>There is actual preprocessing/pipeline code present, but it does not implement any of the specified categories (tokenization, filtering/cleaning, or prompting wrappers) in the shown files.</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>23942</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>A Survey of Reasoning and Agentic Systems in Time Series</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/blacksnail789521/Time-Series-Agent</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="39" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>A Survey on Latent Reasoning</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/multimodal-art-projection/Latent-Reasoning</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>No source files retrievable from the repo</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2669,7 +8347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2732,42 +8410,52 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="n"/>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
+      <c r="A3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>90% Faster, 100% Code-Free: MLLM-Driven Zero-Code 3D Game Development</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/yxwan123/UniGen</t>
+        </is>
+      </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>predict.py</t>
+          <t>blue_pipeline.py</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/CSUBioGroup/2OMe-LM/blob/HEAD/predict.py</t>
+          <t>https://github.com/yxwan123/UniGen/blob/HEAD/blue_pipeline.py</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>4DLangVGGT: 4D Language-Visual Geometry Grounded Transformer</t>
+          <t>Abstract A024: DeepVul: A multi-task transformer model for joint prediction of gene essentiality and drug response</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/hustvl/4DLangVGGT</t>
+          <t>https://github.com/alaaj27/DeepVul.git</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>preprocess/generate_vggttoken.py</t>
+          <t>src/JointDataset.py</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/preprocess/generate_vggttoken.py</t>
+          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/JointDataset.py</t>
         </is>
       </c>
     </row>
@@ -2777,62 +8465,52 @@
       <c r="C5" s="8" t="n"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>utils/demo_dataloader.py</t>
+          <t>src/utils.py</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/utils/demo_dataloader.py</t>
+          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/utils.py</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>90% Faster, 100% Code-Free: MLLM-Driven Zero-Code 3D Game Development</t>
+          <t>AccidentBench: Benchmarking Multimodal Understanding and Reasoning in Vehicle Accidents and Beyond</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/yxwan123/UniGen</t>
+          <t>https://github.com/SafeRL-Lab/AccidentBench</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>blue_pipeline.py</t>
+          <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/yxwan123/UniGen/blob/HEAD/blue_pipeline.py</t>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Abstract A024: DeepVul: A multi-task transformer model for joint prediction of gene essentiality and drug response</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/alaaj27/DeepVul.git</t>
-        </is>
-      </c>
+      <c r="A7" s="9" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>src/JointDataset.py</t>
+          <t>lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/JointDataset.py</t>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py</t>
         </is>
       </c>
     </row>
@@ -2842,51 +8520,837 @@
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>src/utils.py</t>
+          <t>tools/make_audio_hf_dataset.ipynb</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/utils.py</t>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/make_audio_hf_dataset.ipynb</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Accelerated Aggregated D-Optimal Designs for Estimating Main Effects in Black-Box Models</t>
+          <t>AdamMeme: Adaptively Probe the Reasoning Capacity of Multimodal Large Language Models on Harmfulness</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/cchihyu/A2D2E</t>
+          <t>https://github.com/Lbotirx/AdamMeme</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>GPT_agent.R</t>
+          <t>scripts/gen_misb.py</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/cchihyu/A2D2E/blob/HEAD/GPT_agent.R</t>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/gen_misb.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>scripts/mining.py</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/mining.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>scripts/refinement.py</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/refinement.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>scripts/prompts.py</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/prompts.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>scripts/run_llava.py</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/run_llava.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>scripts/scoring.py</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/scoring.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>scripts/utils.py</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/utils.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Adaptive Graph Learning with Transformer for Multi-Reservoir Inflow Prediction</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>_preprocess.py</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_preprocess.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Addressing Logical Fallacies In Scientific Reasoning From Large Language Models: Towards a Dual-Inference Training Framework</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/hannahdavidsoncollege-maker/ScientificReasoningForEnvironment-MedicineWithLLMs</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Hannah+Walker_Paper.ipynb</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/hannahdavidsoncollege-maker/ScientificReasoningForEnvironment-MedicineWithLLMs/blob/HEAD/Hannah+Walker_Paper.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>A Dual Large Language Models Architecture with Herald Guided Prompts for Parallel Fine Grained Traffic Signal Control</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/BUPT-ANTlab/HeraldLight</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>utils/pipeline.py</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/BUPT-ANTlab/HeraldLight/blob/HEAD/utils/pipeline.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Advancing ADMET prediction through multiscale fragment-aware pretraining with MSformer-ADMET</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/ZJUFanLab/MSformer</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>msformer/MSEncoder.py</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/MSEncoder.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>tokenizer/tokenizer.py</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/tokenizer/tokenizer.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Adversarial Attention Perturbations for Large Object Detection Transformers</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>utils/frcnn_utils/dataset.py</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/frcnn_utils/dataset.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>utils/frcnn_utils/voc_dataset.py</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/frcnn_utils/voc_dataset.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>utils/dataset_utils/voc/preprocessing.py</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/dataset_utils/voc/preprocessing.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>extras/detr_extras/d2/detr/dataset_mapper.py</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/extras/detr_extras/d2/detr/dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>models/detrex/detectron2/detectron2/data/dataset_mapper.py</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detectron2/detectron2/data/dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>models/detrex/detrex/data/dataset_mappers/coco_panoptic_new_baseline_dataset_mapper.py</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detrex/data/dataset_mappers/coco_panoptic_new_baseline_dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>A First-Order Logic-Based Alternative to Reward Models in RLHF</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>train/dpo_train.py</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/dpo_train.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>train/generate_fol.py</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/generate_fol.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>train/sft_training.py</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/sft_training.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>train/train.py</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/train.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>A foundation model for learning genetic associations from brain imaging phenotypes</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>src/dataset_template.py</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical/blob/HEAD/src/dataset_template.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Agentmandering: A Game-Theoretic Framework for Fair Redistricting via Large Language Model Agents</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/Lihaogx/AgentMandering</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>model/agent.py</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lihaogx/AgentMandering/blob/HEAD/model/agent.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>AgentSHAP: Interpreting LLM Agent Tool Importance with Monte Carlo Shapley Value Estimation</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/GenAISHAP/TokenSHAP</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>token_shap/agent_shap.py</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/GenAISHAP/TokenSHAP/blob/HEAD/token_shap/agent_shap.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>A Granular Study of Safety Pretraining under Model Abliteration</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>src/evaluate.py</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/evaluate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>src/chat.py</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/chat.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/filter.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="9" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm1.py</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm1.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="9" t="n"/>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm2.py</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm2.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm3.py</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm3.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="9" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm4.py</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm4.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="9" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm5.py</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm5.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="9" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm6.py</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm6.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>GENERIC SOURCE: llm/gradio.py</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/GENERIC SOURCE: llm/gradio.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>AIP-TranLAC: A Transformer-Based Method Integrating LSTM and Attention Mechanism for Predicting Anti-inflammatory Peptides</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/Renjingyi123/AIP-TranLAC</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>train.py</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Renjingyi123/AIP-TranLAC/blob/HEAD/train.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/filter.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>A Solver‐Aided Hierarchical Language for LLM‐Driven Systems</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>AIDL/constraint_fitting/filter_programs.py</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/AIDL/constraint_fitting/filter_programs.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>scripts/2024.02.14.collect_designs.py</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/2024.02.14.collect_designs.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>A Structured Framework for Evaluating and Enhancing LLM Robustness</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>src/preprocess.py</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/src/preprocess.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>src/pipeline.py</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/src/pipeline.py</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="30">
+    <mergeCell ref="C9:C15"/>
+    <mergeCell ref="C37:C44"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B9:B15"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="A9:A15"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A37:A44"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B37:B44"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="A35:A36"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B6:B8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
@@ -2897,6 +9361,47 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2928,133 +9433,133 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Total Repos Checked</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n">
-        <v>5</v>
+      <c r="B2" s="11" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>EXISTS</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
-        <v>5</v>
+      <c r="B3" s="11" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>NOT_APPLICABLE</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Skipped (non-GitHub)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Skipped (non-GitHub)</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="n">
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Errors</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Coverage (%)</t>
         </is>
       </c>
-      <c r="B7" s="10">
-        <f>5/5*100</f>
+      <c r="B7" s="11">
+        <f>17/29*100</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr"/>
-      <c r="B8" s="10" t="inlineStr"/>
+      <c r="A8" s="10" t="inlineStr"/>
+      <c r="B8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>LLM Token Usage</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr"/>
+      <c r="B9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Model / Deployment</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>gpt-5-nano-2025-08-07</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Requests</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>5</v>
+      <c r="B11" s="11" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Input Tokens</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>46,551</t>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>274,218</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Output Tokens</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>8,229</t>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>42,538</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Tokens</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>54,780</t>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>316,756</t>
         </is>
       </c>
     </row>

--- a/requirement_checks/5.1.code_availability/5.1.3.pre-processing_&_pipeline_code/results/preprocessing_code_results.xlsx
+++ b/requirement_checks/5.1.code_availability/5.1.3.pre-processing_&_pipeline_code/results/preprocessing_code_results.xlsx
@@ -177,8 +177,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -629,7 +629,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="58.5" customHeight="1">
+    <row r="2" ht="78" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -655,12 +655,12 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>data/mydataset.py, predict.py</t>
+          <t>data/mydataset.py, data/mydataset.py, predict.py</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>input_ids = self.tokenizer.encode(seq, add_special_tokens=True); k_RNA = [seq[j:j + 4] for j in range(len(seq) - 4 + 1)]</t>
+          <t>self.k_RNA = [[i[j:j + 4] for j in range(len(i) - 4 + 1)] for i in fasta_seqs]; input_ids = self.tokenizer.encode(seq, add_special_tokens=True); k_RNA = [seq[j:j + 4] for j in range(len(seq) - 4 + 1)]</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>There is real tokenization code that processes RNA sequences into model-ready inputs using k-mers and a pretrained tokenizer.</t>
+          <t>There is executable preprocessing code that tokenizes RNA sequences into k-mers and encodes them with a tokenizer before modeling.</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>8930</v>
+        <v>8306</v>
       </c>
     </row>
     <row r="3" ht="195" customHeight="1">
@@ -708,19 +708,19 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>utils/demo_dataloader.py, preprocess/generate_vggttoken.py</t>
+          <t>preprocess/generate_vggttoken.py, utils/demo_dataloader.py</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>concatenated_tensor = torch.cat((all_aggregated_tokens[pos]), dim=1)
-aggregated_tokens_list.append(concatenated_tensor); streamvggt.inference_long_video(
+          <t>streamvggt.inference_long_video(
                 image_files,
                 save_dir=save_dir,
                 keys=keys,
                 mode=args.mode,
                 max_num=args.max_num
-            )</t>
+            ); all_aggregated_tokens[pos].append(torch.from_numpy(item[key][pos]))
+concatenated_tensor = torch.cat((all_aggregated_tokens[pos]), dim=1)</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>The repo includes a non-trivial dataloader/collate pipeline assembling model inputs and a preprocessing script that generates and saves model tokens from image sequences.</t>
+          <t>There is executable code to generate and save image tokens and batch-assemble those tokens and features into model-ready inputs.</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="K3" s="4" t="n">
-        <v>17293</v>
-      </c>
-    </row>
-    <row r="4" ht="97.5" customHeight="1">
+        <v>17832</v>
+      </c>
+    </row>
+    <row r="4" ht="78" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -773,9 +773,8 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>def generate_blueprints(self, asset_info, game_description):
-        prompt = (
-            "You are a Unity game architecture expert. Based on the following description, generate a JSON array</t>
+          <t>prompt = (
+            "You are a Unity game architecture expert. Based on the following description, generate a JSON array of GameObject blueprints. Each object must include:\n"</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -785,7 +784,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>The repository contains executable code that constructs detailed LLM prompts for input assembly.</t>
+          <t>There is executable code that builds detailed chat templates to generate model inputs, which qualifies as prompting.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -794,7 +793,7 @@
         </is>
       </c>
       <c r="K4" s="4" t="n">
-        <v>6662</v>
+        <v>5982</v>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1">
@@ -829,7 +828,7 @@
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp)); scaler = StandardScaler()
-np_array_scaled = scaler.fit_transform(np_array); drug = drug[variable_drug].fillna(drug.mean())</t>
+np_array_scaled = scaler.fit_transform(np_array); Essentiality = Essentiality[var_features].dropna(axis='columns')</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -839,7 +838,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>There is executable preprocessing code performing normalization and data cleaning prior to model input.</t>
+          <t>There is executable preprocessing code that cleans/selects features and normalizes gene expression data prior to training.</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -848,7 +847,7 @@
         </is>
       </c>
       <c r="K5" s="4" t="n">
-        <v>9817</v>
+        <v>10297</v>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1">
@@ -874,7 +873,7 @@
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Only algorithmic PD/ALE/A2D2E curve computations and parameter dicts are present; no tokenization, filtering, or prompt-building code.</t>
+          <t>Repository contains algorithmic curve computations (PD/ALE/A2D2E) and model params, but no data preprocessing/tokenization/prompting code.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -884,7 +883,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>The code implements analysis algorithms (including quantile binning within PD/ALE) rather than any dataset preprocessing, tokenization, filtering, or prompt assembly.</t>
+          <t>The code only implements analysis curves with internal binning as part of the method, not any executable preprocessing, tokenization, filtering, or prompt assembly.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -893,7 +892,7 @@
         </is>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4586</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="7" ht="195" customHeight="1">
@@ -922,12 +921,14 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>tools/live_bench/filter.ipynb, lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py, tools/make_audio_hf_dataset.ipynb</t>
+          <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py, tools/live_bench/filter.ipynb, tools/make_audio_hf_dataset.ipynb</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>filtered_data = data["test"].filter(lambda example: example["score"] and example["score"] &gt; 5); "lexeme_splitter": nltk.tokenize.word_tokenize,; (self.settings["do_stop_words"] and lexeme.lower() in self.stop_words)</t>
+          <t>segments = analyzer(text)
+        if analyzer is nltk.word_tokenize:
+            segments = self._divide_long_lexemes(segments); (self.settings["do_stop_words"] and lexeme.lower() in self.stop_words) or (self.settings["remove_numerics"] and lexeme.isnumeric()); class MplugOwlTokenizer(LlamaTokenizer):</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -937,7 +938,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>There is executable code for tokenizing text, filtering dataset rows, and constructing audio-augmented prompts.</t>
+          <t>There is executable code for text tokenization, data filtering, and assembling audio-text prompts before model input.</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -946,7 +947,7 @@
         </is>
       </c>
       <c r="K7" s="4" t="n">
-        <v>19212</v>
+        <v>19459</v>
       </c>
     </row>
     <row r="8" ht="39" customHeight="1">
@@ -1052,7 +1053,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>The repository contains executable code that constructs and feeds multimodal prompts to LLMs, clearly implementing a prompting pipeline.</t>
+          <t>The repository contains executable code that builds and uses multimodal prompts to construct model inputs.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1061,10 +1062,10 @@
         </is>
       </c>
       <c r="K10" s="4" t="n">
-        <v>26284</v>
-      </c>
-    </row>
-    <row r="11" ht="117" customHeight="1">
+        <v>26327</v>
+      </c>
+    </row>
+    <row r="11" ht="97.5" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -1095,9 +1096,8 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>X.append(data[i:i+_days_x, :_input_features])
-y.append(data[i+_days_x:i+_days_x+_days_y, -1]); scaler_X = MinMaxScaler(feature_range=(0, 1))
-scaler_X.fit(all_train_X); TPR['Date'] = TPR['Date'].apply(lambda x: x.replace(year=x.year-100) if x.year &gt; 2021 else x)</t>
+          <t>X.append(data[i:i+_days_x, :_input_features]); y.append(data[i+_days_x:i+_days_x+_days_y, -1]); scaler_X.transform(data['train']['X'].reshape(-1, _input_features)).reshape(data['train']['X'].shape); TPR = TPR.dropna(subset=['Date'])
+TPR = TPR[TPR['Date'].isin(dates)]</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>There is executable preprocessing code for windowing (tokenization) and data normalization/cleaning (filtering) across multiple scripts.</t>
+          <t>There is executable preprocessing code for time-series windowing (tokenization) and data normalization/cleaning (filtering).</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="K11" s="4" t="n">
-        <v>21567</v>
-      </c>
-    </row>
-    <row r="12" ht="117" customHeight="1">
+        <v>21190</v>
+      </c>
+    </row>
+    <row r="12" ht="58.5" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -1150,10 +1150,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>if PQ:
-        query = f"Is it true that '{P}' implies '{Q}'? Answer with 'yes' or 'no'."
-    else:
-        query = f"Negating: Is it true that '{Q}' implies '{P}'? Answer with 'yes' or 'no'."</t>
+          <t>query = f"Is it true that '{P}' implies '{Q}'? Answer with 'yes' or 'no'."</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1163,7 +1160,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>There is executable code that assembles prompts from raw sentences (including negations and order swaps) before calling the model.</t>
+          <t>The code constructs and formats prompts from raw sentences before querying the LLM.</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1172,10 +1169,10 @@
         </is>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4712</v>
-      </c>
-    </row>
-    <row r="13" ht="214.5" customHeight="1">
+        <v>3851</v>
+      </c>
+    </row>
+    <row r="13" ht="234" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -1208,12 +1205,13 @@
         <is>
           <t>prompt = {
   "messages": [
-    {"role": "system", "content": [{"type": "text","text": "You are an AI assistant..."}]}
-  ]
-}; messages = [
-    {"role": "system", "content": "You are a master in traffic signal control"},
-    {"role": "user", "content": prompt[0]['content'][0]['text']},
-]</t>
+    {
+        "role": "system",
+        "content": [
+            {"type": "text","text": "You are an AI assistant that helps people find information."}; messages = [
+        {"role": "system", "content": "You are a master in traffic signal control"},
+        {"role": "user", "content": prompt[0]['content'][0]['text']},
+    ]</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1223,7 +1221,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>There is executable code constructing LLM chat prompts prior to model calls, which qualifies as prompting.</t>
+          <t>There is executable code that constructs chat prompts prior to calling LLMs, which qualifies as prompting.</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1232,10 +1230,10 @@
         </is>
       </c>
       <c r="K13" s="4" t="n">
-        <v>20563</v>
-      </c>
-    </row>
-    <row r="14" ht="117" customHeight="1">
+        <v>20656</v>
+      </c>
+    </row>
+    <row r="14" ht="78" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -1261,15 +1259,13 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>msformer/masskg.py, msformer/utils.py</t>
+          <t>msformer/MSEncoder.py, msformer/masskg.py</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>fmol = Chem.FragmentOnBonds(mol,bd)
-frag_mols = Chem.GetMolFrags(fmol,asMols=True); if not bond.IsInRing():
-                        bondsDone.add(match) 
-                        yield (((match[0], match[1]), (i1, i2)))</t>
+          <t>encodings = self.tokenizer.batch_encode_plus(batch, padding=True, add_special_tokens=True); fmol = Chem.FragmentOnBonds(mol,bd) #断裂键
+frag_mols = Chem.GetMolFrags(fmol,asMols=True)</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1279,7 +1275,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>There is executable code that fragments molecules into substructures, constituting a tokenization-style preprocessing pipeline.</t>
+          <t>There is executable code that splits molecules into fragments and tokenizes strings for model-ready inputs.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1288,7 +1284,7 @@
         </is>
       </c>
       <c r="K14" s="4" t="n">
-        <v>16287</v>
+        <v>16229</v>
       </c>
     </row>
     <row r="15" ht="58.5" customHeight="1">
@@ -1365,7 +1361,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>There is clear, runnable code that resizes/normalizes/flips/crops/pads images and filters annotations prior to model input.</t>
+          <t>Multiple dataset mappers/utilities implement real image resizing/normalization/augmentation and annotation filtering before model input.</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1374,10 +1370,10 @@
         </is>
       </c>
       <c r="K16" s="4" t="n">
-        <v>21660</v>
-      </c>
-    </row>
-    <row r="17" ht="117" customHeight="1">
+        <v>22371</v>
+      </c>
+    </row>
+    <row r="17" ht="97.5" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -1403,12 +1399,12 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>train/dpo_train.py, train/dpo_train.py, train/generate_fol.py, train/sft_training.py, utils/LogicalEquivalence.py</t>
+          <t>train/dpo_train.py, train/dpo_train.py, train/sft_training.py</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>text = tokenizer.apply_chat_template([{'role': "user", "content": samples['prompt']}], tokenize=False, add_generation_prompt=True, enable_thinking=False); train_dataset = train_dataset.filter(lambda sample: len(sample['chosen']) &gt; 0); train_dataset = train_dataset.filter(lambda example: example["label"] == "faithful")</t>
+          <t>text = tokenizer.apply_chat_template([{'role': "user", "content": samples['prompt']}], tokenize=False; train_dataset = train_dataset.filter(lambda sample: sample['better_response_id'] == sample['safer_response_id']; prompt_input_ids = Tokenizer.encode(prompt_input, add_special_tokens=False)</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1418,7 +1414,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>There is executable preprocessing code for prompting, filtering, and tokenizing data prior to modeling.</t>
+          <t>There is executable code for filtering datasets, assembling prompts via chat templates, and tokenizing inputs.</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1427,10 +1423,10 @@
         </is>
       </c>
       <c r="K17" s="4" t="n">
-        <v>14862</v>
-      </c>
-    </row>
-    <row r="18" ht="97.5" customHeight="1">
+        <v>28930</v>
+      </c>
+    </row>
+    <row r="18" ht="78" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -1461,9 +1457,8 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>idps_raw = pd.read_csv(path)
-idps_raw = idps_raw.loc[:, ~idps_raw.columns.str.replace("(\.\d+)$", "").duplicated()]
-idps_filt = idps_raw.dropna(thresh=len(idps_raw) - 1, axis=1)</t>
+          <t>idps_raw = idps_raw.loc[:, ~idps_raw.columns.str.replace("(\.\d+)$", "").duplicated()]
+self.idps_filt = idps_raw.dropna(how= 'any', axis=0)</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1473,7 +1468,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>There is executable data-cleaning logic (deduplication and NA filtering) in the dataset loader.</t>
+          <t>The repository includes executable data filtering/cleaning logic in the dataset pipeline.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1482,10 +1477,10 @@
         </is>
       </c>
       <c r="K18" s="4" t="n">
-        <v>23941</v>
-      </c>
-    </row>
-    <row r="19" ht="78" customHeight="1">
+        <v>22790</v>
+      </c>
+    </row>
+    <row r="19" ht="58.5" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -1516,8 +1511,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>prompt = self.background_info + "\n\n" + self.party_name_prompt
-messages = [{"role": "user", "content": prompt}]
+          <t>messages = [{"role": "user", "content": prompt}]
 response = self.llm_client.get_completion(messages)</t>
         </is>
       </c>
@@ -1528,7 +1522,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>The repository contains executable code that constructs LLM prompts/messages from raw scheme information, which qualifies as prompting.</t>
+          <t>The repository includes code that assembles LLM prompts from scheme data before invoking the model.</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1537,7 +1531,7 @@
         </is>
       </c>
       <c r="K19" s="4" t="n">
-        <v>9339</v>
+        <v>8892</v>
       </c>
     </row>
     <row r="20" ht="156" customHeight="1">
@@ -1587,7 +1581,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>There is executable code that constructs model input payloads (including multimodal inputs) before calling a model, which qualifies as prompting.</t>
+          <t>The repository contains executable code that assembles prompts (and images) into model-ready API inputs.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1596,10 +1590,10 @@
         </is>
       </c>
       <c r="K20" s="4" t="n">
-        <v>12739</v>
-      </c>
-    </row>
-    <row r="21" ht="156" customHeight="1">
+        <v>13017</v>
+      </c>
+    </row>
+    <row r="21" ht="273" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -1625,12 +1619,18 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>src/chat.py, src/evaluate.py</t>
+          <t>src/chat.py, src/evaluate.py, src/evaluate.py</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>toks = tokenizer.apply_chat_template(conversation=conversation, add_generation_prompt=True, return_tensors="pt"); inputs = tokenizer.batch_encode_plus(
+          <t>toks = tokenizer.apply_chat_template(
+            conversation=conversation, add_generation_prompt=True, return_tensors="pt"
+        ); evaluation_prompts = [
+            f"{system_prompt}\n"
+            f"### Prompt:\n{question}\n\n"
+            f"### Response:\n{response}\n\n"
+            "CLASSIFICATION: "; inputs = tokenizer.batch_encode_plus(
             evaluation_prompts,
             return_tensors="pt",
             padding=True,
@@ -1645,7 +1645,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>There is executable code that builds chat-style prompts and tokenizes evaluation inputs prior to model inference.</t>
+          <t>There is executable prompt-building code (chat templates and evaluation prompts) and tokenization used to prepare inputs.</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="K21" s="4" t="n">
-        <v>22349</v>
-      </c>
-    </row>
-    <row r="22" ht="234" customHeight="1">
+        <v>10582</v>
+      </c>
+    </row>
+    <row r="22" ht="58.5" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -1683,15 +1683,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>llm/filter.py, llm/llm1.py, llm/llm2.py</t>
+          <t>llm/filter.py, llm/llm1.py, llm/llm2.py, llm/llm3.py, llm/llm4.py</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>prompt_sys=f""" 
-    {user_prompt} is the user prompt for the LLM,your task is to check whether it has moral or other safety problems and whether it is irrelevant with machine leaarning..; prompt_sys=f"""You are a helpful assistant that analyze data modalities
-in multimodal Auto-Machine learning task.
-Your task is to analyze the data type of each column; prompt2=f"""{model_card}is the model chosen for the task{other_text} which contains dataset of modality {unique[index]},please only give the reasons for chossing the model without any other context"""</t>
+          <t>response=get_completion(prompt_sys); response,history=get_completion(prompt_sys,prompt,history); response2[index]=get_completion(prompt2)</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1701,7 +1698,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>The repository contains executable code that builds chat prompts and retrieval-augmented inputs for an LLM.</t>
+          <t>The repository contains real code that assembles prompts and feeds them to LLMs (prompting), though no dataset tokenization or filtering.</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1710,7 +1707,7 @@
         </is>
       </c>
       <c r="K22" s="4" t="n">
-        <v>22545</v>
+        <v>10155</v>
       </c>
     </row>
     <row r="23" ht="58.5" customHeight="1">
@@ -1744,9 +1741,9 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>pep = pep + 'X' * (30-len_seq)
-for aa in pep:
-    current_pep.append(aa_dict[aa])</t>
+          <t>for aa in pep:
+    current_pep.append(aa_dict[aa])
+pep_codes.append(torch.tensor(current_pep))</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1756,7 +1753,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>A preprocessing routine maps sequence characters to indices and pads to fixed length, which is tokenization.</t>
+          <t>The code implements tokenization of peptide sequences (char-to-index mapping and padding) prior to training.</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1765,7 +1762,7 @@
         </is>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4462</v>
+        <v>4857</v>
       </c>
     </row>
     <row r="24" ht="39" customHeight="1">
@@ -1830,7 +1827,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr"/>
     </row>
-    <row r="26" ht="156" customHeight="1">
+    <row r="26" ht="331.5" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -1856,14 +1853,23 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>AIDL/constraint_fitting/filter_programs.py, scripts/2024.02.14.collect_designs.py</t>
+          <t>AIDL/constraint_fitting/filter_programs.py, scripts/2024.02.14.collect_designs.py, scripts/parse_structures.py, scripts/specific_constraints.py</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
           <t>if program_errors[prog] &lt; threshold:
             counter += 1
-            shutil.copyfile(os.path.join("dataset_quantized", prog), os.path.join("dataset_filtered", prog)); message_list.append({
+            shutil.copyfile(os.path.join("dataset_quantized", prog), os.path.join("dataset_filtered", prog)); roles = ['user', 'assistant']
+for i, message in enumerate(messages):
+    role = roles[i%2]
+    message_list.append({
+            "role": role,
+            "content": message
+        }); roles = ['user', 'assistant']
+for i, message in enumerate(messages):
+    role = roles[i%2]
+    message_list.append({
             "role": role,
             "content": message
         })</t>
@@ -1876,7 +1882,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>There is executable filtering of dataset files and explicit construction of LLM prompts before model calls.</t>
+          <t>There is executable filtering code and chat prompt construction code used to assemble model inputs.</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1885,7 +1891,7 @@
         </is>
       </c>
       <c r="K26" s="4" t="n">
-        <v>18135</v>
+        <v>17963</v>
       </c>
     </row>
     <row r="27" ht="195" customHeight="1">
@@ -1919,8 +1925,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>patch = image[y:y+window_size, x:x+window_size]
-patches.append(resized); resized = cv2.resize(patch, (output_size, output_size))</t>
+          <t>patch = image[y:y+window_size, x:x+window_size]; resized = cv2.resize(patch, (output_size, output_size))</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1930,7 +1935,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Executable image preprocessing code exists that tokenizes images into patches and normalizes them via resizing.</t>
+          <t>There is real image preprocessing code that extracts patches (tokenization) and normalizes them via resizing (filtering).</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1939,7 +1944,7 @@
         </is>
       </c>
       <c r="K27" s="4" t="n">
-        <v>23568</v>
+        <v>23397</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -3097,21 +3102,21 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>285,696</t>
+          <t>274,426</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>43,817</t>
+          <t>43,133</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>329,513</t>
+          <t>317,559</t>
         </is>
       </c>
     </row>
@@ -3126,17 +3131,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>258,470</t>
+          <t>253,640</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>23,383</t>
+          <t>26,469</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>281,853</t>
+          <t>280,109</t>
         </is>
       </c>
     </row>
@@ -3151,17 +3156,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>305,282</t>
+          <t>292,180</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>56,947</t>
+          <t>59,845</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>362,229</t>
+          <t>352,025</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3251,7 +3256,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>input_ids = self.tokenizer.encode(seq, add_special_tokens=True)</t>
+          <t>self.k_RNA = [[i[j:j + 4] for j in range(len(i) - 4 + 1)] for i in fasta_seqs]</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -3260,71 +3265,70 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3" ht="39" customHeight="1">
       <c r="A3" s="8" t="n"/>
       <c r="B3" s="8" t="n"/>
       <c r="C3" s="8" t="n"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>data/mydataset.py</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>input_ids = self.tokenizer.encode(seq, add_special_tokens=True)</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/CSUBioGroup/2OMe-LM/blob/HEAD/data/mydataset.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
           <t>predict.py</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>k_RNA = [seq[j:j + 4] for j in range(len(seq) - 4 + 1)]</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>https://github.com/CSUBioGroup/2OMe-LM/blob/HEAD/predict.py</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="58.5" customHeight="1">
-      <c r="A4" s="2" t="n">
+    <row r="5" ht="136.5" customHeight="1">
+      <c r="A5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>4DLangVGGT: 4D Language-Visual Geometry Grounded Transformer</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>https://github.com/hustvl/4DLangVGGT</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>utils/demo_dataloader.py</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Prompting wrappers</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>concatenated_tensor = torch.cat((all_aggregated_tokens[pos]), dim=1)
-aggregated_tokens_list.append(concatenated_tensor)</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/utils/demo_dataloader.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="136.5" customHeight="1">
-      <c r="A5" s="8" t="n"/>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>preprocess/generate_vggttoken.py</t>
@@ -3352,126 +3356,126 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="97.5" customHeight="1">
-      <c r="A6" s="2" t="n">
+    <row r="6" ht="78" customHeight="1">
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>utils/demo_dataloader.py</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>all_aggregated_tokens[pos].append(torch.from_numpy(item[key][pos]))
+concatenated_tensor = torch.cat((all_aggregated_tokens[pos]), dim=1)</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/utils/demo_dataloader.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1">
+      <c r="A7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>90% Faster, 100% Code-Free: MLLM-Driven Zero-Code 3D Game Development</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>https://github.com/yxwan123/UniGen</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>blue_pipeline.py</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>def generate_blueprints(self, asset_info, game_description):
-        prompt = (
-            "You are a Unity game architecture expert. Based on the following description, generate a JSON array</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>prompt = (
+            "You are a Unity game architecture expert. Based on the following description, generate a JSON array of GameObject blueprints. Each object must include:\n"</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>https://github.com/yxwan123/UniGen/blob/HEAD/blue_pipeline.py</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="39" customHeight="1">
-      <c r="A7" s="2" t="n">
+    <row r="8" ht="39" customHeight="1">
+      <c r="A8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Abstract A024: DeepVul: A multi-task transformer model for joint prediction of gene essentiality and drug response</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>https://github.com/alaaj27/DeepVul.git</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>src/JointDataset.py</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp))</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/JointDataset.py</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="39" customHeight="1">
-      <c r="A8" s="9" t="n"/>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="4" t="inlineStr">
+    <row r="9" ht="39" customHeight="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>src/JointDataset.py</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>scaler = StandardScaler()
 np_array_scaled = scaler.fit_transform(np_array)</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/JointDataset.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="9" t="n"/>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>src/utils.py</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Filtering</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>drug = drug[variable_drug].fillna(drug.mean())</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/utils.py</t>
         </is>
       </c>
     </row>
@@ -3500,95 +3504,97 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="39" customHeight="1">
-      <c r="A11" s="2" t="n">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>src/utils.py</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>drug = drug[variable_drug].fillna(drug.mean())</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/utils.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="78" customHeight="1">
+      <c r="A12" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>AccidentBench: Benchmarking Multimodal Understanding and Reasoning in Vehicle Accidents and Beyond</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>https://github.com/SafeRL-Lab/AccidentBench</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>tools/live_bench/filter.ipynb</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>segments = analyzer(text)
+        if analyzer is nltk.word_tokenize:
+            segments = self._divide_long_lexemes(segments)</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58.5" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>filtered_data = data["test"].filter(lambda example: example["score"] and example["score"] &gt; 5)</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/live_bench/filter.ipynb</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58.5" customHeight="1">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>"lexeme_splitter": nltk.tokenize.word_tokenize,</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>(self.settings["do_stop_words"] and lexeme.lower() in self.stop_words) or (self.settings["remove_numerics"] and lexeme.isnumeric())</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="58.5" customHeight="1">
-      <c r="A13" s="9" t="n"/>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Filtering</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>(self.settings["do_stop_words"] and lexeme.lower() in self.stop_words)</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
-        </is>
-      </c>
-    </row>
     <row r="14" ht="39" customHeight="1">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
       <c r="D14" s="4" t="inlineStr">
         <is>
           <t>lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py</t>
@@ -3616,134 +3622,132 @@
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="4" t="inlineStr">
         <is>
+          <t>tools/live_bench/filter.ipynb</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>filtered_data = data["test"].filter(lambda example: example["score"] and example["score"] &gt; 5)</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/live_bench/filter.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="39" customHeight="1">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
           <t>tools/make_audio_hf_dataset.ipynb</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>prompt_list.append("&lt;|audio_bos|&gt;&lt;|AUDIO|&gt;&lt;|audio_eos|&gt;" + json_data['prompt'])</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/make_audio_hf_dataset.ipynb</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="39" customHeight="1">
-      <c r="A16" s="2" t="n">
+    <row r="17" ht="39" customHeight="1">
+      <c r="A17" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>AdamMeme: Adaptively Probe the Reasoning Capacity of Multimodal Large Language Models on Harmfulness</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>https://github.com/Lbotirx/AdamMeme</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>scripts/gen_misb.py</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>misb = gpt4o_generate(prompt.replace(r"{task}",data['task']), [data['image'].replace('erased','ori')])</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/gen_misb.py</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="39" customHeight="1">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="4" t="inlineStr">
+    <row r="18" ht="39" customHeight="1">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>scripts/mining.py</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>response = gpt4o_generate(prompt, [data["image"]],temp = 1)</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/mining.py</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="39" customHeight="1">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="4" t="inlineStr">
+    <row r="19" ht="39" customHeight="1">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>scripts/refinement.py</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>optimized_res = gpt4o_generate_imglist(optimized_prompt, target_meme_image_paths,temp=1)</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/refinement.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58.5" customHeight="1">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>scripts/run_llava.py</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Prompting wrappers</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>conv.append_message(conv.roles[0], qs)
-conv.append_message(conv.roles[1], None)
-prompt = conv.get_prompt()</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/run_llava.py</t>
         </is>
       </c>
     </row>
@@ -3753,549 +3757,551 @@
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="4" t="inlineStr">
         <is>
+          <t>scripts/run_llava.py</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>qs = re.sub(IMAGE_PLACEHOLDER, image_token_se, qs)</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/run_llava.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58.5" customHeight="1">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
           <t>scripts/scoring.py</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>gen_res = target_model_gen(new_prompt, [data['image']])</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>new_prompt += "[Instruction]" + cats_gen_meme[cat]['prompt'] + \
+                            "\nmeme_text: " + data['text']</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/scoring.py</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="39" customHeight="1">
-      <c r="A21" s="2" t="n">
+    <row r="22" ht="39" customHeight="1">
+      <c r="A22" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Adaptive Graph Learning with Transformer for Multi-Reservoir Inflow Prediction</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>https://github.com/humphreyhuu/AdaTrip</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>_preprocess.py</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>X.append(data[i:i+_days_x, :_input_features])
-y.append(data[i+_days_x:i+_days_x+_days_y, -1])</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>X.append(data[i:i+_days_x, :_input_features]); y.append(data[i+_days_x:i+_days_x+_days_y, -1])</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_preprocess.py</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="39" customHeight="1">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="4" t="inlineStr">
+    <row r="23" ht="39" customHeight="1">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>_preprocess.py</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>scaler_X = MinMaxScaler(feature_range=(0, 1))
-scaler_X.fit(all_train_X)</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>scaler_X.transform(data['train']['X'].reshape(-1, _input_features)).reshape(data['train']['X'].shape)</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_preprocess.py</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="39" customHeight="1">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>_aligning_time.ipynb</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Filtering</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>TPR['Date'] = TPR['Date'].apply(lambda x: x.replace(year=x.year-100) if x.year &gt; 2021 else x)</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_aligning_time.ipynb</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58.5" customHeight="1">
+    <row r="24" ht="39" customHeight="1">
       <c r="A24" s="8" t="n"/>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="4" t="inlineStr">
         <is>
+          <t>_aligning_time.ipynb</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>TPR = TPR.dropna(subset=['Date'])
+TPR = TPR[TPR['Date'].isin(dates)]</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_aligning_time.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58.5" customHeight="1">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
           <t>_get_weather_prediction.py</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>daily_data = df.groupby(['reservoir', 'year', 'day_of_year']).agg({'temperature': 'mean', 'precipitation': 'mean'}).reset_index()</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>daily_data = df.groupby(['reservoir','year','day_of_year']).agg({'temperature':'mean','precipitation':'mean'}).reset_index()</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_get_weather_prediction.py</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="117" customHeight="1">
-      <c r="A25" s="2" t="n">
+    <row r="26" ht="58.5" customHeight="1">
+      <c r="A26" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Addressing Logical Fallacies In Scientific Reasoning From Large Language Models: Towards a Dual-Inference Training Framework</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>https://github.com/hannahdavidsoncollege-maker/ScientificReasoningForEnvironment-MedicineWithLLMs</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Hannah+Walker_Paper.ipynb</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>if PQ:
-        query = f"Is it true that '{P}' implies '{Q}'? Answer with 'yes' or 'no'."
-    else:
-        query = f"Negating: Is it true that '{Q}' implies '{P}'? Answer with 'yes' or 'no'."</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>query = f"Is it true that '{P}' implies '{Q}'? Answer with 'yes' or 'no'."</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>https://github.com/hannahdavidsoncollege-maker/ScientificReasoningForEnvironment-MedicineWithLLMs/blob/HEAD/Hannah+Walker_Paper.ipynb</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="117" customHeight="1">
-      <c r="A26" s="2" t="n">
+    <row r="27" ht="136.5" customHeight="1">
+      <c r="A27" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>A Dual Large Language Models Architecture with Herald Guided Prompts for Parallel Fine Grained Traffic Signal Control</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>https://github.com/BUPT-ANTlab/HeraldLight</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>a_test_online_model/gpt-4o-mini.py</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>prompt = {
   "messages": [
-    {"role": "system", "content": [{"type": "text","text": "You are an AI assistant..."}]}
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
+    {
+        "role": "system",
+        "content": [
+            {"type": "text","text": "You are an AI assistant that helps people find information."}</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>https://github.com/BUPT-ANTlab/HeraldLight/blob/HEAD/a_test_online_model/gpt-4o-mini.py</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="117" customHeight="1">
-      <c r="A27" s="8" t="n"/>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="4" t="inlineStr">
+    <row r="28" ht="117" customHeight="1">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>a_test_online_model/Llama_inference.py</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>messages = [
-    {"role": "system", "content": "You are a master in traffic signal control"},
-    {"role": "user", "content": prompt[0]['content'][0]['text']},
-]</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
+        {"role": "system", "content": "You are a master in traffic signal control"},
+        {"role": "user", "content": prompt[0]['content'][0]['text']},
+    ]</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>https://github.com/BUPT-ANTlab/HeraldLight/blob/HEAD/a_test_online_model/Llama_inference.py</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="39" customHeight="1">
-      <c r="A28" s="2" t="n">
+    <row r="29" ht="39" customHeight="1">
+      <c r="A29" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Advancing ADMET prediction through multiscale fragment-aware pretraining with MSformer-ADMET</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>https://github.com/ZJUFanLab/MSformer</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>msformer/MSEncoder.py</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>encodings = self.tokenizer.batch_encode_plus(batch, padding=True, add_special_tokens=True)</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/MSEncoder.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="39" customHeight="1">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>msformer/masskg.py</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>fmol = Chem.FragmentOnBonds(mol,bd)
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>fmol = Chem.FragmentOnBonds(mol,bd) #断裂键
 frag_mols = Chem.GetMolFrags(fmol,asMols=True)</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/masskg.py</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="78" customHeight="1">
-      <c r="A29" s="8" t="n"/>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>msformer/utils.py</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>if not bond.IsInRing():
-                        bondsDone.add(match) 
-                        yield (((match[0], match[1]), (i1, i2)))</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/utils.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="39" customHeight="1">
-      <c r="A30" s="2" t="n">
+    <row r="31" ht="39" customHeight="1">
+      <c r="A31" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Adversarial Attention Perturbations for Large Object Detection Transformers</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>https://github.com/zacharyyahn/AFOG</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>utils/frcnn_utils/dataset.py</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>img = sktsf.resize(img, (C, H * scale, W * scale), mode='reflect', anti_aliasing=False)</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/frcnn_utils/dataset.py</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="58.5" customHeight="1">
-      <c r="A31" s="9" t="n"/>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="4" t="inlineStr">
+    <row r="32" ht="58.5" customHeight="1">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>utils/frcnn_utils/voc_dataset.py</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>if not self.use_difficult and int(obj.find('difficult').text) == 1:
                 continue</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/frcnn_utils/voc_dataset.py</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="39" customHeight="1">
-      <c r="A32" s="9" t="n"/>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="4" t="inlineStr">
+    <row r="33" ht="39" customHeight="1">
+      <c r="A33" s="8" t="n"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>utils/dataset_utils/voc/preprocessing.py</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>image_copy = image_copy.resize((nw, nh), Image.BICUBIC)
     new_image = Image.new('RGB', size, (0, 0, 0))</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/dataset_utils/voc/preprocessing.py</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="39" customHeight="1">
-      <c r="A33" s="9" t="n"/>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="4" t="inlineStr">
+    <row r="34" ht="58.5" customHeight="1">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>extras/detr_extras/d2/detr/dataset_mapper.py</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>image, transforms = T.apply_transform_gens(self.tfm_gens, image)</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>tfm_gens.append(T.RandomFlip())
+    tfm_gens.append(T.ResizeShortestEdge(min_size, max_size, sample_style))</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/extras/detr_extras/d2/detr/dataset_mapper.py</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="58.5" customHeight="1">
-      <c r="A34" s="9" t="n"/>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Filtering</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>image, transforms = T.apply_transform_gens(self.augmentation, image)</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="58.5" customHeight="1">
+    <row r="35" ht="136.5" customHeight="1">
       <c r="A35" s="8" t="n"/>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="4" t="inlineStr">
         <is>
+          <t>models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>augmentation.extend([
+        T.ResizeScale(
+            min_scale=min_scale, max_scale=max_scale, target_height=image_size, target_width=image_size,
+        ),
+        T.FixedSizeCrop(crop_size=(image_size, image_size))
+    ])</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58.5" customHeight="1">
+      <c r="A36" s="9" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
           <t>models/detrex/detrex/data/dataset_mappers/mask_former_instance_dataset_mapper.py</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>image = F.pad(image, padding_size, value=128).contiguous()</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detrex/data/dataset_mappers/mask_former_instance_dataset_mapper.py</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="58.5" customHeight="1">
-      <c r="A36" s="2" t="n">
+    <row r="37" ht="39" customHeight="1">
+      <c r="A37" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>A First-Order Logic-Based Alternative to Reward Models in RLHF</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>https://github.com/ChunjinJiang/sgrpo</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>train/dpo_train.py</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>text = tokenizer.apply_chat_template([{'role': "user", "content": samples['prompt']}], tokenize=False, add_generation_prompt=True, enable_thinking=False)</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>text = tokenizer.apply_chat_template([{'role': "user", "content": samples['prompt']}], tokenize=False</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/dpo_train.py</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="39" customHeight="1">
-      <c r="A37" s="9" t="n"/>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="4" t="inlineStr">
+    <row r="38" ht="39" customHeight="1">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>train/dpo_train.py</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>train_dataset = train_dataset.filter(lambda sample: len(sample['chosen']) &gt; 0)</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>train_dataset = train_dataset.filter(lambda sample: sample['better_response_id'] == sample['safer_response_id']</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/dpo_train.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="39" customHeight="1">
-      <c r="A38" s="9" t="n"/>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>train/generate_fol.py</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Filtering</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>train_dataset = train_dataset.filter(lambda example: example["label"] == "faithful")</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/generate_fol.py</t>
         </is>
       </c>
     </row>
@@ -4310,101 +4316,109 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>prompt_input_ids = Tokenizer.encode(prompt_input, add_special_tokens=False)</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/sft_training.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58.5" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>A foundation model for learning genetic associations from brain imaging phenotypes</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>src/dataset_template.py</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>idps_raw = idps_raw.loc[:, ~idps_raw.columns.str.replace("(\.\d+)$", "").duplicated()]
+self.idps_filt = idps_raw.dropna(how= 'any', axis=0)</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical/blob/HEAD/src/dataset_template.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="39" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Agentmandering: A Game-Theoretic Framework for Fair Redistricting via Large Language Model Agents</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/Lihaogx/AgentMandering</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>model/agent.py</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>prompt_input = message_prompt.format(**data_point)</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/sft_training.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="58.5" customHeight="1">
-      <c r="A40" s="8" t="n"/>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>utils/LogicalEquivalence.py</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>def msplit(s):
-    for op in op_ls:
-        s = s.replace(op, ' %s ' % op)</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/utils/LogicalEquivalence.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="97.5" customHeight="1">
-      <c r="A41" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>A foundation model for learning genetic associations from brain imaging phenotypes</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/IBM/comical</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>src/dataset_template.py</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Filtering</t>
-        </is>
-      </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>idps_raw = pd.read_csv(path)
-idps_raw = idps_raw.loc[:, ~idps_raw.columns.str.replace("(\.\d+)$", "").duplicated()]
-idps_filt = idps_raw.dropna(thresh=len(idps_raw) - 1, axis=1)</t>
+          <t>messages = [{"role": "user", "content": prompt}]
+response = self.llm_client.get_completion(messages)</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/IBM/comical/blob/HEAD/src/dataset_template.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="78" customHeight="1">
+          <t>https://github.com/Lihaogx/AgentMandering/blob/HEAD/model/agent.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="156" customHeight="1">
       <c r="A42" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Agentmandering: A Game-Theoretic Framework for Fair Redistricting via Large Language Model Agents</t>
+          <t>AgentSHAP: Interpreting LLM Agent Tool Importance with Monte Carlo Shapley Value Estimation</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/Lihaogx/AgentMandering</t>
+          <t>https://github.com/GenAISHAP/TokenSHAP</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>model/agent.py</t>
+          <t>token_shap/base.py</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -4413,43 +4427,6 @@
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>prompt = self.background_info + "\n\n" + self.party_name_prompt
-messages = [{"role": "user", "content": prompt}]
-response = self.llm_client.get_completion(messages)</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/Lihaogx/AgentMandering/blob/HEAD/model/agent.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="156" customHeight="1">
-      <c r="A43" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>AgentSHAP: Interpreting LLM Agent Tool Importance with Monte Carlo Shapley Value Estimation</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/GenAISHAP/TokenSHAP</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>token_shap/base.py</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Prompting wrappers</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>data = {'model': model, 'stream': stream}
 if messages:
@@ -4460,29 +4437,56 @@
         data['images'] = [encode_image_to_base64(image_path)]</t>
         </is>
       </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/GenAISHAP/TokenSHAP/blob/HEAD/token_shap/base.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="78" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>A Granular Study of Safety Pretraining under Model Abliteration</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>src/chat.py</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>toks = tokenizer.apply_chat_template(
+            conversation=conversation, add_generation_prompt=True, return_tensors="pt"
+        )</t>
+        </is>
+      </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/GenAISHAP/TokenSHAP/blob/HEAD/token_shap/base.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="39" customHeight="1">
-      <c r="A44" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>A Granular Study of Safety Pretraining under Model Abliteration</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/shashankskagnihotri/safety_pretraining</t>
-        </is>
-      </c>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/chat.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="97.5" customHeight="1">
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>src/chat.py</t>
+          <t>src/evaluate.py</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -4492,19 +4496,23 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>toks = tokenizer.apply_chat_template(conversation=conversation, add_generation_prompt=True, return_tensors="pt")</t>
+          <t>evaluation_prompts = [
+            f"{system_prompt}\n"
+            f"### Prompt:\n{question}\n\n"
+            f"### Response:\n{response}\n\n"
+            "CLASSIFICATION: "</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/chat.py</t>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/evaluate.py</t>
         </is>
       </c>
     </row>
     <row r="45" ht="117" customHeight="1">
-      <c r="A45" s="8" t="n"/>
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="8" t="n"/>
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
       <c r="D45" s="4" t="inlineStr">
         <is>
           <t>src/evaluate.py</t>
@@ -4531,7 +4539,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="78" customHeight="1">
+    <row r="46" ht="39" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>21</v>
       </c>
@@ -4557,8 +4565,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>prompt_sys=f""" 
-    {user_prompt} is the user prompt for the LLM,your task is to check whether it has moral or other safety problems and whether it is irrelevant with machine leaarning..</t>
+          <t>response=get_completion(prompt_sys)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -4567,10 +4574,10 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="78" customHeight="1">
-      <c r="A47" s="9" t="n"/>
-      <c r="B47" s="9" t="n"/>
-      <c r="C47" s="9" t="n"/>
+    <row r="47" ht="39" customHeight="1">
+      <c r="A47" s="8" t="n"/>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
       <c r="D47" s="4" t="inlineStr">
         <is>
           <t>llm/llm1.py</t>
@@ -4583,9 +4590,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>prompt_sys=f"""You are a helpful assistant that analyze data modalities
-in multimodal Auto-Machine learning task.
-Your task is to analyze the data type of each column</t>
+          <t>response,history=get_completion(prompt_sys,prompt,history)</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -4594,7 +4599,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="78" customHeight="1">
+    <row r="48" ht="39" customHeight="1">
       <c r="A48" s="8" t="n"/>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="8" t="n"/>
@@ -4610,7 +4615,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>prompt2=f"""{model_card}is the model chosen for the task{other_text} which contains dataset of modality {unique[index]},please only give the reasons for chossing the model without any other context"""</t>
+          <t>response2[index]=get_completion(prompt2)</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -4619,164 +4624,278 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="58.5" customHeight="1">
-      <c r="A49" s="2" t="n">
+    <row r="49" ht="39" customHeight="1">
+      <c r="A49" s="8" t="n"/>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm3.py</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>response,history=get_completion(prompt_sys,prompt,history)</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm3.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="39" customHeight="1">
+      <c r="A50" s="9" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>llm/llm4.py</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>response,history=get_completion(prompt_sys,prompt,history)</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm4.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58.5" customHeight="1">
+      <c r="A51" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>AIP-TranLAC: A Transformer-Based Method Integrating LSTM and Attention Mechanism for Predicting Anti-inflammatory Peptides</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>https://github.com/Renjingyi123/AIP-TranLAC</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>train.py</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>pep = pep + 'X' * (30-len_seq)
-for aa in pep:
-    current_pep.append(aa_dict[aa])</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>for aa in pep:
+    current_pep.append(aa_dict[aa])
+pep_codes.append(torch.tensor(current_pep))</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>https://github.com/Renjingyi123/AIP-TranLAC/blob/HEAD/train.py</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="78" customHeight="1">
-      <c r="A50" s="2" t="n">
+    <row r="52" ht="78" customHeight="1">
+      <c r="A52" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>A Solver‐Aided Hierarchical Language for LLM‐Driven Systems</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>https://github.com/deGravity/aidl</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>AIDL/constraint_fitting/filter_programs.py</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>if program_errors[prog] &lt; threshold:
             counter += 1
             shutil.copyfile(os.path.join("dataset_quantized", prog), os.path.join("dataset_filtered", prog))</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>https://github.com/deGravity/aidl/blob/HEAD/AIDL/constraint_fitting/filter_programs.py</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="78" customHeight="1">
-      <c r="A51" s="8" t="n"/>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>scripts/2024.02.14.collect_designs.py</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Prompting wrappers</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>message_list.append({
-            "role": role,
-            "content": message
-        })</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/2024.02.14.collect_designs.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="39" customHeight="1">
-      <c r="A52" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>A Structured Framework for Evaluating and Enhancing LLM Robustness</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/yha9806/VULCA-EMNLP2025</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>src/preprocess.py</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>patch = image[y:y+window_size, x:x+window_size]
-patches.append(resized)</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/src/preprocess.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="39" customHeight="1">
+    <row r="53" ht="136.5" customHeight="1">
       <c r="A53" s="8" t="n"/>
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="8" t="n"/>
       <c r="D53" s="4" t="inlineStr">
         <is>
+          <t>scripts/2024.02.14.collect_designs.py</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>roles = ['user', 'assistant']
+for i, message in enumerate(messages):
+    role = roles[i%2]
+    message_list.append({
+            "role": role,
+            "content": message
+        })</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/2024.02.14.collect_designs.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="136.5" customHeight="1">
+      <c r="A54" s="8" t="n"/>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>scripts/parse_structures.py</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>roles = ['user', 'assistant']
+for i, message in enumerate(messages):
+    role = roles[i%2]
+    message_list.append({
+            "role": role,
+            "content": message
+        })</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/parse_structures.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="136.5" customHeight="1">
+      <c r="A55" s="9" t="n"/>
+      <c r="B55" s="9" t="n"/>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>scripts/specific_constraints.py</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>roles = ['user', 'assistant']
+for i, message in enumerate(messages):
+    role = roles[i%2]
+    message_list.append({
+            "role": role,
+            "content": message
+        })</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/specific_constraints.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="39" customHeight="1">
+      <c r="A56" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>A Structured Framework for Evaluating and Enhancing LLM Robustness</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
           <t>src/preprocess.py</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>patch = image[y:y+window_size, x:x+window_size]</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/src/preprocess.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="39" customHeight="1">
+      <c r="A57" s="9" t="n"/>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>src/preprocess.py</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>resized = cv2.resize(patch, (output_size, output_size))</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/src/preprocess.py</t>
         </is>
@@ -4784,48 +4903,48 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C30:C35"/>
-    <mergeCell ref="C11:C15"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="C36:C40"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="B36:B40"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B16:B20"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="A36:A40"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B30:B35"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="A16:A20"/>
-    <mergeCell ref="C16:C20"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A31:A36"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="C31:C36"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="C52:C55"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B46:B50"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A52:A55"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="A46:A50"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
@@ -4880,6 +4999,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5002,7 +5125,7 @@
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -5013,7 +5136,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>285,696</t>
+          <t>274,426</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5148,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>43,817</t>
+          <t>43,133</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5160,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>329,513</t>
+          <t>317,559</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5248,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="117" customHeight="1">
+    <row r="2" ht="58.5" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -5146,7 +5269,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>tokenization</t>
+          <t>filtering, tokenization</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -5156,8 +5279,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>self.k_RNA = [[i[j:j + 4] for j in range(len(i) - 4 + 1)] for i in fasta_seqs]; seq = ' '.join(list(seq.upper().replace("U", "T")))
-input_ids = self.tokenizer.encode(seq, add_special_tokens=True); k_RNA = [seq[j:j + 4] for j in range(len(seq) - 4 + 1)]</t>
+          <t>input_ids = self.tokenizer.encode(seq, add_special_tokens=True); seq = ' '.join(list(seq.upper().replace("U", "T"))); input_ids = tokenizer.encode(seq, add_special_tokens=True)</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -5167,7 +5289,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Data preprocessing and tokenization (k-mer splitting and transformer tokenization/embedding extraction) are implemented in data/mydataset.py and predict.py.</t>
+          <t>Code in data/mydataset.py and predict.py implements real preprocessing (normalization and tokenization/feature extraction) for RNA sequences.</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -5176,10 +5298,10 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>8387</v>
-      </c>
-    </row>
-    <row r="3" ht="78" customHeight="1">
+        <v>8465</v>
+      </c>
+    </row>
+    <row r="3" ht="117" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -5205,12 +5327,14 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>preprocess/generate_vggttoken.py, utils/demo_dataloader.py</t>
+          <t>preprocess/generate_vggttoken.py, utils/demo_dataloader.py, inference.py</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>streamvggt.inference_long_video(image_files, save_dir=save_dir, keys=keys, mode=args.mode, max_num=args.max_num); streamvggt_info = np.load(streamvggt_path, allow_pickle=True).item()</t>
+          <t>streamvggt.inference_long_video(
+                image_files,
+                save_dir=save_dir,; concatenated_tensor = torch.cat((all_aggregated_tokens[pos]), dim=1); images, img_width, img_height = load_and_preprocess_images(img_paths, mode="original")</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -5220,7 +5344,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Preprocessing code exists: a token-generation script and a dataset/collate implementation that prepares tokenized image features for the model.</t>
+          <t>Executable image preprocessing/tokenization code is present: token generation from image sequences and code that prepares aggregated token tensors for the model.</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -5229,10 +5353,10 @@
         </is>
       </c>
       <c r="K3" s="4" t="n">
-        <v>16516</v>
-      </c>
-    </row>
-    <row r="4" ht="58.5" customHeight="1">
+        <v>15996</v>
+      </c>
+    </row>
+    <row r="4" ht="136.5" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -5258,12 +5382,14 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>blue_pipeline.py</t>
+          <t>blue_pipeline.py, gpt_interface.py</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>prompt = ("You are a Unity game architecture expert. Based on the following description, generate a JSON array of GameObject blueprints.</t>
+          <t>prompt = ("You are a Unity game architecture expert. Based on the following description, generate a JSON array of GameObject blueprints.; response = self.client.chat.completions.create(
+                    model=self.model,
+                    messages=[{"role": "user", "content": prompt}],</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -5273,7 +5399,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>The repository contains executable code that constructs and sends rich prompts to an LLM (prompt assembly) prior to generation.</t>
+          <t>Prompt construction and LLM message assembly are present, so executable prompting preprocessing exists.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -5282,7 +5408,7 @@
         </is>
       </c>
       <c r="K4" s="4" t="n">
-        <v>6095</v>
+        <v>6428</v>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1">
@@ -5311,13 +5437,12 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>src/JointDataset.py, src/JointDataset.py, src/utils.py, src/utils.py</t>
+          <t>src/JointDataset.py, src/utils.py, src/utils.py</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp)); scaler = StandardScaler()
-np_array_scaled = scaler.fit_transform(np_array); drug = drug[variable_drug].fillna(drug.mean())</t>
+          <t>self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp)); drug = drug[variable_drug].fillna(drug.mean()); Essentiality = Essentiality[var_features].dropna(axis='columns')</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -5327,7 +5452,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Preprocessing/filtering code is present (data loading, selection, NA handling, and normalization), so EXISTS.</t>
+          <t>There is executable preprocessing code that filters/cleans data and normalizes expression tensors before model training.</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -5336,7 +5461,7 @@
         </is>
       </c>
       <c r="K5" s="4" t="n">
-        <v>9427</v>
+        <v>9039</v>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1">
@@ -5362,7 +5487,7 @@
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Files contain algorithmic routines for PD/ALE/DALE curves and model parameter dumps, but no code that performs tokenization, data cleaning/deduplication/normalisation, or prompt assembly as a preprocessing pipeline.</t>
+          <t>Repo contains analysis/algorithm code (PD, ALE, A2D2E curve computations and binning) and model parameter files, but no tokenization, data cleaning/deduplication/normalisation, or prompt-assembly pipelines.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -5372,7 +5497,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>The repository provides analysis/algorithm functions and parameter fixtures, not executable preprocessing (tokenization/filtering/prompting) pipelines.</t>
+          <t>The provided code implements model-analysis algorithms and percentile/binning logic as part of methods, not executable preprocessing (tokenization, filtering, or prompting) of raw data.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -5381,7 +5506,7 @@
         </is>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4785</v>
+        <v>4432</v>
       </c>
     </row>
     <row r="7" ht="195" customHeight="1">
@@ -5410,12 +5535,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py, tools/make_audio_hf_dataset.ipynb, tools/make_image_hf_dataset.ipynb, tools/data_process/data_process_revise_dataset_name.py, tools/live_bench/filter.ipynb</t>
+          <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py, tools/make_audio_hf_dataset.ipynb, tools/live_bench/filter.ipynb</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>"lexeme_splitter": nltk.tokenize.word_tokenize,; return ( (self.settings["do_punct_removal"] and lexeme in self.PUNCTUATION_CHARS) or (self.settings["do_stop_words"] and lexeme.lower() in self.stop_words); class MplugOwlTokenizer(LlamaTokenizer):</t>
+          <t>"lexeme_splitter": nltk.tokenize.word_tokenize,; return ((self.settings["do_punct_removal"] and lexeme in self.PUNCTUATION_CHARS) or (self.settings["do_stop_words"] and lexeme.lower() in self.stop_words); class MplugOwlTokenizer(LlamaTokenizer):</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -5425,7 +5550,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Executable preprocessing exists: explicit tokenization and text/image/audio dataset construction and filtering/prompt-assembly code are present.</t>
+          <t>Multiple files implement real preprocessing: text tokenizers with lexeme filtering, HF dataset builders that assemble prompts/audio entries, and dataset filtering operations.</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -5434,7 +5559,7 @@
         </is>
       </c>
       <c r="K7" s="4" t="n">
-        <v>19538</v>
+        <v>19279</v>
       </c>
     </row>
     <row r="8" ht="39" customHeight="1">
@@ -5499,7 +5624,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr"/>
     </row>
-    <row r="10" ht="234" customHeight="1">
+    <row r="10" ht="136.5" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -5525,19 +5650,12 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>scripts/prompts.py, scripts/run_llava.py, scripts/mining.py, scripts/utils.py, scripts/gen_misb.py</t>
+          <t>scripts/run_llava.py, scripts/gen_misb.py, scripts/mining.py</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>gen_meme_prompt1 = """
-You are tasked with assisting in the creation of challenging harmful memes for a specific target model.; images_tensor = process_images(
-            images,
-            image_processor,
-            model.config
-        ).to(model.device, dtype=torch.float16); if new_cat_count[cat] &lt; 5:
-                                del new_cat_count[cat]
-                                del taxonomy["meme_harmfulness"][cat]</t>
+          <t>input_ids = (\n            tokenizer_image_token(prompt, tokenizer, IMAGE_TOKEN_INDEX, return_tensors="pt")\n            .unsqueeze(0)\n            .cuda()\n        ); misb = gpt4o_generate(prompt.replace(r"{task}",data['task']), [data['image'].replace('erased','ori')]); count = Counter(tasks)\n                tasks = [item for item in count.keys() if count[item] &gt;= 2]</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -5547,7 +5665,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>There is real, executable preprocessing code: prompt templates and prompt-assembly, image processing/tokenization, and dataset filtering steps are implemented.</t>
+          <t>Executable scripts perform prompting (prompt construction and multimodal API calls), tokenization of image placeholders into input IDs, and filtering/aggregation of classification labels for dataset preprocessing.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -5556,10 +5674,10 @@
         </is>
       </c>
       <c r="K10" s="4" t="n">
-        <v>12998</v>
-      </c>
-    </row>
-    <row r="11" ht="58.5" customHeight="1">
+        <v>12665</v>
+      </c>
+    </row>
+    <row r="11" ht="97.5" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -5580,18 +5698,19 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>filtering, tokenization</t>
+          <t>filtering, prompting</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>_preprocess.py, _preprocess.py</t>
+          <t>_preprocess.py, _preprocess.py, _aligning_time.ipynb, _build_graph.ipynb, _get_weather_prediction.py</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>X.append(data[i:i+_days_x, :_input_features]); scaler_X = MinMaxScaler(feature_range=(0, 1))
-scaler_X.fit(all_train_X)</t>
+          <t>scaler_X = MinMaxScaler(feature_range=(0, 1))
+scaler_y = MinMaxScaler(feature_range=(0, 1)); X = torch.stack(xs, dim=1) # [N, 30nodes, 30days, F]
+X = X.transpose(1, 2) # [N, 30days, num_nodes, F]; all_data[reservoir].to_csv(output_path, index=False)</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -5601,7 +5720,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>create_sliding_windows constructs model-ready input windows (tokenization-like) and the script applies MinMaxScaler and time-based splits (filtering), so preprocessing exists.</t>
+          <t>Multiple files implement non-trivial data preprocessing (splitting, scaling, aggregation, graph building) and assembly of model-ready tensors, so preprocessing code exists.</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -5610,7 +5729,7 @@
         </is>
       </c>
       <c r="K11" s="4" t="n">
-        <v>20148</v>
+        <v>20843</v>
       </c>
     </row>
     <row r="12" ht="58.5" customHeight="1">
@@ -5654,7 +5773,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Code explicitly constructs prompts from raw sentences (P implies Q variants) and sends them to an LLM, which qualifies as prompting preprocessing.</t>
+          <t>The repository contains code that builds and issues prompts to an LLM (prompting), not tokenization or dataset filtering pipelines.</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -5663,10 +5782,10 @@
         </is>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3852</v>
-      </c>
-    </row>
-    <row r="13" ht="292.5" customHeight="1">
+        <v>3491</v>
+      </c>
+    </row>
+    <row r="13" ht="58.5" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -5697,18 +5816,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>prompt = {
-  "messages": [
-    {
-        "role": "system",
-        "content": [
-            {
-              "type": "text",
-              "text": "You are an AI assistant that helps people find information."
-            },; messages = [
-        {"role": "system", "content": "You are a master in traffic signal control"},
-        {"role": "user", "content": prompt[0]['content'][0]['text']},
-    ]</t>
+          <t>prompt = {\n  "messages": [; messages = [\n        {"role": "system", "content": "You are a master in traffic signal control"},</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -5718,7 +5826,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Prompt assembly code for LLM interaction is present, so executable prompting preprocessing exists in the repo.</t>
+          <t>Prompt-building code is present (chat message dict construction and assembly) so prompting preprocessing exists.</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -5727,10 +5835,10 @@
         </is>
       </c>
       <c r="K13" s="4" t="n">
-        <v>20337</v>
-      </c>
-    </row>
-    <row r="14" ht="117" customHeight="1">
+        <v>20405</v>
+      </c>
+    </row>
+    <row r="14" ht="156" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -5756,16 +5864,17 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>msformer/MSEncoder.py, msformer/MSEncoder.py, msformer/masskg.py, msformer/masskg.py, msformer/masskg.py, msformer/utils.py, msformer/utils.py</t>
+          <t>msformer/masskg.py, msformer/masskg.py, msformer/MSEncoder.py</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>self.tokenizer = MolTranBertTokenizer(vocab_file); encodings = self.tokenizer.batch_encode_plus(
+          <t>fmol = Chem.FragmentOnBonds(mol,bd) #断裂键; if not max(fw_)&gt;=50:
+                continue; encodings = self.tokenizer.batch_encode_plus(
             batch, 
             padding=True, 
             add_special_tokens=True
-        ); def get_fragments(mol,bonds_comb,adduct,mode):</t>
+        )</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -5775,7 +5884,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>The repo includes executable code that splits molecules into fragments/tokenizes them and applies simple fragment filtering, so preprocessing exists.</t>
+          <t>Non-trivial molecular tokenization (fragmentation) and fragment filtering code is present, so executable preprocessing exists.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -5784,7 +5893,7 @@
         </is>
       </c>
       <c r="K14" s="4" t="n">
-        <v>16015</v>
+        <v>16161</v>
       </c>
     </row>
     <row r="15" ht="58.5" customHeight="1">
@@ -5844,14 +5953,15 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>utils/frcnn_utils/dataset.py, utils/frcnn_utils/voc_dataset.py, utils/dataset_utils/voc/preprocessing.py, extras/detr_extras/d2/detr/dataset_mapper.py, models/detrex/detrex/data/detr_dataset_mapper.py</t>
+          <t>utils/frcnn_utils/dataset.py, utils/dataset_utils/voc/preprocessing.py, extras/detr_extras/d2/detr/dataset_mapper.py, models/detrex/detrex/data/detr_dataset_mapper.py, models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>img = sktsf.resize(img, (C, H * scale, W * scale), mode='reflect', anti_aliasing=False); if not self.use_difficult and int(obj.find('difficult').text) == 1:
-                continue; image_copy = image_copy.resize((nw, nh), Image.BICUBIC)
-    new_image = Image.new('RGB', size, (0, 0, 0))</t>
+          <t>img = sktsf.resize(img, (C, H * scale, W * scale), mode='reflect', anti_aliasing=False); image_copy = image_copy.resize((nw, nh), Image.BICUBIC)
+new_image = Image.new('RGB', size, (0, 0, 0)); tfm_gens.append(T.ResizeShortestEdge(min_size, max_size, sample_style))
+if is_train:
+    tfm_gens.append(T.RandomFlip())</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -5861,7 +5971,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Executable preprocessing code for image datasets (augmentation, resizing, padding, and filtering of annotations) is present.</t>
+          <t>Image preprocessing and augmentation pipelines are implemented (resizing, normalization, cropping, flips and transform application), so executable filtering preprocessing code exists.</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -5870,10 +5980,10 @@
         </is>
       </c>
       <c r="K16" s="4" t="n">
-        <v>21270</v>
-      </c>
-    </row>
-    <row r="17" ht="136.5" customHeight="1">
+        <v>20521</v>
+      </c>
+    </row>
+    <row r="17" ht="117" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -5899,12 +6009,12 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>train/sft_training.py, train/dpo_train.py, train/dpo_train.py, train/generate_fol.py, train/generate_fol.py, utils/LogicalEquivalence.py</t>
+          <t>train/dpo_train.py, train/dpo_train.py, train/generate_fol.py, train/generate_fol.py, train/sft_training.py, utils/LogicalEquivalence.py, utils/sgrpo_trainer.py</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>prompt_input_ids = Tokenizer.encode(prompt_input, add_special_tokens=False); text = tokenizer.apply_chat_template([{'role': "user", "content": samples['prompt']}], tokenize=False,; train_dataset = train_dataset.filter(lambda sample: sample['better_response_id'] == sample['safer_response_id'] and sample.get(f"is_response_{sample['better_response_id']}_safe", False))</t>
+          <t>train_dataset = train_dataset.filter(lambda sample: sample['better_response_id'] == sample['safer_response_id']; text = tokenizer.apply_chat_template([{'role': "user", "content": samples['prompt']}], tokenize=False,; train_dataset = train_dataset.filter(lambda example: example["label"] == "faithful")</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -5914,7 +6024,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Multiple files implement real preprocessing: dataset filtering/length checks, tokenization of text/prompts, and prompt assembly for model inputs.</t>
+          <t>Multiple scripts implement non-trivial preprocessing: filtering/deduplication of datasets, tokenization of text/FOL, and prompt assembly before model calls.</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -5923,10 +6033,10 @@
         </is>
       </c>
       <c r="K17" s="4" t="n">
-        <v>14616</v>
-      </c>
-    </row>
-    <row r="18" ht="97.5" customHeight="1">
+        <v>14430</v>
+      </c>
+    </row>
+    <row r="18" ht="175.5" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -5947,7 +6057,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>filtering, prompting, tokenization</t>
+          <t>filtering, tokenization</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -5957,7 +6067,10 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>return idp_tokenization('cpu',count,self.rnd_st,data.index,{'train':data.values.astype('float')}); idps_filt = idps_raw.dropna(thresh=len(idps_raw) - 1, axis=1) # Drop columns with all NA values on columns; 'pairs' : np.concatenate((a.to_numpy(),b.to_numpy()),axis=1)</t>
+          <t>idps_raw = idps_raw.loc[:, ~idps_raw.columns.str.replace("(\.\d+)$", "").duplicated()]
+idps_filt = idps_raw.dropna(thresh=len(idps_raw) - 1, axis=1) # Drop columns with all NA values on columns; return idp_tokenization('cpu',count,self.rnd_st,data.index,{'train':data.values.astype('float')}); print('Tokenization of modality started')
+mod_a_melted = self.mod_a.melt()
+mod_b_melted = self.mod_b.melt()</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -5967,7 +6080,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Repository includes executable preprocessing: filtering/cleaning of IDP tables, tokenization calls, and code that builds paired model inputs for training.</t>
+          <t>Data-loading code in src/dataset_template.py implements non-trivial filtering and tokenization/pair-assembly, so preprocessing code exists in the repo.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -5976,10 +6089,10 @@
         </is>
       </c>
       <c r="K18" s="4" t="n">
-        <v>21599</v>
-      </c>
-    </row>
-    <row r="19" ht="78" customHeight="1">
+        <v>21287</v>
+      </c>
+    </row>
+    <row r="19" ht="58.5" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -6011,7 +6124,6 @@
       <c r="G19" s="4" t="inlineStr">
         <is>
           <t>prompt = self.background_info + "\n\n" + self.party_name_prompt
-...
 messages = [{"role": "user", "content": prompt}]</t>
         </is>
       </c>
@@ -6022,7 +6134,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>The repository contains executable code that constructs and assembles prompts (model inputs) from scheme data for LLM agents.</t>
+          <t>The repository includes executable code that assembles and dispatches prompts to an LLM, qualifying as prompting preprocessing.</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -6031,10 +6143,10 @@
         </is>
       </c>
       <c r="K19" s="4" t="n">
-        <v>9026</v>
-      </c>
-    </row>
-    <row r="20" ht="156" customHeight="1">
+        <v>8971</v>
+      </c>
+    </row>
+    <row r="20" ht="117" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -6060,16 +6172,15 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>token_shap/base.py, token_shap/agent_shap.py</t>
+          <t>token_shap/agent_shap.py, token_shap/base.py</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>data['prompt'] = prompt
+          <t>return {"prompt": original_content, "tools": filtered_tools}; if prompt:
+        data['prompt'] = prompt
         if image_path:
-            data['images'] = [encode_image_to_base64(image_path)]; def _prepare_generate_args(self, content: Any, **kwargs) -&gt; Dict:
-        """Prepare arguments for baseline generation with ALL tools."""
-        return {"prompt": content, "tools": self.tools}</t>
+            data['images'] = [encode_image_to_base64(image_path)]</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -6079,7 +6190,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Files implement prompt assembly (building request payloads and prepare prompt+tools arguments), which qualifies as preprocessing under prompting.</t>
+          <t>AgentSHAP/base utilities construct request payloads (prompt, tools, images), which qualifies as prompting preprocessing code.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -6088,10 +6199,10 @@
         </is>
       </c>
       <c r="K20" s="4" t="n">
-        <v>12539</v>
-      </c>
-    </row>
-    <row r="21" ht="234" customHeight="1">
+        <v>12333</v>
+      </c>
+    </row>
+    <row r="21" ht="312" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -6122,8 +6233,13 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>system_prompt = """
-        You are an AI system whose sole task is to classify whether another model’s response constitutes a refusal or non-refusal.; inputs = tokenizer.batch_encode_plus(
+          <t>evaluation_prompts = [
+            f"{system_prompt}\n"
+            f"### Prompt:\n{question}\n\n"
+            f"### Response:\n{response}\n\n"
+            "CLASSIFICATION: "
+            for question, response in zip(batch_questions, batch_responses)
+        ]; inputs = tokenizer.batch_encode_plus(
             evaluation_prompts,
             return_tensors="pt",
             padding=True,
@@ -6140,7 +6256,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>The code assembles evaluation/chat prompts and calls tokenizer.batch_encode_plus/apply_chat_template, so executable prompt-building and tokenization preprocessing is present.</t>
+          <t>There is executable code that builds evaluation/chat prompts and tokenizes them before passing to models.</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -6149,7 +6265,7 @@
         </is>
       </c>
       <c r="K21" s="4" t="n">
-        <v>9474</v>
+        <v>9330</v>
       </c>
     </row>
     <row r="22" ht="175.5" customHeight="1">
@@ -6173,21 +6289,20 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>prompting</t>
+          <t>filtering, prompting</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>llm/filter.py, llm/llm1.py, llm/llm3.py</t>
+          <t>llm/filter.py, llm/filter.py, llm/llm1.py, llm/llm3.py</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
           <t>prompt_sys=f""" 
-    {user_prompt} is the user prompt for the LLM,your task is to check whether it has moral or other safety problems; prompt_sys=f"""You are a helpful assistant that analyze data modalities
-in multimodal Auto-Machine learning task.; prompt_sys=f"""You are a helpful assistant that writes data processors
-        code to load different types of data for multimodal
-        Auto-Machine learning task.</t>
+    {user_prompt} is the user prompt for the LLM,your task is to check whether it has moral or other safety problems; prompt_sys=f""" 
+    {stage_response} is the stage response of the LLM, your task is to check whether it has moral or other safety problems.; prompt_sys=f"""You are a helpful assistant that analyze data modalities
+in multimodal Auto-Machine learning task.</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -6197,7 +6312,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>The repository contains executable code that builds and issues prompts to LLMs to generate preprocessing/data-processor code, so prompting preprocessing exists.</t>
+          <t>Several files build detailed prompt templates (prompting) and include an LLM-based content filter (filtering), so executable prompting/filtering pipelines exist.</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -6206,10 +6321,10 @@
         </is>
       </c>
       <c r="K22" s="4" t="n">
-        <v>9748</v>
-      </c>
-    </row>
-    <row r="23" ht="78" customHeight="1">
+        <v>10023</v>
+      </c>
+    </row>
+    <row r="23" ht="58.5" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -6242,8 +6357,7 @@
         <is>
           <t>pep = pep + 'X' * (30-len_seq)
 for aa in pep:
-    current_pep.append(aa_dict[aa])
-data = rnn_utils.pad_sequence(pep_codes, batch_first=True)</t>
+    current_pep.append(aa_dict[aa])</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -6253,7 +6367,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Repository includes executable preprocessing that tokenizes and pads peptide sequences into model-ready integer tensors.</t>
+          <t>The repository includes code that tokenizes peptide sequences (AA-&gt;ids) and pads them into model-ready tensors, so preprocessing exists.</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -6262,7 +6376,7 @@
         </is>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4422</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="24" ht="39" customHeight="1">
@@ -6327,7 +6441,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr"/>
     </row>
-    <row r="26" ht="117" customHeight="1">
+    <row r="26" ht="175.5" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -6358,7 +6472,12 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>shutil.copyfile(os.path.join("dataset_quantized", prog), os.path.join("dataset_filtered", prog)); "role": "system",; response = client.chat.completions.create(</t>
+          <t>if program_errors[prog] &lt; threshold:
+            shutil.copyfile(os.path.join("dataset_quantized", prog), os.path.join("dataset_filtered", prog)); response = client.chat.completions.create(
+                model="gpt-4-turbo-preview",
+                messages=message_list,; response = client.chat.completions.create(
+                model="gpt-4-turbo-preview",
+                messages=message_list,</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -6368,7 +6487,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>There is real filtering code for datasets and prompt-assembly functions that interact with an LLM, so preprocessing/pipeline code exists.</t>
+          <t>There is real prompting code that builds message lists and calls the chat API plus a dataset filtering script that copies selected files, so preprocessing exists.</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -6377,7 +6496,7 @@
         </is>
       </c>
       <c r="K26" s="4" t="n">
-        <v>18034</v>
+        <v>17605</v>
       </c>
     </row>
     <row r="27" ht="195" customHeight="1">
@@ -6406,14 +6525,13 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>src/preprocess.py, scripts/analyze-exhibition-data.py</t>
+          <t>src/preprocess.py, scripts/analyze-exhibition-data.py, scripts/analyze-ppt-artworks.js, scripts/add-artwork2-refs.js</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>resized = cv2.resize(patch, (output_size, output_size))
-                patches.append(resized); patterns = [
-        r'([^《]+)《([^》]+)》',  # 基本模式</t>
+          <t>patch = image[y:y+window_size, x:x+window_size]
+resized = cv2.resize(patch, (output_size, output_size)); patterns = [ r'([^《]+)《([^》]+)》', r'([^《]+)、([^《]+)《([^》]+)》', r'([^《]+)、([^《]+)、([^《]+)《([^》]+)》' ]; const artworkTitlePattern = /^[\\u4e00-\\u9fa5a-zA-Z\\s]+《.+》/;</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -6423,7 +6541,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Image patch extraction (tokenization) and dataset structuring/normalization (filtering) code are present and executable.</t>
+          <t>Executable image patching (sliding-window) and multiple data-filtering/normalization scripts are present, so preprocessing code exists.</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -6432,7 +6550,7 @@
         </is>
       </c>
       <c r="K27" s="4" t="n">
-        <v>23027</v>
+        <v>24165</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -6583,7 +6701,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>self.k_RNA = [[i[j:j + 4] for j in range(len(i) - 4 + 1)] for i in fasta_seqs]</t>
+          <t>input_ids = self.tokenizer.encode(seq, add_special_tokens=True)</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -6592,10 +6710,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58.5" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
+    <row r="3" ht="39" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>data/mydataset.py</t>
@@ -6603,73 +6721,71 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>seq = ' '.join(list(seq.upper().replace("U", "T")))</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/CSUBioGroup/2OMe-LM/blob/HEAD/data/mydataset.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>predict.py</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>seq = ' '.join(list(seq.upper().replace("U", "T")))
-input_ids = self.tokenizer.encode(seq, add_special_tokens=True)</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/CSUBioGroup/2OMe-LM/blob/HEAD/data/mydataset.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>input_ids = tokenizer.encode(seq, add_special_tokens=True)</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/CSUBioGroup/2OMe-LM/blob/HEAD/predict.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>predict.py</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>k_RNA = [seq[j:j + 4] for j in range(len(seq) - 4 + 1)]</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>seq = ' '.join(list(seq.upper().replace("U", "T")))</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>https://github.com/CSUBioGroup/2OMe-LM/blob/HEAD/predict.py</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="39" customHeight="1">
-      <c r="A5" s="8" t="n"/>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>predict.py</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>seq = ' '.join(list(seq.upper().replace("U", "T")))
-input_ids = tokenizer.encode(seq, add_special_tokens=True)</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/CSUBioGroup/2OMe-LM/blob/HEAD/predict.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="39" customHeight="1">
+    <row r="6" ht="58.5" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>2</v>
       </c>
@@ -6695,7 +6811,9 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>streamvggt.inference_long_video(image_files, save_dir=save_dir, keys=keys, mode=args.mode, max_num=args.max_num)</t>
+          <t>streamvggt.inference_long_video(
+                image_files,
+                save_dir=save_dir,</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -6720,7 +6838,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>streamvggt_info = np.load(streamvggt_path, allow_pickle=True).item()</t>
+          <t>concatenated_tensor = torch.cat((all_aggregated_tokens[pos]), dim=1)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -6729,128 +6847,129 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="58.5" customHeight="1">
-      <c r="A8" s="2" t="n">
+    <row r="8" ht="39" customHeight="1">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>inference.py</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>images, img_width, img_height = load_and_preprocess_images(img_paths, mode="original")</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/inference.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58.5" customHeight="1">
+      <c r="A9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>90% Faster, 100% Code-Free: MLLM-Driven Zero-Code 3D Game Development</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>https://github.com/yxwan123/UniGen</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>blue_pipeline.py</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>prompt = ("You are a Unity game architecture expert. Based on the following description, generate a JSON array of GameObject blueprints.</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>https://github.com/yxwan123/UniGen/blob/HEAD/blue_pipeline.py</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="39" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Abstract A024: DeepVul: A multi-task transformer model for joint prediction of gene essentiality and drug response</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/alaaj27/DeepVul.git</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>src/JointDataset.py</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Filtering</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp))</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/JointDataset.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="39" customHeight="1">
+    <row r="10" ht="78" customHeight="1">
       <c r="A10" s="9" t="n"/>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="4" t="inlineStr">
         <is>
+          <t>gpt_interface.py</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>response = self.client.chat.completions.create(
+                    model=self.model,
+                    messages=[{"role": "user", "content": prompt}],</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yxwan123/UniGen/blob/HEAD/gpt_interface.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="39" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Abstract A024: DeepVul: A multi-task transformer model for joint prediction of gene essentiality and drug response</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/alaaj27/DeepVul.git</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
           <t>src/JointDataset.py</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>scaler = StandardScaler()
-np_array_scaled = scaler.fit_transform(np_array)</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp))</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/JointDataset.py</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="9" t="n"/>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>src/utils.py</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Filtering</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>drug = drug[variable_drug].fillna(drug.mean())</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/utils.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="97.5" customHeight="1">
+    <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="n"/>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -6866,9 +6985,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>with open("../data/top1000_variable_genes.txt", 'r') as file:
-    var_features = file.read().splitlines()
-    Essentiality = Essentiality[var_features].dropna(axis='columns')</t>
+          <t>drug = drug[variable_drug].fillna(drug.mean())</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -6877,138 +6994,138 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58.5" customHeight="1">
-      <c r="A13" s="2" t="n">
+    <row r="13" ht="39" customHeight="1">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>src/utils.py</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Essentiality = Essentiality[var_features].dropna(axis='columns')</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/utils.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58.5" customHeight="1">
+      <c r="A14" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>AccidentBench: Benchmarking Multimodal Understanding and Reasoning in Vehicle Accidents and Beyond</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>https://github.com/SafeRL-Lab/AccidentBench</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>"lexeme_splitter": nltk.tokenize.word_tokenize,</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="58.5" customHeight="1">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="4" t="inlineStr">
+    <row r="15" ht="58.5" customHeight="1">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>return ( (self.settings["do_punct_removal"] and lexeme in self.PUNCTUATION_CHARS) or (self.settings["do_stop_words"] and lexeme.lower() in self.stop_words)</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>return ((self.settings["do_punct_removal"] and lexeme in self.PUNCTUATION_CHARS) or (self.settings["do_stop_words"] and lexeme.lower() in self.stop_words)</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="39" customHeight="1">
-      <c r="A15" s="9" t="n"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="4" t="inlineStr">
+    <row r="16" ht="39" customHeight="1">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>class MplugOwlTokenizer(LlamaTokenizer):</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="39" customHeight="1">
-      <c r="A16" s="9" t="n"/>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="4" t="inlineStr">
+    <row r="17" ht="39" customHeight="1">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>tools/make_audio_hf_dataset.ipynb</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>prompt_list.append("&lt;|audio_bos|&gt;&lt;|AUDIO|&gt;&lt;|audio_eos|&gt;" + json_data['prompt'])</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/make_audio_hf_dataset.ipynb</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39" customHeight="1">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>tools/make_image_hf_dataset.ipynb</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>q["image"] = Image.open(image_path)</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/make_image_hf_dataset.ipynb</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7135,7 @@
       <c r="C18" s="9" t="n"/>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>tools/data_process/data_process_revise_dataset_name.py</t>
+          <t>tools/live_bench/filter.ipynb</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -7028,57 +7145,57 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>os.rename(full_path, new_full_path)</t>
+          <t>filtered_data = data["test"].filter(lambda example: example["score"] and example["score"] &gt; 5)</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/data_process/data_process_revise_dataset_name.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="39" customHeight="1">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/live_bench/filter.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58.5" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>AdamMeme: Adaptively Probe the Reasoning Capacity of Multimodal Large Language Models on Harmfulness</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/Lbotirx/AdamMeme</t>
+        </is>
+      </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>tools/live_bench/filter.ipynb</t>
+          <t>scripts/run_llava.py</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Filtering</t>
+          <t>Tokenization</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>filtered_data = data["test"].filter(lambda example: example["score"] and example["score"] &gt; 5)</t>
+          <t>input_ids = (\n            tokenizer_image_token(prompt, tokenizer, IMAGE_TOKEN_INDEX, return_tensors="pt")\n            .unsqueeze(0)\n            .cuda()\n        )</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/live_bench/filter.ipynb</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58.5" customHeight="1">
-      <c r="A20" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>AdamMeme: Adaptively Probe the Reasoning Capacity of Multimodal Large Language Models on Harmfulness</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/Lbotirx/AdamMeme</t>
-        </is>
-      </c>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/run_llava.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="39" customHeight="1">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>scripts/prompts.py</t>
+          <t>scripts/gen_misb.py</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -7088,52 +7205,57 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>gen_meme_prompt1 = """
-You are tasked with assisting in the creation of challenging harmful memes for a specific target model.</t>
+          <t>misb = gpt4o_generate(prompt.replace(r"{task}",data['task']), [data['image'].replace('erased','ori')])</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/prompts.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="97.5" customHeight="1">
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/gen_misb.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="39" customHeight="1">
       <c r="A21" s="9" t="n"/>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="9" t="n"/>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>scripts/run_llava.py</t>
+          <t>scripts/mining.py</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Tokenization</t>
+          <t>Filtering</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>images_tensor = process_images(
-            images,
-            image_processor,
-            model.config
-        ).to(model.device, dtype=torch.float16)</t>
+          <t>count = Counter(tasks)\n                tasks = [item for item in count.keys() if count[item] &gt;= 2]</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/run_llava.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="78" customHeight="1">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
+          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/mining.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="39" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Adaptive Graph Learning with Transformer for Multi-Reservoir Inflow Prediction</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/humphreyhuu/AdaTrip</t>
+        </is>
+      </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>scripts/mining.py</t>
+          <t>_preprocess.py</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -7143,24 +7265,23 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>if new_cat_count[cat] &lt; 5:
-                                del new_cat_count[cat]
-                                del taxonomy["meme_harmfulness"][cat]</t>
+          <t>scaler_X = MinMaxScaler(feature_range=(0, 1))
+scaler_y = MinMaxScaler(feature_range=(0, 1))</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/mining.py</t>
+          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_preprocess.py</t>
         </is>
       </c>
     </row>
     <row r="23" ht="39" customHeight="1">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>scripts/utils.py</t>
+          <t>_preprocess.py</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -7170,12 +7291,13 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>content.append({"type": "image_url", "image_url": {"url": f"data:image/png;base64,{base64_image}"}})</t>
+          <t>X = torch.stack(xs, dim=1) # [N, 30nodes, 30days, F]
+X = X.transpose(1, 2) # [N, 30days, num_nodes, F]</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/utils.py</t>
+          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_preprocess.py</t>
         </is>
       </c>
     </row>
@@ -7185,67 +7307,59 @@
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>scripts/gen_misb.py</t>
+          <t>_aligning_time.ipynb</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Prompting wrappers</t>
+          <t>Filtering</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>misb = gpt4o_generate(prompt.replace(r"{task}",data['task']), [data['image'].replace('erased','ori')])</t>
+          <t>all_data[reservoir].to_csv(output_path, index=False)</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/Lbotirx/AdamMeme/blob/HEAD/scripts/gen_misb.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="39" customHeight="1">
-      <c r="A25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Adaptive Graph Learning with Transformer for Multi-Reservoir Inflow Prediction</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/humphreyhuu/AdaTrip</t>
-        </is>
-      </c>
+          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_aligning_time.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="78" customHeight="1">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>_preprocess.py</t>
+          <t>_build_graph.ipynb</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Tokenization</t>
+          <t>Filtering</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>X.append(data[i:i+_days_x, :_input_features])</t>
+          <t>A = np.zeros((n, n), dtype=int)  # Initialize adjacency matrix
+for j in selected_neighbors:
+    A[i, j] = 1</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_preprocess.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="39" customHeight="1">
-      <c r="A26" s="8" t="n"/>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
+          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_build_graph.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="97.5" customHeight="1">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>_preprocess.py</t>
+          <t>_get_weather_prediction.py</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -7255,13 +7369,15 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>scaler_X = MinMaxScaler(feature_range=(0, 1))
-scaler_X.fit(all_train_X)</t>
+          <t>daily_data = df.groupby(['reservoir', 'year', 'day_of_year']).agg({
+    'temperature': 'mean',
+    'precipitation': 'mean'
+}).reset_index()</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_preprocess.py</t>
+          <t>https://github.com/humphreyhuu/AdaTrip/blob/HEAD/_get_weather_prediction.py</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7416,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="195" customHeight="1">
+    <row r="28" ht="39" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>12</v>
       </c>
@@ -7326,15 +7442,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>prompt = {
-  "messages": [
-    {
-        "role": "system",
-        "content": [
-            {
-              "type": "text",
-              "text": "You are an AI assistant that helps people find information."
-            },</t>
+          <t>prompt = {\n  "messages": [</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -7343,10 +7451,10 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="117" customHeight="1">
-      <c r="A29" s="8" t="n"/>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
+    <row r="29" ht="39" customHeight="1">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
       <c r="D29" s="4" t="inlineStr">
         <is>
           <t>a_test_online_model/Llama_inference.py</t>
@@ -7359,10 +7467,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>messages = [
-        {"role": "system", "content": "You are a master in traffic signal control"},
-        {"role": "user", "content": prompt[0]['content'][0]['text']},
-    ]</t>
+          <t>messages = [\n        {"role": "system", "content": "You are a master in traffic signal control"},</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -7387,40 +7492,66 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
+          <t>msformer/masskg.py</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>fmol = Chem.FragmentOnBonds(mol,bd) #断裂键</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/masskg.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="39" customHeight="1">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>msformer/masskg.py</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>if not max(fw_)&gt;=50:
+                continue</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/masskg.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="97.5" customHeight="1">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
           <t>msformer/MSEncoder.py</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>self.tokenizer = MolTranBertTokenizer(vocab_file)</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/MSEncoder.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="97.5" customHeight="1">
-      <c r="A31" s="9" t="n"/>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>msformer/MSEncoder.py</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>encodings = self.tokenizer.batch_encode_plus(
             batch, 
@@ -7429,70 +7560,54 @@
         )</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/MSEncoder.py</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="39" customHeight="1">
-      <c r="A32" s="9" t="n"/>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>msformer/masskg.py</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>def get_fragments(mol,bonds_comb,adduct,mode):</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/masskg.py</t>
-        </is>
-      </c>
-    </row>
     <row r="33" ht="39" customHeight="1">
-      <c r="A33" s="9" t="n"/>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
+      <c r="A33" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Adversarial Attention Perturbations for Large Object Detection Transformers</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG</t>
+        </is>
+      </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>msformer/masskg.py</t>
+          <t>utils/frcnn_utils/dataset.py</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Tokenization</t>
+          <t>Filtering</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>fmol = Chem.FragmentOnBonds(mol,bd)
-        frag_mols = Chem.GetMolFrags(fmol,asMols=True)</t>
+          <t>img = sktsf.resize(img, (C, H * scale, W * scale), mode='reflect', anti_aliasing=False)</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/masskg.py</t>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/frcnn_utils/dataset.py</t>
         </is>
       </c>
     </row>
     <row r="34" ht="39" customHeight="1">
-      <c r="A34" s="9" t="n"/>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="9" t="n"/>
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>msformer/masskg.py</t>
+          <t>utils/dataset_utils/voc/preprocessing.py</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -7502,84 +7617,76 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>if not max(fw_)&gt;=50:
-                continue</t>
+          <t>image_copy = image_copy.resize((nw, nh), Image.BICUBIC)
+new_image = Image.new('RGB', size, (0, 0, 0))</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/masskg.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="39" customHeight="1">
-      <c r="A35" s="9" t="n"/>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/dataset_utils/voc/preprocessing.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="78" customHeight="1">
+      <c r="A35" s="8" t="n"/>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>msformer/utils.py</t>
+          <t>extras/detr_extras/d2/detr/dataset_mapper.py</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Tokenization</t>
+          <t>Filtering</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>def searchBonds(mol,maxSR=8):</t>
+          <t>tfm_gens.append(T.ResizeShortestEdge(min_size, max_size, sample_style))
+if is_train:
+    tfm_gens.append(T.RandomFlip())</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/utils.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="39" customHeight="1">
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/extras/detr_extras/d2/detr/dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58.5" customHeight="1">
       <c r="A36" s="8" t="n"/>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>msformer/utils.py</t>
+          <t>models/detrex/detrex/data/detr_dataset_mapper.py</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Tokenization</t>
+          <t>Filtering</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>matches = mol.GetSubstructMatches(patt)
-            for match in matches:</t>
+          <t>image, transforms = T.apply_transform_gens(self.augmentation, image)
+image_shape = image.shape[:2]</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/utils.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="39" customHeight="1">
-      <c r="A37" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Adversarial Attention Perturbations for Large Object Detection Transformers</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/zacharyyahn/AFOG</t>
-        </is>
-      </c>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detrex/data/detr_dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="78" customHeight="1">
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>utils/frcnn_utils/dataset.py</t>
+          <t>models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -7589,22 +7696,32 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>img = sktsf.resize(img, (C, H * scale, W * scale), mode='reflect', anti_aliasing=False)</t>
+          <t>augmentation.extend([T.ResizeScale(min_scale=min_scale, max_scale=max_scale, target_height=image_size, target_width=image_size), T.FixedSizeCrop(crop_size=(image_size, image_size))])</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/frcnn_utils/dataset.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="58.5" customHeight="1">
-      <c r="A38" s="9" t="n"/>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="9" t="n"/>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detrex/data/dataset_mappers/coco_instance_new_baseline_dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="39" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>A First-Order Logic-Based Alternative to Reward Models in RLHF</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo</t>
+        </is>
+      </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>utils/frcnn_utils/voc_dataset.py</t>
+          <t>train/dpo_train.py</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -7614,64 +7731,62 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>if not self.use_difficult and int(obj.find('difficult').text) == 1:
-                continue</t>
+          <t>train_dataset = train_dataset.filter(lambda sample: sample['better_response_id'] == sample['safer_response_id']</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/frcnn_utils/voc_dataset.py</t>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/dpo_train.py</t>
         </is>
       </c>
     </row>
     <row r="39" ht="39" customHeight="1">
-      <c r="A39" s="9" t="n"/>
-      <c r="B39" s="9" t="n"/>
-      <c r="C39" s="9" t="n"/>
+      <c r="A39" s="8" t="n"/>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>utils/dataset_utils/voc/preprocessing.py</t>
+          <t>train/dpo_train.py</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>text = tokenizer.apply_chat_template([{'role': "user", "content": samples['prompt']}], tokenize=False,</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/dpo_train.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="39" customHeight="1">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>train/generate_fol.py</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>image_copy = image_copy.resize((nw, nh), Image.BICUBIC)
-    new_image = Image.new('RGB', size, (0, 0, 0))</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/dataset_utils/voc/preprocessing.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="39" customHeight="1">
-      <c r="A40" s="9" t="n"/>
-      <c r="B40" s="9" t="n"/>
-      <c r="C40" s="9" t="n"/>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>extras/detr_extras/d2/detr/dataset_mapper.py</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Filtering</t>
-        </is>
-      </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>image, transforms = T.apply_transform_gens(self.tfm_gens, image)</t>
+          <t>train_dataset = train_dataset.filter(lambda example: example["label"] == "faithful")</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/extras/detr_extras/d2/detr/dataset_mapper.py</t>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/generate_fol.py</t>
         </is>
       </c>
     </row>
@@ -7681,39 +7796,29 @@
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>models/detrex/detrex/data/detr_dataset_mapper.py</t>
+          <t>train/generate_fol.py</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Filtering</t>
+          <t>Prompting wrappers</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>image, transforms = T.apply_transform_gens(self.augmentation, image)</t>
+          <t>train_dataset = train_dataset.map(lambda samples: {"prompt": message_prompt.format(**samples)})</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detrex/data/detr_dataset_mapper.py</t>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/generate_fol.py</t>
         </is>
       </c>
     </row>
     <row r="42" ht="39" customHeight="1">
-      <c r="A42" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>A First-Order Logic-Based Alternative to Reward Models in RLHF</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/ChunjinJiang/sgrpo</t>
-        </is>
-      </c>
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
       <c r="D42" s="4" t="inlineStr">
         <is>
           <t>train/sft_training.py</t>
@@ -7736,112 +7841,124 @@
       </c>
     </row>
     <row r="43" ht="39" customHeight="1">
-      <c r="A43" s="9" t="n"/>
-      <c r="B43" s="9" t="n"/>
-      <c r="C43" s="9" t="n"/>
+      <c r="A43" s="8" t="n"/>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>train/dpo_train.py</t>
+          <t>utils/LogicalEquivalence.py</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Prompting wrappers</t>
+          <t>Tokenization</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>text = tokenizer.apply_chat_template([{'role': "user", "content": samples['prompt']}], tokenize=False,</t>
+          <t>for op in op_ls:
+        s = s.replace(op, ' %s ' % op)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/dpo_train.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="78" customHeight="1">
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/utils/LogicalEquivalence.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="39" customHeight="1">
       <c r="A44" s="9" t="n"/>
       <c r="B44" s="9" t="n"/>
       <c r="C44" s="9" t="n"/>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>train/dpo_train.py</t>
+          <t>utils/sgrpo_trainer.py</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>prompt_inputs = self.processing_class(text=prompts_text, return_tensors="pt", padding=True, padding_side="left",</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/utils/sgrpo_trainer.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="78" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>A foundation model for learning genetic associations from brain imaging phenotypes</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>src/dataset_template.py</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>train_dataset = train_dataset.filter(lambda sample: sample['better_response_id'] == sample['safer_response_id'] and sample.get(f"is_response_{sample['better_response_id']}_safe", False))</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/dpo_train.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="39" customHeight="1">
-      <c r="A45" s="9" t="n"/>
-      <c r="B45" s="9" t="n"/>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>train/generate_fol.py</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>idps_raw = idps_raw.loc[:, ~idps_raw.columns.str.replace("(\.\d+)$", "").duplicated()]
+idps_filt = idps_raw.dropna(thresh=len(idps_raw) - 1, axis=1) # Drop columns with all NA values on columns</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical/blob/HEAD/src/dataset_template.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="39" customHeight="1">
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>src/dataset_template.py</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>inputs = tokenizer(prompts, return_tensors="pt", padding=True, padding_side="left").to(device)</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/generate_fol.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="39" customHeight="1">
-      <c r="A46" s="9" t="n"/>
-      <c r="B46" s="9" t="n"/>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>train/generate_fol.py</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>Filtering</t>
-        </is>
-      </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>train_dataset = train_dataset.filter(filter_long_examples)</t>
+          <t>return idp_tokenization('cpu',count,self.rnd_st,data.index,{'train':data.values.astype('float')})</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/generate_fol.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="39" customHeight="1">
-      <c r="A47" s="8" t="n"/>
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
+          <t>https://github.com/IBM/comical/blob/HEAD/src/dataset_template.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58.5" customHeight="1">
+      <c r="A47" s="9" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>utils/LogicalEquivalence.py</t>
+          <t>src/dataset_template.py</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -7851,82 +7968,95 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>for op in op_ls: s = s.replace(op, ' %s ' % op)</t>
+          <t>print('Tokenization of modality started')
+mod_a_melted = self.mod_a.melt()
+mod_b_melted = self.mod_b.melt()</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/utils/LogicalEquivalence.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="39" customHeight="1">
+          <t>https://github.com/IBM/comical/blob/HEAD/src/dataset_template.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58.5" customHeight="1">
       <c r="A48" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>A foundation model for learning genetic associations from brain imaging phenotypes</t>
+          <t>Agentmandering: A Game-Theoretic Framework for Fair Redistricting via Large Language Model Agents</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/IBM/comical</t>
+          <t>https://github.com/Lihaogx/AgentMandering</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>src/dataset_template.py</t>
+          <t>model/agent.py</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Tokenization</t>
+          <t>Prompting wrappers</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>return idp_tokenization('cpu',count,self.rnd_st,data.index,{'train':data.values.astype('float')})</t>
+          <t>prompt = self.background_info + "\n\n" + self.party_name_prompt
+messages = [{"role": "user", "content": prompt}]</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/IBM/comical/blob/HEAD/src/dataset_template.py</t>
+          <t>https://github.com/Lihaogx/AgentMandering/blob/HEAD/model/agent.py</t>
         </is>
       </c>
     </row>
     <row r="49" ht="39" customHeight="1">
-      <c r="A49" s="9" t="n"/>
-      <c r="B49" s="9" t="n"/>
-      <c r="C49" s="9" t="n"/>
+      <c r="A49" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>AgentSHAP: Interpreting LLM Agent Tool Importance with Monte Carlo Shapley Value Estimation</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/GenAISHAP/TokenSHAP</t>
+        </is>
+      </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>src/dataset_template.py</t>
+          <t>token_shap/agent_shap.py</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Filtering</t>
+          <t>Prompting wrappers</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>idps_filt = idps_raw.dropna(thresh=len(idps_raw) - 1, axis=1) # Drop columns with all NA values on columns</t>
+          <t>return {"prompt": original_content, "tools": filtered_tools}</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/IBM/comical/blob/HEAD/src/dataset_template.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="39" customHeight="1">
-      <c r="A50" s="8" t="n"/>
-      <c r="B50" s="8" t="n"/>
-      <c r="C50" s="8" t="n"/>
+          <t>https://github.com/GenAISHAP/TokenSHAP/blob/HEAD/token_shap/agent_shap.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="97.5" customHeight="1">
+      <c r="A50" s="9" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>src/dataset_template.py</t>
+          <t>token_shap/base.py</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -7936,167 +8066,74 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>'pairs' : np.concatenate((a.to_numpy(),b.to_numpy()),axis=1)</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/IBM/comical/blob/HEAD/src/dataset_template.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="78" customHeight="1">
-      <c r="A51" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>Agentmandering: A Game-Theoretic Framework for Fair Redistricting via Large Language Model Agents</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/Lihaogx/AgentMandering</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>model/agent.py</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Prompting wrappers</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>prompt = self.background_info + "\n\n" + self.party_name_prompt
-...
-messages = [{"role": "user", "content": prompt}]</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/Lihaogx/AgentMandering/blob/HEAD/model/agent.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="78" customHeight="1">
-      <c r="A52" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>AgentSHAP: Interpreting LLM Agent Tool Importance with Monte Carlo Shapley Value Estimation</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/GenAISHAP/TokenSHAP</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>token_shap/base.py</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Prompting wrappers</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>data['prompt'] = prompt
+          <t>if prompt:
+        data['prompt'] = prompt
         if image_path:
             data['images'] = [encode_image_to_base64(image_path)]</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>https://github.com/GenAISHAP/TokenSHAP/blob/HEAD/token_shap/base.py</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="97.5" customHeight="1">
-      <c r="A53" s="8" t="n"/>
-      <c r="B53" s="8" t="n"/>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>token_shap/agent_shap.py</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
+    <row r="51" ht="156" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>A Granular Study of Safety Pretraining under Model Abliteration</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>src/evaluate.py</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>def _prepare_generate_args(self, content: Any, **kwargs) -&gt; Dict:
-        """Prepare arguments for baseline generation with ALL tools."""
-        return {"prompt": content, "tools": self.tools}</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/GenAISHAP/TokenSHAP/blob/HEAD/token_shap/agent_shap.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="78" customHeight="1">
-      <c r="A54" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>A Granular Study of Safety Pretraining under Model Abliteration</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/shashankskagnihotri/safety_pretraining</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>evaluation_prompts = [
+            f"{system_prompt}\n"
+            f"### Prompt:\n{question}\n\n"
+            f"### Response:\n{response}\n\n"
+            "CLASSIFICATION: "
+            for question, response in zip(batch_questions, batch_responses)
+        ]</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/evaluate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="117" customHeight="1">
+      <c r="A52" s="8" t="n"/>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>src/evaluate.py</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Prompting wrappers</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>system_prompt = """
-        You are an AI system whose sole task is to classify whether another model’s response constitutes a refusal or non-refusal.</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/evaluate.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="117" customHeight="1">
-      <c r="A55" s="9" t="n"/>
-      <c r="B55" s="9" t="n"/>
-      <c r="C55" s="9" t="n"/>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>src/evaluate.py</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>inputs = tokenizer.batch_encode_plus(
             evaluation_prompts,
@@ -8106,19 +8143,108 @@
         ).to(device)</t>
         </is>
       </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/evaluate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="78" customHeight="1">
+      <c r="A53" s="9" t="n"/>
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>src/chat.py</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>toks = tokenizer.apply_chat_template(
+            conversation=conversation, add_generation_prompt=True, return_tensors="pt"
+        )</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/chat.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="58.5" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>prompt_sys=f""" 
+    {user_prompt} is the user prompt for the LLM,your task is to check whether it has moral or other safety problems</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/filter.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="78" customHeight="1">
+      <c r="A55" s="8" t="n"/>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>llm/filter.py</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>prompt_sys=f""" 
+    {stage_response} is the stage response of the LLM, your task is to check whether it has moral or other safety problems.</t>
+        </is>
+      </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/evaluate.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="78" customHeight="1">
+          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/filter.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="58.5" customHeight="1">
       <c r="A56" s="8" t="n"/>
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>src/chat.py</t>
+          <t>llm/llm1.py</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -8127,202 +8253,204 @@
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>toks = tokenizer.apply_chat_template(
-            conversation=conversation, add_generation_prompt=True, return_tensors="pt"
-        )</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/chat.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="58.5" customHeight="1">
-      <c r="A57" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/richarf22/UniAutoML</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>llm/filter.py</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Prompting wrappers</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>prompt_sys=f""" 
-    {user_prompt} is the user prompt for the LLM,your task is to check whether it has moral or other safety problems</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/filter.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="58.5" customHeight="1">
-      <c r="A58" s="9" t="n"/>
-      <c r="B58" s="9" t="n"/>
-      <c r="C58" s="9" t="n"/>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>llm/llm1.py</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>Prompting wrappers</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>prompt_sys=f"""You are a helpful assistant that analyze data modalities
 in multimodal Auto-Machine learning task.</t>
         </is>
       </c>
-      <c r="G58" s="7" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm1.py</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="78" customHeight="1">
-      <c r="A59" s="8" t="n"/>
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="4" t="inlineStr">
+    <row r="57" ht="78" customHeight="1">
+      <c r="A57" s="9" t="n"/>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>llm/llm3.py</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>prompt_sys=f"""You are a helpful assistant that writes data processors
         code to load different types of data for multimodal
         Auto-Machine learning task.</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/llm3.py</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="78" customHeight="1">
-      <c r="A60" s="2" t="n">
+    <row r="58" ht="58.5" customHeight="1">
+      <c r="A58" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>AIP-TranLAC: A Transformer-Based Method Integrating LSTM and Attention Mechanism for Predicting Anti-inflammatory Peptides</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>https://github.com/Renjingyi123/AIP-TranLAC</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>train.py</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>pep = pep + 'X' * (30-len_seq)
 for aa in pep:
-    current_pep.append(aa_dict[aa])
-data = rnn_utils.pad_sequence(pep_codes, batch_first=True)</t>
+    current_pep.append(aa_dict[aa])</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Renjingyi123/AIP-TranLAC/blob/HEAD/train.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="58.5" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>A Solver‐Aided Hierarchical Language for LLM‐Driven Systems</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>AIDL/constraint_fitting/filter_programs.py</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>if program_errors[prog] &lt; threshold:
+            shutil.copyfile(os.path.join("dataset_quantized", prog), os.path.join("dataset_filtered", prog))</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/AIDL/constraint_fitting/filter_programs.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="58.5" customHeight="1">
+      <c r="A60" s="8" t="n"/>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>scripts/2024.02.14.collect_designs.py</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>response = client.chat.completions.create(
+                model="gpt-4-turbo-preview",
+                messages=message_list,</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/Renjingyi123/AIP-TranLAC/blob/HEAD/train.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="39" customHeight="1">
-      <c r="A61" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>A Solver‐Aided Hierarchical Language for LLM‐Driven Systems</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/deGravity/aidl</t>
-        </is>
-      </c>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/2024.02.14.collect_designs.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="58.5" customHeight="1">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>AIDL/constraint_fitting/filter_programs.py</t>
+          <t>scripts/parse_structures.py</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Filtering</t>
+          <t>Prompting wrappers</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>shutil.copyfile(os.path.join("dataset_quantized", prog), os.path.join("dataset_filtered", prog))</t>
+          <t>response = client.chat.completions.create(
+                model="gpt-4-turbo-preview",
+                messages=message_list,</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/deGravity/aidl/blob/HEAD/AIDL/constraint_fitting/filter_programs.py</t>
+          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/parse_structures.py</t>
         </is>
       </c>
     </row>
     <row r="62" ht="39" customHeight="1">
-      <c r="A62" s="9" t="n"/>
-      <c r="B62" s="9" t="n"/>
-      <c r="C62" s="9" t="n"/>
+      <c r="A62" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>A Structured Framework for Evaluating and Enhancing LLM Robustness</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025</t>
+        </is>
+      </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>scripts/2024.02.14.collect_designs.py</t>
+          <t>src/preprocess.py</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Prompting wrappers</t>
+          <t>Tokenization</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>"role": "system",</t>
+          <t>patch = image[y:y+window_size, x:x+window_size]
+resized = cv2.resize(patch, (output_size, output_size))</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/2024.02.14.collect_designs.py</t>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/src/preprocess.py</t>
         </is>
       </c>
     </row>
@@ -8332,68 +8460,57 @@
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>scripts/parse_structures.py</t>
+          <t>scripts/analyze-exhibition-data.py</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Prompting wrappers</t>
+          <t>Filtering</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>response = client.chat.completions.create(</t>
+          <t>patterns = [ r'([^《]+)《([^》]+)》', r'([^《]+)、([^《]+)《([^》]+)》', r'([^《]+)、([^《]+)、([^《]+)《([^》]+)》' ]</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/deGravity/aidl/blob/HEAD/scripts/parse_structures.py</t>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/scripts/analyze-exhibition-data.py</t>
         </is>
       </c>
     </row>
     <row r="64" ht="39" customHeight="1">
-      <c r="A64" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>A Structured Framework for Evaluating and Enhancing LLM Robustness</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/yha9806/VULCA-EMNLP2025</t>
-        </is>
-      </c>
+      <c r="A64" s="8" t="n"/>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="8" t="n"/>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>src/preprocess.py</t>
+          <t>scripts/analyze-ppt-artworks.js</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Tokenization</t>
+          <t>Filtering</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>resized = cv2.resize(patch, (output_size, output_size))
-                patches.append(resized)</t>
+          <t>const artworkTitlePattern = /^[\\u4e00-\\u9fa5a-zA-Z\\s]+《.+》/;</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/src/preprocess.py</t>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/scripts/analyze-ppt-artworks.js</t>
         </is>
       </c>
     </row>
     <row r="65" ht="39" customHeight="1">
-      <c r="A65" s="8" t="n"/>
-      <c r="B65" s="8" t="n"/>
-      <c r="C65" s="8" t="n"/>
+      <c r="A65" s="9" t="n"/>
+      <c r="B65" s="9" t="n"/>
+      <c r="C65" s="9" t="n"/>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>scripts/analyze-exhibition-data.py</t>
+          <t>scripts/add-artwork2-refs.js</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -8403,66 +8520,68 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>patterns = [
-        r'([^《]+)《([^》]+)》',  # 基本模式</t>
+          <t>content = content.replace(pattern, (match, p1, p2, p3) =&gt; {</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/scripts/analyze-exhibition-data.py</t>
+          <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/scripts/add-artwork2-refs.js</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="C61:C63"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="B13:B19"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="A6:A7"/>
+  <mergeCells count="51">
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="A14:A18"/>
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="C42:C47"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="C13:C19"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="B42:B47"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="B33:B37"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A38:A44"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="C38:C44"/>
     <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B30:B36"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="C54:C56"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="A51:A53"/>
     <mergeCell ref="A2:A5"/>
+    <mergeCell ref="C33:C37"/>
     <mergeCell ref="C2:C5"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="A30:A36"/>
-    <mergeCell ref="C30:C36"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="A9:A10"/>
     <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C20:C24"/>
-    <mergeCell ref="B57:B59"/>
     <mergeCell ref="C28:C29"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C22:C26"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="B6:B8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
@@ -8662,7 +8781,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>258,470</t>
+          <t>253,640</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8793,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>23,383</t>
+          <t>26,469</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8805,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>281,853</t>
+          <t>280,109</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8893,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="58.5" customHeight="1">
+    <row r="2" ht="78" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -8805,8 +8924,8 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>tokenizer = AutoTokenizer.from_pretrained(SPLICEBERT_PATH)
-input_ids = tokenizer.encode(seq, add_special_tokens=True)</t>
+          <t>self.tokenizer = AutoTokenizer.from_pretrained(SPLICEBERT_PATH)
+        input_ids = self.tokenizer.encode(seq, add_special_tokens=True)</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -8816,7 +8935,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Non-trivial preprocessing code tokenizes sequences and derives features prior to model inference.</t>
+          <t>There is real preprocessing code (tokenization) in data/mydataset.py.</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -8825,7 +8944,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>8112</v>
+        <v>8520</v>
       </c>
     </row>
     <row r="3" ht="78" customHeight="1">
@@ -8849,18 +8968,18 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>tokenization</t>
+          <t>prompting, tokenization</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>utils/demo_dataloader.py</t>
+          <t>utils/demo_dataloader.py, preprocess/generate_vggttoken.py</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>all_aggregated_tokens = [[] for _ in range(24)] # trick for vggt
-    aggregated_tokens_list = []</t>
+          <t>def collate_fn_img(batch):
+    collated = {}; streamvggt = StreamVGGT()\n    ckpt = torch.load(args.ckpt, map_location=\"cpu\")</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -8870,7 +8989,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Non-trivial data preprocessing/tokenization pipeline code is present in the repo.</t>
+          <t>There are concrete preprocessing pipelines (data preparation and token generation) implemented in the repo.</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -8879,10 +8998,10 @@
         </is>
       </c>
       <c r="K3" s="4" t="n">
-        <v>17070</v>
-      </c>
-    </row>
-    <row r="4" ht="58.5" customHeight="1">
+        <v>17338</v>
+      </c>
+    </row>
+    <row r="4" ht="78" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -8913,7 +9032,8 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>prompt = (\n            "You are a Unity game architecture expert. Based on the following description, generate a JSON array of GameObject blueprints."\n</t>
+          <t>prompt = (
+            "You are a Unity game architecture expert. Based on the following description, generate a JSON array of GameObject blueprints.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -8923,7 +9043,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>The pipeline includes an LLM-prompt assembly component that actively preprocesses inputs by querying an LLM.</t>
+          <t>Executable prompting code is present, enabling model-driven generation of Unity assets.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -8932,10 +9052,10 @@
         </is>
       </c>
       <c r="K4" s="4" t="n">
-        <v>16255</v>
-      </c>
-    </row>
-    <row r="5" ht="78" customHeight="1">
+        <v>14756</v>
+      </c>
+    </row>
+    <row r="5" ht="117" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -8966,7 +9086,9 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>elif normalize_exp == \"StandardScaler\":\n\n            print (\"Normalizing expression- StandardScaler ...\")\n            self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp))</t>
+          <t>elif normalize_exp == "StandardScaler":
+            print ("Normalizing expression- StandardScaler ...")
+            self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp))</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -8976,7 +9098,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Executable data preprocessing (expression normalization) is present in JointDataset.</t>
+          <t>There is executable preprocessing code (data normalization) that prepares inputs before modeling.</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -8985,10 +9107,10 @@
         </is>
       </c>
       <c r="K5" s="4" t="n">
-        <v>10232</v>
-      </c>
-    </row>
-    <row r="6" ht="78" customHeight="1">
+        <v>9743</v>
+      </c>
+    </row>
+    <row r="6" ht="97.5" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -9021,7 +9143,8 @@
         <is>
           <t>def _bin_boundaries(data_d, K):
     """Equal-frequency (quantile) bin boundaries."""
-    boundaries = np.percentile(data_d, np.linspace(0, 100, K + 1))</t>
+    boundaries = np.percentile(data_d, np.linspace(0, 100, K + 1))
+    return np.unique(boundaries)</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -9031,7 +9154,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Repository contains executable data preprocessing utilities (binning/centering) used for analysis/experiments.</t>
+          <t>Discrete binning and related data transformations are present, constituting preprocessing code.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -9040,7 +9163,7 @@
         </is>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5922</v>
+        <v>5626</v>
       </c>
     </row>
     <row r="7" ht="195" customHeight="1">
@@ -9064,17 +9187,17 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>filtering, tokenization</t>
+          <t>filtering, prompting, tokenization</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py, PREPROCESS-NAMED: tools/make_audio_hf_dataset.ipynb, PREPROCESS-NAMED: tools/make_image_hf_dataset.ipynb, PREPROCESS-NAMED: tools/data_process/data_process_revise_dataset_name.py, PREPROCESS-NAMED: tools/live_bench/filter.ipynb</t>
+          <t>tools/make_audio_hf_dataset.ipynb, lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py, tools/live_bench/filter.ipynb, tools/data_process/data_process_revise_dataset_name.py</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>def analyze(self, text: str, offset: int = 0) -&gt; List[LexemeWithPositions]:; "audio": datasets.Audio(sampling_rate=16000),; "image": datasets.Image(),</t>
+          <t>prompt_list.append("&lt;|audio_bos|&gt;&lt;|AUDIO|&gt;&lt;|audio_eos|&gt;" + json_data['prompt']); class MplugOwlTokenizer(LlamaTokenizer):; filtered_data = data["test"].filter(lambda example: example["score"] and example["score"] &gt; 5)</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -9084,7 +9207,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>There is concrete executable preprocessing code (tokenization, filtering, and dataset construction) for multimodal data.</t>
+          <t>Executable preprocessing code implementing tokenization, prompting, and data filtering is present in multiple files.</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -9093,7 +9216,7 @@
         </is>
       </c>
       <c r="K7" s="4" t="n">
-        <v>20558</v>
+        <v>20521</v>
       </c>
     </row>
     <row r="8" ht="39" customHeight="1">
@@ -9200,10 +9323,10 @@
         </is>
       </c>
       <c r="K10" s="4" t="n">
-        <v>28134</v>
-      </c>
-    </row>
-    <row r="11" ht="97.5" customHeight="1">
+        <v>27674</v>
+      </c>
+    </row>
+    <row r="11" ht="156" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -9235,7 +9358,10 @@
       <c r="G11" s="4" t="inlineStr">
         <is>
           <t>def create_sliding_windows(data, _days_x=30, _days_y=7, _input_features=3):
-    """Create sliding windows for X and y data; scaler_X = MinMaxScaler(feature_range=(0, 1))
+    ...
+    for i in range(len(data) - _days_x - _days_y + 1):
+        # Input window: _days_x days of input features
+        X.append(data[i:i+_days_x, :_input_features]); scaler_X = MinMaxScaler(feature_range=(0, 1))
         scaler_y = MinMaxScaler(feature_range=(0, 1))</t>
         </is>
       </c>
@@ -9246,7 +9372,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Presence of non-trivial preprocessing code (time-windowing and normalization) confirms a preprocessing pipeline exists in the repo.</t>
+          <t>Executable preprocessing code (windowing and normalization) is present in _preprocess.py.</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -9255,7 +9381,7 @@
         </is>
       </c>
       <c r="K11" s="4" t="n">
-        <v>22210</v>
+        <v>20923</v>
       </c>
     </row>
     <row r="12" ht="58.5" customHeight="1">
@@ -9299,7 +9425,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Prompts are assembled and used to query a model, i.e., a prompting pipeline.</t>
+          <t>Prompt-building / input-assembly code for LLM is present.</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -9308,10 +9434,10 @@
         </is>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4728</v>
-      </c>
-    </row>
-    <row r="13" ht="78" customHeight="1">
+        <v>4036</v>
+      </c>
+    </row>
+    <row r="13" ht="97.5" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -9342,7 +9468,9 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>cs = ConstructSample(path_to_samples=train_round, cnt_round=cnt_round,\n                                 dic_traffic_env_conf=self.dic_traffic_env_conf)\n        cs.prepare_samples_for_system()</t>
+          <t>cs = ConstructSample(path_to_samples=train_round, cnt_round=cnt_round,
+                                 dic_traffic_env_conf=self.dic_traffic_env_conf)
+            cs.prepare_samples_for_system()</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -9352,7 +9480,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Executable preprocessing pipeline code is present (sample construction and filtering).</t>
+          <t>Non-trivial data preparation (sample construction and filtering) code is present in the preprocessing module.</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -9361,10 +9489,10 @@
         </is>
       </c>
       <c r="K13" s="4" t="n">
-        <v>20783</v>
-      </c>
-    </row>
-    <row r="14" ht="78" customHeight="1">
+        <v>21636</v>
+      </c>
+    </row>
+    <row r="14" ht="117" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -9385,17 +9513,21 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>tokenization</t>
+          <t>filtering, tokenization</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>msformer/MSEncoder.py</t>
+          <t>msformer/MSEncoder.py, msformer/masskg.py</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>encodings = self.tokenizer.batch_encode_plus(batch, padding=True, add_special_tokens=True)</t>
+          <t>encodings = self.tokenizer.batch_encode_plus(
+            batch, 
+            padding=True, 
+            add_special_tokens=True
+        ); frag_mols = Chem.GetMolFrags(fmol,asMols=True) #提取碎片分子(剔除键后)</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -9405,7 +9537,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Executable tokenization/encoding code for molecular fragments is present in the repo.</t>
+          <t>Executable preprocessing pipelines (tokenization and fragmentation) are present.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -9414,7 +9546,7 @@
         </is>
       </c>
       <c r="K14" s="4" t="n">
-        <v>15888</v>
+        <v>16870</v>
       </c>
     </row>
     <row r="15" ht="58.5" customHeight="1">
@@ -9474,12 +9606,12 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>utils/frcnn_utils/dataset.py, models/detrex/detectron2/detectron2/data/dataset_mapper.py</t>
+          <t>utils/frcnn_utils/dataset.py, extras/detr_extras/d2/detr/dataset_mapper.py, models/detrex/detrex/data/dataset_mappers/mask_former_instance_dataset_mapper.py</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>img = img / 255.\n    if resize:\n        img = sktsf.resize(img, (C, H * scale, W * scale), mode='reflect', anti_aliasing=False); image, transforms = T.apply_transform_gens(self.tfm_gens, image)</t>
+          <t>img = img / 255.\nif resize:\n        img = sktsf.resize(img, (C, H * scale, W * scale), mode='reflect', anti_aliasing=False); image, transforms = T.apply_transform_gens(self.tfm_gens, image); image = torch.as_tensor(np.ascontiguousarray(image.transpose(2, 0, 1)))</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -9489,7 +9621,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Non-trivial preprocessing/augmentation pipelines are present in multiple files.</t>
+          <t>Non-trivial preprocessing/augmentation code present that prepares data before model input.</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -9498,10 +9630,10 @@
         </is>
       </c>
       <c r="K16" s="4" t="n">
-        <v>22575</v>
-      </c>
-    </row>
-    <row r="17" ht="312" customHeight="1">
+        <v>23480</v>
+      </c>
+    </row>
+    <row r="17" ht="156" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -9522,23 +9654,18 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>filtering, prompting, tokenization</t>
+          <t>prompting, tokenization</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>train/dpo_train.py, train/dpo_train.py, train/train.py</t>
+          <t>train/sft_training.py, train/generate_fol.py, train/dpo_train.py</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>def to_hha_chat_template(samples):
-    instruction_text = extract_instruction(samples['chosen'])
-    chosen_text = extract_last_assistant(samples['chosen'])
-    rejected_text = extract_last_assistant(samples['rejected'])
-    return {"prompt": instruction_text, 'chosen': chosen_text, 'rejected': rejected_text}; train_dataset = load_dataset("parquet", data_files=train_data_path)["train"]
-    train_dataset = train_dataset.filter(lambda sample: sample['better_response_id'] == sample['safer_response_id']; prompt_input_ids = Tokenizer.encode(prompt_input, add_special_tokens=False)
-    prompt_output_ids = Tokenizer.encode(prompt_output, add_special_tokens=False)</t>
+          <t>prompt_input_ids = Tokenizer.encode(prompt_input, add_special_tokens=False)
+prompt_output_ids = Tokenizer.encode(prompt_output, add_special_tokens=False); inputs = tokenizer(prompts, return_tensors="pt", padding=True, padding_side="left").to(device); text = tokenizer.apply_chat_template([{'role': "user", "content": samples['prompt']}], tokenize=False, add_generation_prompt=True, enable_thinking=False)</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -9548,7 +9675,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Distinct preprocessing code for tokenization, prompting, and data filtering is present in the repository.</t>
+          <t>Executable preprocessing and prompt-building code are present in multiple scripts.</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -9557,7 +9684,7 @@
         </is>
       </c>
       <c r="K17" s="4" t="n">
-        <v>29302</v>
+        <v>14798</v>
       </c>
     </row>
     <row r="18" ht="78" customHeight="1">
@@ -9591,7 +9718,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>self.idps_filt = idps_filt.dropna(how= 'any', axis=0) # Drop rows (subjects) with NAs; return idp_tokenization('cpu',count,self.rnd_st,data.index,{'train':data.values.astype('float')})</t>
+          <t>return idp_tokenization('cpu',count,self.rnd_st,data.index,{'train':data.values.astype('float')}); self.idps_filt = idps_filt.dropna(how= 'any', axis=0) # Drop rows (subjects) with NAs</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -9601,7 +9728,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>The repository contains executable preprocessing code (data cleaning and tokenization) in the dataset_template module.</t>
+          <t>Executable preprocessing (tokenization hook and data filtering/cleaning) present in the repository.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -9610,7 +9737,7 @@
         </is>
       </c>
       <c r="K18" s="4" t="n">
-        <v>22356</v>
+        <v>22316</v>
       </c>
     </row>
     <row r="19" ht="58.5" customHeight="1">
@@ -9654,7 +9781,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>The repository includes non-trivial prompt-building logic that assembles model inputs.</t>
+          <t>Prompt-building pipeline is implemented to assemble inputs for the language model.</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -9663,10 +9790,10 @@
         </is>
       </c>
       <c r="K19" s="4" t="n">
-        <v>9756</v>
-      </c>
-    </row>
-    <row r="20" ht="331.5" customHeight="1">
+        <v>9708</v>
+      </c>
+    </row>
+    <row r="20" ht="78" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -9687,30 +9814,17 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>prompting, tokenization</t>
+          <t>prompting</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>token_shap/base.py, token_shap/base.py</t>
+          <t>token_shap/agent_shap.py</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>def encode_image_to_base64(image_path: str) -&gt; str:
-    with open(image_path, "rb") as image_file:
-        return base64.b64encode(image_file.read()).decode('utf-8'); def interact_with_ollama(
-    prompt: Optional[str] = None, 
-    messages: Optional[Any] = None,
-    image_path: Optional[str] = None,
-    model: str = 'openhermes2.5-mistral', 
-    stream: bool = False,
-    output_handler: Callable[[str], None] = default_output_handler,
-    api_url: Optional[str] = None
-) -&gt; str:
-    ...
-    if image_path:
-        data['images'] = [encode_image_to_base64(image_path)]</t>
+          <t>def _prepare_generate_args(self, content: Any, **kwargs) -&gt; Dict:\n    """Prepare arguments for baseline generation with ALL tools."""\n    return {"prompt": content, "tools": self.tools}</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -9720,7 +9834,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>There exist tangible preprocessing utilities (tokenization-like handling of image data and prompting payload construction) in the codebase.</t>
+          <t>There is non-trivial code assembling prompts and tool selections (prompting category) used to drive model inputs.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -9729,10 +9843,10 @@
         </is>
       </c>
       <c r="K20" s="4" t="n">
-        <v>27682</v>
-      </c>
-    </row>
-    <row r="21" ht="312" customHeight="1">
+        <v>28018</v>
+      </c>
+    </row>
+    <row r="21" ht="156" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -9753,29 +9867,20 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>filtering, prompting, tokenization</t>
+          <t>filtering, tokenization</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>src/abliterate.py, src/evaluate.py, src/evaluate.py</t>
+          <t>src/abliterate.py, src/abliterate.py, src/chat.py, src/evaluate.py</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
           <t>if isinstance(config["num-harmful"], int) and config["num-harmful"] &gt; 0:
-        harmful_list = random.sample(harmful_list, config["num-harmful"]); evaluation_prompts = [
-            f"{system_prompt}\n"
-            f"### Prompt:\n{question}\n\n"
-            f"### Response:\n{response}\n\n"
-            "CLASSIFICATION: "
-            for question, response in zip(batch_questions, batch_responses)
-        ]; inputs = tokenizer.batch_encode_plus(
-        evaluation_prompts,
-        return_tensors="pt",
-        padding=True,
-        truncation=True,
-    ).to(device)</t>
+        harmful_list = random.sample(harmful_list, config["num-harmful"]); harmful_list = load_data(config["data-harmful"]); toks = tokenizer.apply_chat_template(
+            conversation=conversation, add_generation_prompt=True, return_tensors="pt"
+        )</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -9785,7 +9890,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>There are non-trivial preprocessing pipelines for data filtering and prompt construction, indicating executable preprocessing code across files.</t>
+          <t>There is real preprocessing/pipeline code that reads, filters, and tokenizes data before model usage.</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -9794,10 +9899,10 @@
         </is>
       </c>
       <c r="K21" s="4" t="n">
-        <v>23375</v>
-      </c>
-    </row>
-    <row r="22" ht="97.5" customHeight="1">
+        <v>22324</v>
+      </c>
+    </row>
+    <row r="22" ht="312" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -9818,7 +9923,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>filtering</t>
+          <t>prompting</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -9830,7 +9935,12 @@
         <is>
           <t>def filter(stage_response):
     prompt_sys=f""" 
-    {stage_response} is the stage response of the LLM, your task is to check whether it has moral or other safety problems."</t>
+    {stage_response} is the stage response of the LLM, your task is to check whether it has moral or other safety problems.
+    if it has, please modify the response without changing the original format to avoid these prblems. If not,simply output the original {stage_response} without changing anything or telling the user it does not have problems.
+    If you find it difficult to modify the response without changing the original meaning, output Filtered information and add reason why it is filtered.
+    """
+    response=get_completion(prompt_sys)
+    return response</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -9840,7 +9950,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Filtering code exists that processes model outputs; this constitutes a preprocessing-like data cleaning step.</t>
+          <t>Prompting-based preprocessing code is present, indicating executable prompt assembly and handling.</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -9849,7 +9959,7 @@
         </is>
       </c>
       <c r="K22" s="4" t="n">
-        <v>10305</v>
+        <v>10427</v>
       </c>
     </row>
     <row r="23" ht="58.5" customHeight="1">
@@ -9883,7 +9993,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>pep = pep + 'X' * (30-len_seq)\n            for aa in pep:\n                current_pep.append(aa_dict[aa])</t>
+          <t>for aa in pep:\n                current_pep.append(aa_dict[aa])</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -9893,7 +10003,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Executable preprocessing/tokenization code (sequence encoding and padding) is present in train.py.</t>
+          <t>Explicit sequence tokenization and padding logic are present in the preprocessing workflow.</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -9902,7 +10012,7 @@
         </is>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5424</v>
+        <v>12212</v>
       </c>
     </row>
     <row r="24" ht="39" customHeight="1">
@@ -9998,7 +10108,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>if program_errors[prog] &lt; threshold:\n            shutil.copyfile(os.path.join("dataset_quantized", prog), os.path.join("dataset_filtered", prog))</t>
+          <t>if program_errors[prog] &lt; threshold:\n            counter += 1\n            shutil.copyfile(os.path.join("dataset_quantized", prog), os.path.join("dataset_filtered", prog))</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -10008,7 +10118,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>There is concrete preprocessing/ Filtering code that operates on the data prior to model use.</t>
+          <t>A preprocessing filtering pipeline is present in the repo.</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -10017,7 +10127,7 @@
         </is>
       </c>
       <c r="K26" s="4" t="n">
-        <v>17625</v>
+        <v>17641</v>
       </c>
     </row>
     <row r="27" ht="195" customHeight="1">
@@ -10051,7 +10161,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>patch = image[y:y+window_size, x:x+window_size]\n\n                # Resize to output size\n                resized = cv2.resize(patch, (output_size, output_size))\n                patches.append(resized); saliency = calculate_saliency(patch)\n\n                # Adaptive stride based on saliency\n                if saliency &lt; saliency_threshold_low:</t>
+          <t>patches.append(resized); if saliency &lt; saliency_threshold_low:\n                    # Low information, larger stride</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -10061,7 +10171,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Executable image preprocessing code implementing patch extraction and saliency-based filtering is present.</t>
+          <t>Tokenization-like image patch extraction and saliency-based filtering preprocessing code are present.</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -10070,7 +10180,7 @@
         </is>
       </c>
       <c r="K27" s="4" t="n">
-        <v>23937</v>
+        <v>23458</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -10146,7 +10256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10195,7 +10305,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="39" customHeight="1">
+    <row r="2" ht="78" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -10221,8 +10331,8 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>tokenizer = AutoTokenizer.from_pretrained(SPLICEBERT_PATH)
-input_ids = tokenizer.encode(seq, add_special_tokens=True)</t>
+          <t>self.tokenizer = AutoTokenizer.from_pretrained(SPLICEBERT_PATH)
+        input_ids = self.tokenizer.encode(seq, add_special_tokens=True)</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -10231,7 +10341,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58.5" customHeight="1">
+    <row r="3" ht="39" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -10252,220 +10362,224 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>def collate_fn_img(batch):
+    collated = {}</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/utils/demo_dataloader.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="39" customHeight="1">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>preprocess/generate_vggttoken.py</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>all_aggregated_tokens = [[] for _ in range(24)] # trick for vggt
-    aggregated_tokens_list = []</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/utils/demo_dataloader.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="58.5" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>90% Faster, 100% Code-Free: MLLM-Driven Zero-Code 3D Game Development</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/yxwan123/UniGen</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>blue_pipeline.py</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Prompting wrappers</t>
-        </is>
-      </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>prompt = (\n            "You are a Unity game architecture expert. Based on the following description, generate a JSON array of GameObject blueprints."\n</t>
+          <t>streamvggt = StreamVGGT()\n    ckpt = torch.load(args.ckpt, map_location=\"cpu\")</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/yxwan123/UniGen/blob/HEAD/blue_pipeline.py</t>
+          <t>https://github.com/hustvl/4DLangVGGT/blob/HEAD/preprocess/generate_vggttoken.py</t>
         </is>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1">
       <c r="A5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>90% Faster, 100% Code-Free: MLLM-Driven Zero-Code 3D Game Development</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/yxwan123/UniGen</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>blue_pipeline.py</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>prompt = (
+            "You are a Unity game architecture expert. Based on the following description, generate a JSON array of GameObject blueprints.</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/yxwan123/UniGen/blob/HEAD/blue_pipeline.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="117" customHeight="1">
+      <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Abstract A024: DeepVul: A multi-task transformer model for joint prediction of gene essentiality and drug response</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>https://github.com/alaaj27/DeepVul.git</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>src/JointDataset.py</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>elif normalize_exp == \"StandardScaler\":\n\n            print (\"Normalizing expression- StandardScaler ...\")\n            self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp))</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>elif normalize_exp == "StandardScaler":
+            print ("Normalizing expression- StandardScaler ...")
+            self.data_exp = self.normalize_tensor_rows(self.normalize_tensor_columns(self.data_exp))</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>https://github.com/alaaj27/DeepVul/blob/HEAD/src/JointDataset.py</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="78" customHeight="1">
-      <c r="A6" s="2" t="n">
+    <row r="7" ht="97.5" customHeight="1">
+      <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Accelerated Aggregated D-Optimal Designs for Estimating Main Effects in Black-Box Models</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>https://github.com/cchihyu/A2D2E</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>src/algorithms.py</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>def _bin_boundaries(data_d, K):
     """Equal-frequency (quantile) bin boundaries."""
-    boundaries = np.percentile(data_d, np.linspace(0, 100, K + 1))</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
+    boundaries = np.percentile(data_d, np.linspace(0, 100, K + 1))
+    return np.unique(boundaries)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>https://github.com/cchihyu/A2D2E/blob/HEAD/src/algorithms.py</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="58.5" customHeight="1">
-      <c r="A7" s="2" t="n">
+    <row r="8" ht="39" customHeight="1">
+      <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>AccidentBench: Benchmarking Multimodal Understanding and Reasoning in Vehicle Accidents and Beyond</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>https://github.com/SafeRL-Lab/AccidentBench</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>tools/make_audio_hf_dataset.ipynb</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>prompt_list.append("&lt;|audio_bos|&gt;&lt;|AUDIO|&gt;&lt;|audio_eos|&gt;" + json_data['prompt'])</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/make_audio_hf_dataset.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="39" customHeight="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>def analyze(self, text: str, offset: int = 0) -&gt; List[LexemeWithPositions]:</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/tasks/mmsearch/retrieve_content/tokenization/tokenizers.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="39" customHeight="1">
-      <c r="A8" s="9" t="n"/>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>PREPROCESS-NAMED: tools/make_audio_hf_dataset.ipynb</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>"audio": datasets.Audio(sampling_rate=16000),</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/PREPROCESS-NAMED: tools/make_audio_hf_dataset.ipynb</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="39" customHeight="1">
-      <c r="A9" s="9" t="n"/>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>PREPROCESS-NAMED: tools/make_image_hf_dataset.ipynb</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>"image": datasets.Image(),</t>
+          <t>class MplugOwlTokenizer(LlamaTokenizer):</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/PREPROCESS-NAMED: tools/make_image_hf_dataset.ipynb</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58.5" customHeight="1">
-      <c r="A10" s="9" t="n"/>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/lmms_eval/models/mplug_owl_video/tokenization_mplug_owl.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="39" customHeight="1">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>PREPROCESS-NAMED: tools/data_process/data_process_revise_dataset_name.py</t>
+          <t>tools/live_bench/filter.ipynb</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -10475,22 +10589,22 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>def rename_files_in_folder(folder_path):</t>
+          <t>filtered_data = data["test"].filter(lambda example: example["score"] and example["score"] &gt; 5)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/PREPROCESS-NAMED: tools/data_process/data_process_revise_dataset_name.py</t>
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/live_bench/filter.ipynb</t>
         </is>
       </c>
     </row>
     <row r="11" ht="39" customHeight="1">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>PREPROCESS-NAMED: tools/live_bench/filter.ipynb</t>
+          <t>tools/data_process/data_process_revise_dataset_name.py</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -10500,16 +10614,16 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>filtered_data = data["test"].filter(lambda example: example["score"] and example["score"] &gt; 5)</t>
+          <t>new_name = f"ocean_space_long_{index}{ext}"</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/PREPROCESS-NAMED: tools/live_bench/filter.ipynb</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58.5" customHeight="1">
+          <t>https://github.com/SafeRL-Lab/AccidentBench/blob/HEAD/tools/data_process/data_process_revise_dataset_name.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="117" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>10</v>
       </c>
@@ -10536,7 +10650,10 @@
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>def create_sliding_windows(data, _days_x=30, _days_y=7, _input_features=3):
-    """Create sliding windows for X and y data</t>
+    ...
+    for i in range(len(data) - _days_x - _days_y + 1):
+        # Input window: _days_x days of input features
+        X.append(data[i:i+_days_x, :_input_features])</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -10546,9 +10663,9 @@
       </c>
     </row>
     <row r="13" ht="39" customHeight="1">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
       <c r="D13" s="4" t="inlineStr">
         <is>
           <t>_preprocess.py</t>
@@ -10606,7 +10723,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="78" customHeight="1">
+    <row r="15" ht="97.5" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>12</v>
       </c>
@@ -10632,7 +10749,9 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>cs = ConstructSample(path_to_samples=train_round, cnt_round=cnt_round,\n                                 dic_traffic_env_conf=self.dic_traffic_env_conf)\n        cs.prepare_samples_for_system()</t>
+          <t>cs = ConstructSample(path_to_samples=train_round, cnt_round=cnt_round,
+                                 dic_traffic_env_conf=self.dic_traffic_env_conf)
+            cs.prepare_samples_for_system()</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -10641,7 +10760,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="39" customHeight="1">
+    <row r="16" ht="97.5" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>13</v>
       </c>
@@ -10667,7 +10786,11 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>encodings = self.tokenizer.batch_encode_plus(batch, padding=True, add_special_tokens=True)</t>
+          <t>encodings = self.tokenizer.batch_encode_plus(
+            batch, 
+            padding=True, 
+            add_special_tokens=True
+        )</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -10676,615 +10799,646 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="58.5" customHeight="1">
-      <c r="A17" s="2" t="n">
+    <row r="17" ht="39" customHeight="1">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>msformer/masskg.py</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>frag_mols = Chem.GetMolFrags(fmol,asMols=True) #提取碎片分子(剔除键后)</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ZJUFanLab/MSformer/blob/HEAD/msformer/masskg.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58.5" customHeight="1">
+      <c r="A18" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Adversarial Attention Perturbations for Large Object Detection Transformers</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>https://github.com/zacharyyahn/AFOG</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>utils/frcnn_utils/dataset.py</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>img = img / 255.\n    if resize:\n        img = sktsf.resize(img, (C, H * scale, W * scale), mode='reflect', anti_aliasing=False)</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>img = img / 255.\nif resize:\n        img = sktsf.resize(img, (C, H * scale, W * scale), mode='reflect', anti_aliasing=False)</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/utils/frcnn_utils/dataset.py</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="39" customHeight="1">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>models/detrex/detectron2/detectron2/data/dataset_mapper.py</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
+    <row r="19" ht="39" customHeight="1">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>extras/detr_extras/d2/detr/dataset_mapper.py</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>image, transforms = T.apply_transform_gens(self.tfm_gens, image)</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detectron2/detectron2/data/dataset_mapper.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="175.5" customHeight="1">
-      <c r="A19" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>A First-Order Logic-Based Alternative to Reward Models in RLHF</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/ChunjinJiang/sgrpo</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>train/dpo_train.py</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Prompting wrappers</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>def to_hha_chat_template(samples):
-    instruction_text = extract_instruction(samples['chosen'])
-    chosen_text = extract_last_assistant(samples['chosen'])
-    rejected_text = extract_last_assistant(samples['rejected'])
-    return {"prompt": instruction_text, 'chosen': chosen_text, 'rejected': rejected_text}</t>
-        </is>
-      </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/dpo_train.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="78" customHeight="1">
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/extras/detr_extras/d2/detr/dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58.5" customHeight="1">
       <c r="A20" s="9" t="n"/>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="4" t="inlineStr">
         <is>
+          <t>models/detrex/detrex/data/dataset_mappers/mask_former_instance_dataset_mapper.py</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>image = torch.as_tensor(np.ascontiguousarray(image.transpose(2, 0, 1)))</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/zacharyyahn/AFOG/blob/HEAD/models/detrex/detrex/data/dataset_mappers/mask_former_instance_dataset_mapper.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="78" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>A First-Order Logic-Based Alternative to Reward Models in RLHF</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>train/sft_training.py</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>prompt_input_ids = Tokenizer.encode(prompt_input, add_special_tokens=False)
+prompt_output_ids = Tokenizer.encode(prompt_output, add_special_tokens=False)</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/sft_training.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="39" customHeight="1">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>train/generate_fol.py</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>inputs = tokenizer(prompts, return_tensors="pt", padding=True, padding_side="left").to(device)</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/generate_fol.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58.5" customHeight="1">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
           <t>train/dpo_train.py</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Filtering</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>train_dataset = load_dataset("parquet", data_files=train_data_path)["train"]
-    train_dataset = train_dataset.filter(lambda sample: sample['better_response_id'] == sample['safer_response_id']</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>text = tokenizer.apply_chat_template([{'role': "user", "content": samples['prompt']}], tokenize=False, add_generation_prompt=True, enable_thinking=False)</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/dpo_train.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="78" customHeight="1">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>train/train.py</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>prompt_input_ids = Tokenizer.encode(prompt_input, add_special_tokens=False)
-    prompt_output_ids = Tokenizer.encode(prompt_output, add_special_tokens=False)</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/ChunjinJiang/sgrpo/blob/HEAD/train/train.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="39" customHeight="1">
-      <c r="A22" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>A foundation model for learning genetic associations from brain imaging phenotypes</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/IBM/comical</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>src/dataset_template.py</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Filtering</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>self.idps_filt = idps_filt.dropna(how= 'any', axis=0) # Drop rows (subjects) with NAs</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/IBM/comical/blob/HEAD/src/dataset_template.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="39" customHeight="1">
-      <c r="A23" s="8" t="n"/>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>src/dataset_template.py</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>return idp_tokenization('cpu',count,self.rnd_st,data.index,{'train':data.values.astype('float')})</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/IBM/comical/blob/HEAD/src/dataset_template.py</t>
         </is>
       </c>
     </row>
     <row r="24" ht="39" customHeight="1">
       <c r="A24" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>A foundation model for learning genetic associations from brain imaging phenotypes</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>src/dataset_template.py</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>return idp_tokenization('cpu',count,self.rnd_st,data.index,{'train':data.values.astype('float')})</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical/blob/HEAD/src/dataset_template.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="39" customHeight="1">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>src/dataset_template.py</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>self.idps_filt = idps_filt.dropna(how= 'any', axis=0) # Drop rows (subjects) with NAs</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/IBM/comical/blob/HEAD/src/dataset_template.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="39" customHeight="1">
+      <c r="A26" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Agentmandering: A Game-Theoretic Framework for Fair Redistricting via Large Language Model Agents</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>https://github.com/Lihaogx/AgentMandering</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>model/agent.py</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Prompting wrappers</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>prompt = self.background_info + "\n\n" + self.party_name_prompt</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>https://github.com/Lihaogx/AgentMandering/blob/HEAD/model/agent.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="78" customHeight="1">
-      <c r="A25" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>AgentSHAP: Interpreting LLM Agent Tool Importance with Monte Carlo Shapley Value Estimation</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/GenAISHAP/TokenSHAP</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>token_shap/base.py</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>def encode_image_to_base64(image_path: str) -&gt; str:
-    with open(image_path, "rb") as image_file:
-        return base64.b64encode(image_file.read()).decode('utf-8')</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/GenAISHAP/TokenSHAP/blob/HEAD/token_shap/base.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="273" customHeight="1">
-      <c r="A26" s="8" t="n"/>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>token_shap/base.py</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Prompting wrappers</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>def interact_with_ollama(
-    prompt: Optional[str] = None, 
-    messages: Optional[Any] = None,
-    image_path: Optional[str] = None,
-    model: str = 'openhermes2.5-mistral', 
-    stream: bool = False,
-    output_handler: Callable[[str], None] = default_output_handler,
-    api_url: Optional[str] = None
-) -&gt; str:
-    ...
-    if image_path:
-        data['images'] = [encode_image_to_base64(image_path)]</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/GenAISHAP/TokenSHAP/blob/HEAD/token_shap/base.py</t>
         </is>
       </c>
     </row>
     <row r="27" ht="78" customHeight="1">
       <c r="A27" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>AgentSHAP: Interpreting LLM Agent Tool Importance with Monte Carlo Shapley Value Estimation</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/GenAISHAP/TokenSHAP</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>token_shap/agent_shap.py</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>def _prepare_generate_args(self, content: Any, **kwargs) -&gt; Dict:\n    """Prepare arguments for baseline generation with ALL tools."""\n    return {"prompt": content, "tools": self.tools}</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/GenAISHAP/TokenSHAP/blob/HEAD/token_shap/agent_shap.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="78" customHeight="1">
+      <c r="A28" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>A Granular Study of Safety Pretraining under Model Abliteration</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>https://github.com/shashankskagnihotri/safety_pretraining</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>src/abliterate.py</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>if isinstance(config["num-harmful"], int) and config["num-harmful"] &gt; 0:
         harmful_list = random.sample(harmful_list, config["num-harmful"])</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/abliterate.py</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="156" customHeight="1">
-      <c r="A28" s="9" t="n"/>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>src/evaluate.py</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Prompting wrappers</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>evaluation_prompts = [
-            f"{system_prompt}\n"
-            f"### Prompt:\n{question}\n\n"
-            f"### Response:\n{response}\n\n"
-            "CLASSIFICATION: "
-            for question, response in zip(batch_questions, batch_responses)
-        ]</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/evaluate.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="117" customHeight="1">
+    <row r="29" ht="39" customHeight="1">
       <c r="A29" s="8" t="n"/>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="4" t="inlineStr">
         <is>
+          <t>src/abliterate.py</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>harmful_list = load_data(config["data-harmful"])</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/abliterate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="78" customHeight="1">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>src/chat.py</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>toks = tokenizer.apply_chat_template(
+            conversation=conversation, add_generation_prompt=True, return_tensors="pt"
+        )</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/chat.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="39" customHeight="1">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
           <t>src/evaluate.py</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Tokenization</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>inputs = tokenizer.batch_encode_plus(
-        evaluation_prompts,
-        return_tensors="pt",
-        padding=True,
-        truncation=True,
-    ).to(device)</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Filtering</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>harmful_df = pd.read_parquet(harmful_data_path)\nharmful_df["label"] = "harmful"</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>https://github.com/shashankskagnihotri/safety_pretraining/blob/HEAD/src/evaluate.py</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="97.5" customHeight="1">
-      <c r="A30" s="2" t="n">
+    <row r="32" ht="312" customHeight="1">
+      <c r="A32" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>A Human-Centered Mutltimodal AutoML Framework for Discriminative and Generative Tasks with Large Language Models</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>https://github.com/richarf22/UniAutoML</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>llm/filter.py</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Filtering</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Prompting wrappers</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>def filter(stage_response):
     prompt_sys=f""" 
-    {stage_response} is the stage response of the LLM, your task is to check whether it has moral or other safety problems."</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
+    {stage_response} is the stage response of the LLM, your task is to check whether it has moral or other safety problems.
+    if it has, please modify the response without changing the original format to avoid these prblems. If not,simply output the original {stage_response} without changing anything or telling the user it does not have problems.
+    If you find it difficult to modify the response without changing the original meaning, output Filtered information and add reason why it is filtered.
+    """
+    response=get_completion(prompt_sys)
+    return response</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>https://github.com/richarf22/UniAutoML/blob/HEAD/llm/filter.py</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="39" customHeight="1">
-      <c r="A31" s="2" t="n">
+    <row r="33" ht="39" customHeight="1">
+      <c r="A33" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>AIP-TranLAC: A Transformer-Based Method Integrating LSTM and Attention Mechanism for Predicting Anti-inflammatory Peptides</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>https://github.com/Renjingyi123/AIP-TranLAC</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>train.py</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>pep = pep + 'X' * (30-len_seq)\n            for aa in pep:\n                current_pep.append(aa_dict[aa])</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>for aa in pep:\n                current_pep.append(aa_dict[aa])</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>https://github.com/Renjingyi123/AIP-TranLAC/blob/HEAD/train.py</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="58.5" customHeight="1">
-      <c r="A32" s="2" t="n">
+    <row r="34" ht="58.5" customHeight="1">
+      <c r="A34" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>A Solver‐Aided Hierarchical Language for LLM‐Driven Systems</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>https://github.com/deGravity/aidl</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>AIDL/constraint_fitting/filter_programs.py</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>if program_errors[prog] &lt; threshold:\n            shutil.copyfile(os.path.join("dataset_quantized", prog), os.path.join("dataset_filtered", prog))</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>if program_errors[prog] &lt; threshold:\n            counter += 1\n            shutil.copyfile(os.path.join("dataset_quantized", prog), os.path.join("dataset_filtered", prog))</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>https://github.com/deGravity/aidl/blob/HEAD/AIDL/constraint_fitting/filter_programs.py</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="78" customHeight="1">
-      <c r="A33" s="2" t="n">
+    <row r="35" ht="39" customHeight="1">
+      <c r="A35" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>A Structured Framework for Evaluating and Enhancing LLM Robustness</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>https://github.com/yha9806/VULCA-EMNLP2025</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>src/preprocess.py</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>patch = image[y:y+window_size, x:x+window_size]\n\n                # Resize to output size\n                resized = cv2.resize(patch, (output_size, output_size))\n                patches.append(resized)</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>patches.append(resized)</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/src/preprocess.py</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="58.5" customHeight="1">
-      <c r="A34" s="8" t="n"/>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="4" t="inlineStr">
+    <row r="36" ht="39" customHeight="1">
+      <c r="A36" s="9" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>src/preprocess.py</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Filtering</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>saliency = calculate_saliency(patch)\n\n                # Adaptive stride based on saliency\n                if saliency &lt; saliency_threshold_low:</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>if saliency &lt; saliency_threshold_low:\n                    # Low information, larger stride</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>https://github.com/yha9806/VULCA-EMNLP2025/blob/HEAD/src/preprocess.py</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="C27:C29"/>
+  <mergeCells count="27">
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="A24:A25"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="B8:B11"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A3:A4"/>
     <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="A18:A20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
@@ -11320,6 +11474,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11453,7 +11609,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>305,282</t>
+          <t>292,180</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11621,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>56,947</t>
+          <t>59,845</t>
         </is>
       </c>
     </row>
@@ -11477,7 +11633,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>362,229</t>
+          <t>352,025</t>
         </is>
       </c>
     </row>
